--- a/raw/Từ vựng.xlsx
+++ b/raw/Từ vựng.xlsx
@@ -71007,1670 +71007,1670 @@
       </c>
     </row>
     <row r="3026">
-      <c r="A3026" t="inlineStr">
+      <c r="A3026" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3026" t="inlineStr">
+      <c r="B3026" s="0" t="inlineStr">
         <is>
           <t>难堪</t>
         </is>
       </c>
-      <c r="C3026" t="inlineStr">
+      <c r="C3026" s="0" t="inlineStr">
         <is>
           <t>nánkān</t>
         </is>
       </c>
-      <c r="D3026" t="inlineStr">
+      <c r="D3026" s="0" t="inlineStr">
         <is>
           <t>感到很不好意思，很尴尬，下不来台</t>
         </is>
       </c>
-      <c r="E3026" t="inlineStr">
+      <c r="E3026" s="0" t="inlineStr">
         <is>
           <t>khó xử, bẽ bàng, ngượng</t>
         </is>
       </c>
-      <c r="F3026" t="inlineStr">
-        <is>
-          <t>这件事情让他感到很难堪，脸都涨红了。</t>
-        </is>
-      </c>
-      <c r="G3026" t="inlineStr"/>
-      <c r="H3026" t="inlineStr"/>
+      <c r="F3026" s="0" t="inlineStr">
+        <is>
+          <t>上课时被学生问到一个我也不太确定的语法，我一时有点难堪。</t>
+        </is>
+      </c>
+      <c r="G3026" s="0" t="inlineStr"/>
+      <c r="H3026" s="0" t="inlineStr"/>
     </row>
     <row r="3027">
-      <c r="A3027" t="inlineStr">
+      <c r="A3027" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3027" t="inlineStr">
+      <c r="B3027" s="0" t="inlineStr">
         <is>
           <t>岂有此理</t>
         </is>
       </c>
-      <c r="C3027" t="inlineStr">
+      <c r="C3027" s="0" t="inlineStr">
         <is>
           <t>qǐyǒucǐlǐ</t>
         </is>
       </c>
-      <c r="D3027" t="inlineStr">
+      <c r="D3027" s="0" t="inlineStr">
         <is>
           <t>哪有这样的道理；表示对不合理的事很生气</t>
         </is>
       </c>
-      <c r="E3027" t="inlineStr">
+      <c r="E3027" s="0" t="inlineStr">
         <is>
           <t>thật vô lý, làm gì có cái lý đó</t>
         </is>
       </c>
-      <c r="F3027" t="inlineStr">
-        <is>
-          <t>大家好心问你，你倒说别人多管闲事，真是岂有此理！</t>
-        </is>
-      </c>
-      <c r="G3027" t="inlineStr"/>
-      <c r="H3027" t="inlineStr"/>
+      <c r="F3027" s="0" t="inlineStr">
+        <is>
+          <t>我熬夜背了那么多生词，考试居然一个都没考到，真是岂有此理！</t>
+        </is>
+      </c>
+      <c r="G3027" s="0" t="inlineStr"/>
+      <c r="H3027" s="0" t="inlineStr"/>
     </row>
     <row r="3028">
-      <c r="A3028" t="inlineStr">
+      <c r="A3028" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3028" t="inlineStr">
+      <c r="B3028" s="0" t="inlineStr">
         <is>
           <t>庸俗</t>
         </is>
       </c>
-      <c r="C3028" t="inlineStr">
+      <c r="C3028" s="0" t="inlineStr">
         <is>
           <t>yōngsú</t>
         </is>
       </c>
-      <c r="D3028" t="inlineStr">
+      <c r="D3028" s="0" t="inlineStr">
         <is>
           <t>不高雅，低级，没有品味</t>
         </is>
       </c>
-      <c r="E3028" t="inlineStr">
+      <c r="E3028" s="0" t="inlineStr">
         <is>
           <t>tầm thường, dung tục</t>
         </is>
       </c>
-      <c r="F3028" t="inlineStr">
-        <is>
-          <t>这歌曲的歌词太庸俗了。</t>
-        </is>
-      </c>
-      <c r="G3028" t="inlineStr"/>
-      <c r="H3028" t="inlineStr"/>
+      <c r="F3028" s="0" t="inlineStr">
+        <is>
+          <t>我不太喜欢那种只谈钱、谈名牌的庸俗话题。</t>
+        </is>
+      </c>
+      <c r="G3028" s="0" t="inlineStr"/>
+      <c r="H3028" s="0" t="inlineStr"/>
     </row>
     <row r="3029">
-      <c r="A3029" t="inlineStr">
+      <c r="A3029" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3029" t="inlineStr">
+      <c r="B3029" s="0" t="inlineStr">
         <is>
           <t>档次</t>
         </is>
       </c>
-      <c r="C3029" t="inlineStr">
+      <c r="C3029" s="0" t="inlineStr">
         <is>
           <t>dàngcì</t>
         </is>
       </c>
-      <c r="D3029" t="inlineStr">
+      <c r="D3029" s="0" t="inlineStr">
         <is>
           <t>按质量或水平分出的高低等级</t>
         </is>
       </c>
-      <c r="E3029" t="inlineStr">
+      <c r="E3029" s="0" t="inlineStr">
         <is>
           <t>đẳng cấp, thứ hạng</t>
         </is>
       </c>
-      <c r="F3029" t="inlineStr">
-        <is>
-          <t>业主消费档次和消费要求不一样，真让我为难。</t>
-        </is>
-      </c>
-      <c r="G3029" t="inlineStr"/>
-      <c r="H3029" t="inlineStr"/>
+      <c r="F3029" s="0" t="inlineStr">
+        <is>
+          <t>这家咖啡馆虽然不大，但装修和服务都挺有档次的。</t>
+        </is>
+      </c>
+      <c r="G3029" s="0" t="inlineStr"/>
+      <c r="H3029" s="0" t="inlineStr"/>
     </row>
     <row r="3030">
-      <c r="A3030" t="inlineStr">
+      <c r="A3030" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3030" t="inlineStr">
+      <c r="B3030" s="0" t="inlineStr">
         <is>
           <t>诸位</t>
         </is>
       </c>
-      <c r="C3030" t="inlineStr">
+      <c r="C3030" s="0" t="inlineStr">
         <is>
           <t>zhūwèi</t>
         </is>
       </c>
-      <c r="D3030" t="inlineStr">
+      <c r="D3030" s="0" t="inlineStr">
         <is>
           <t>对很多人的尊称，各位</t>
         </is>
       </c>
-      <c r="E3030" t="inlineStr">
+      <c r="E3030" s="0" t="inlineStr">
         <is>
           <t>chư vị, các vị (các anh chị)</t>
         </is>
       </c>
-      <c r="F3030" t="inlineStr">
-        <is>
-          <t>以上是我对该书的一点见解，仅供诸位参考。</t>
-        </is>
-      </c>
-      <c r="G3030" t="inlineStr"/>
-      <c r="H3030" t="inlineStr"/>
+      <c r="F3030" s="0" t="inlineStr">
+        <is>
+          <t>上课第一天我常对学生说：“诸位，学中文最重要的就是坚持。”</t>
+        </is>
+      </c>
+      <c r="G3030" s="0" t="inlineStr"/>
+      <c r="H3030" s="0" t="inlineStr"/>
     </row>
     <row r="3031">
-      <c r="A3031" t="inlineStr">
+      <c r="A3031" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3031" t="inlineStr">
+      <c r="B3031" s="0" t="inlineStr">
         <is>
           <t>预先</t>
         </is>
       </c>
-      <c r="C3031" t="inlineStr">
+      <c r="C3031" s="0" t="inlineStr">
         <is>
           <t>yùxiān</t>
         </is>
       </c>
-      <c r="D3031" t="inlineStr">
+      <c r="D3031" s="0" t="inlineStr">
         <is>
           <t>在事情发生之前就先做某事</t>
         </is>
       </c>
-      <c r="E3031" t="inlineStr">
+      <c r="E3031" s="0" t="inlineStr">
         <is>
           <t>trước, từ trước</t>
         </is>
       </c>
-      <c r="F3031" t="inlineStr">
-        <is>
-          <t>洪水到来之前，我们得到了有关部门的预先通知。</t>
-        </is>
-      </c>
-      <c r="G3031" t="inlineStr"/>
-      <c r="H3031" t="inlineStr"/>
+      <c r="F3031" s="0" t="inlineStr">
+        <is>
+          <t>明天要跟中国同事开会，我得预先把要说的话准备好。</t>
+        </is>
+      </c>
+      <c r="G3031" s="0" t="inlineStr"/>
+      <c r="H3031" s="0" t="inlineStr"/>
     </row>
     <row r="3032">
-      <c r="A3032" t="inlineStr">
+      <c r="A3032" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3032" t="inlineStr">
+      <c r="B3032" s="0" t="inlineStr">
         <is>
           <t>直觉</t>
         </is>
       </c>
-      <c r="C3032" t="inlineStr">
+      <c r="C3032" s="0" t="inlineStr">
         <is>
           <t>zhíjué</t>
         </is>
       </c>
-      <c r="D3032" t="inlineStr">
+      <c r="D3032" s="0" t="inlineStr">
         <is>
           <t>不用思考就直接感觉到的判断</t>
         </is>
       </c>
-      <c r="E3032" t="inlineStr">
+      <c r="E3032" s="0" t="inlineStr">
         <is>
           <t>trực giác</t>
         </is>
       </c>
-      <c r="F3032" t="inlineStr">
-        <is>
-          <t>其实他并不确定是哪条路，但直觉告诉他，要左拐。</t>
-        </is>
-      </c>
-      <c r="G3032" t="inlineStr"/>
-      <c r="H3032" t="inlineStr"/>
+      <c r="F3032" s="0" t="inlineStr">
+        <is>
+          <t>做HSK阅读题时，有时候我会先凭直觉选一个答案，再回头检查。</t>
+        </is>
+      </c>
+      <c r="G3032" s="0" t="inlineStr"/>
+      <c r="H3032" s="0" t="inlineStr"/>
     </row>
     <row r="3033">
-      <c r="A3033" t="inlineStr">
+      <c r="A3033" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3033" t="inlineStr">
+      <c r="B3033" s="0" t="inlineStr">
         <is>
           <t>座右铭</t>
         </is>
       </c>
-      <c r="C3033" t="inlineStr">
+      <c r="C3033" s="0" t="inlineStr">
         <is>
           <t>zuòyòumíng</t>
         </is>
       </c>
-      <c r="D3033" t="inlineStr">
+      <c r="D3033" s="0" t="inlineStr">
         <is>
           <t>用来提醒、勉励自己的一句话</t>
         </is>
       </c>
-      <c r="E3033" t="inlineStr">
+      <c r="E3033" s="0" t="inlineStr">
         <is>
           <t>châm ngôn (tự nhắc mình)</t>
         </is>
       </c>
-      <c r="F3033" t="inlineStr">
-        <is>
-          <t>人人为我，我为人人，这是我们的座右铭。</t>
-        </is>
-      </c>
-      <c r="G3033" t="inlineStr"/>
-      <c r="H3033" t="inlineStr"/>
+      <c r="F3033" s="0" t="inlineStr">
+        <is>
+          <t>“坚持就是胜利”是我备考路上的座右铭。</t>
+        </is>
+      </c>
+      <c r="G3033" s="0" t="inlineStr"/>
+      <c r="H3033" s="0" t="inlineStr"/>
     </row>
     <row r="3034">
-      <c r="A3034" t="inlineStr">
+      <c r="A3034" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3034" t="inlineStr">
+      <c r="B3034" s="0" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="C3034" t="inlineStr">
+      <c r="C3034" s="0" t="inlineStr">
         <is>
           <t>tōngyòng</t>
         </is>
       </c>
-      <c r="D3034" t="inlineStr">
+      <c r="D3034" s="0" t="inlineStr">
         <is>
           <t>大家都可以用，普遍使用</t>
         </is>
       </c>
-      <c r="E3034" t="inlineStr">
+      <c r="E3034" s="0" t="inlineStr">
         <is>
           <t>dùng chung, thông dụng</t>
         </is>
       </c>
-      <c r="F3034" t="inlineStr">
-        <is>
-          <t>微笑是一种国际通用的语言。</t>
-        </is>
-      </c>
-      <c r="G3034" t="inlineStr"/>
-      <c r="H3034" t="inlineStr"/>
+      <c r="F3034" s="0" t="inlineStr">
+        <is>
+          <t>微笑和礼貌几乎在哪个国家都是通用的。</t>
+        </is>
+      </c>
+      <c r="G3034" s="0" t="inlineStr"/>
+      <c r="H3034" s="0" t="inlineStr"/>
     </row>
     <row r="3035">
-      <c r="A3035" t="inlineStr">
+      <c r="A3035" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3035" t="inlineStr">
+      <c r="B3035" s="0" t="inlineStr">
         <is>
           <t>调节</t>
         </is>
       </c>
-      <c r="C3035" t="inlineStr">
+      <c r="C3035" s="0" t="inlineStr">
         <is>
           <t>tiáojié</t>
         </is>
       </c>
-      <c r="D3035" t="inlineStr">
+      <c r="D3035" s="0" t="inlineStr">
         <is>
           <t>调整，使更合适、更协调</t>
         </is>
       </c>
-      <c r="E3035" t="inlineStr">
+      <c r="E3035" s="0" t="inlineStr">
         <is>
           <t>điều tiết, điều hòa</t>
         </is>
       </c>
-      <c r="F3035" t="inlineStr">
-        <is>
-          <t>老师为我调节了与同学之间的矛盾。</t>
-        </is>
-      </c>
-      <c r="G3035" t="inlineStr"/>
-      <c r="H3035" t="inlineStr"/>
+      <c r="F3035" s="0" t="inlineStr">
+        <is>
+          <t>工作压力大的时候，我会用跑步来调节自己的情绪。</t>
+        </is>
+      </c>
+      <c r="G3035" s="0" t="inlineStr"/>
+      <c r="H3035" s="0" t="inlineStr"/>
     </row>
     <row r="3036">
-      <c r="A3036" t="inlineStr">
+      <c r="A3036" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3036" t="inlineStr">
+      <c r="B3036" s="0" t="inlineStr">
         <is>
           <t>循环</t>
         </is>
       </c>
-      <c r="C3036" t="inlineStr">
+      <c r="C3036" s="0" t="inlineStr">
         <is>
           <t>xúnhuán</t>
         </is>
       </c>
-      <c r="D3036" t="inlineStr">
+      <c r="D3036" s="0" t="inlineStr">
         <is>
           <t>按顺序重复地运行一圈又一圈</t>
         </is>
       </c>
-      <c r="E3036" t="inlineStr">
+      <c r="E3036" s="0" t="inlineStr">
         <is>
           <t>tuần hoàn</t>
         </is>
       </c>
-      <c r="F3036" t="inlineStr">
-        <is>
-          <t>由于药物的作用，血液循环加快了。</t>
-        </is>
-      </c>
-      <c r="G3036" t="inlineStr"/>
-      <c r="H3036" t="inlineStr"/>
+      <c r="F3036" s="0" t="inlineStr">
+        <is>
+          <t>早睡早起形成良性循环，我白天学习的效率就高多了。</t>
+        </is>
+      </c>
+      <c r="G3036" s="0" t="inlineStr"/>
+      <c r="H3036" s="0" t="inlineStr"/>
     </row>
     <row r="3037">
-      <c r="A3037" t="inlineStr">
+      <c r="A3037" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3037" t="inlineStr">
+      <c r="B3037" s="0" t="inlineStr">
         <is>
           <t>收缩</t>
         </is>
       </c>
-      <c r="C3037" t="inlineStr">
+      <c r="C3037" s="0" t="inlineStr">
         <is>
           <t>shōusuō</t>
         </is>
       </c>
-      <c r="D3037" t="inlineStr">
+      <c r="D3037" s="0" t="inlineStr">
         <is>
           <t>由大变小、往里缩</t>
         </is>
       </c>
-      <c r="E3037" t="inlineStr">
+      <c r="E3037" s="0" t="inlineStr">
         <is>
           <t>co lại, thu nhỏ</t>
         </is>
       </c>
-      <c r="F3037" t="inlineStr">
-        <is>
-          <t>含羞草一受刺激，叶子就收缩起来。</t>
-        </is>
-      </c>
-      <c r="G3037" t="inlineStr"/>
-      <c r="H3037" t="inlineStr"/>
+      <c r="F3037" s="0" t="inlineStr">
+        <is>
+          <t>运动完一定要拉伸，不然肌肉一直收缩，第二天会很酸。</t>
+        </is>
+      </c>
+      <c r="G3037" s="0" t="inlineStr"/>
+      <c r="H3037" s="0" t="inlineStr"/>
     </row>
     <row r="3038">
-      <c r="A3038" t="inlineStr">
+      <c r="A3038" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3038" t="inlineStr">
+      <c r="B3038" s="0" t="inlineStr">
         <is>
           <t>氧气</t>
         </is>
       </c>
-      <c r="C3038" t="inlineStr">
+      <c r="C3038" s="0" t="inlineStr">
         <is>
           <t>yǎngqì</t>
         </is>
       </c>
-      <c r="D3038" t="inlineStr">
+      <c r="D3038" s="0" t="inlineStr">
         <is>
           <t>空气里让人呼吸、能助燃的气体</t>
         </is>
       </c>
-      <c r="E3038" t="inlineStr">
+      <c r="E3038" s="0" t="inlineStr">
         <is>
           <t>khí oxy</t>
         </is>
       </c>
-      <c r="F3038" t="inlineStr">
-        <is>
-          <t>因为有氧气，所以地球上才有生命。</t>
-        </is>
-      </c>
-      <c r="G3038" t="inlineStr"/>
-      <c r="H3038" t="inlineStr"/>
+      <c r="F3038" s="0" t="inlineStr">
+        <is>
+          <t>房间闷的时候我会开窗，让新鲜氧气进来，脑子也清醒些。</t>
+        </is>
+      </c>
+      <c r="G3038" s="0" t="inlineStr"/>
+      <c r="H3038" s="0" t="inlineStr"/>
     </row>
     <row r="3039">
-      <c r="A3039" t="inlineStr">
+      <c r="A3039" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3039" t="inlineStr">
+      <c r="B3039" s="0" t="inlineStr">
         <is>
           <t>斟酌</t>
         </is>
       </c>
-      <c r="C3039" t="inlineStr">
+      <c r="C3039" s="0" t="inlineStr">
         <is>
           <t>zhēnzhuó</t>
         </is>
       </c>
-      <c r="D3039" t="inlineStr">
+      <c r="D3039" s="0" t="inlineStr">
         <is>
           <t>反复考虑，仔细掂量该怎么做</t>
         </is>
       </c>
-      <c r="E3039" t="inlineStr">
+      <c r="E3039" s="0" t="inlineStr">
         <is>
           <t>cân nhắc, đắn đo</t>
         </is>
       </c>
-      <c r="F3039" t="inlineStr">
-        <is>
-          <t>事情比较复杂，怎么处理，还得斟酌一下。</t>
-        </is>
-      </c>
-      <c r="G3039" t="inlineStr"/>
-      <c r="H3039" t="inlineStr"/>
+      <c r="F3039" s="0" t="inlineStr">
+        <is>
+          <t>给学生写评语时，我会反复斟酌用词，怕伤到他们的自信。</t>
+        </is>
+      </c>
+      <c r="G3039" s="0" t="inlineStr"/>
+      <c r="H3039" s="0" t="inlineStr"/>
     </row>
     <row r="3040">
-      <c r="A3040" t="inlineStr">
+      <c r="A3040" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3040" t="inlineStr">
+      <c r="B3040" s="0" t="inlineStr">
         <is>
           <t>虚伪</t>
         </is>
       </c>
-      <c r="C3040" t="inlineStr">
+      <c r="C3040" s="0" t="inlineStr">
         <is>
           <t>xūwěi</t>
         </is>
       </c>
-      <c r="D3040" t="inlineStr">
+      <c r="D3040" s="0" t="inlineStr">
         <is>
           <t>不真实，假装的，表里不一</t>
         </is>
       </c>
-      <c r="E3040" t="inlineStr">
+      <c r="E3040" s="0" t="inlineStr">
         <is>
           <t>giả dối, đạo đức giả</t>
         </is>
       </c>
-      <c r="F3040" t="inlineStr">
-        <is>
-          <t>法官揭露了这个坏蛋虚伪的面目。</t>
-        </is>
-      </c>
-      <c r="G3040" t="inlineStr"/>
-      <c r="H3040" t="inlineStr"/>
+      <c r="F3040" s="0" t="inlineStr">
+        <is>
+          <t>我不太会应付那种表面客气、其实很虚伪的人。</t>
+        </is>
+      </c>
+      <c r="G3040" s="0" t="inlineStr"/>
+      <c r="H3040" s="0" t="inlineStr"/>
     </row>
     <row r="3041">
-      <c r="A3041" t="inlineStr">
+      <c r="A3041" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3041" t="inlineStr">
+      <c r="B3041" s="0" t="inlineStr">
         <is>
           <t>违背</t>
         </is>
       </c>
-      <c r="C3041" t="inlineStr">
+      <c r="C3041" s="0" t="inlineStr">
         <is>
           <t>wéibèi</t>
         </is>
       </c>
-      <c r="D3041" t="inlineStr">
+      <c r="D3041" s="0" t="inlineStr">
         <is>
           <t>不遵守，跟…相反</t>
         </is>
       </c>
-      <c r="E3041" t="inlineStr">
+      <c r="E3041" s="0" t="inlineStr">
         <is>
           <t>làm trái, đi ngược lại</t>
         </is>
       </c>
-      <c r="F3041" t="inlineStr">
-        <is>
-          <t>哥哥违背了爸爸的意愿当了一名医生。</t>
-        </is>
-      </c>
-      <c r="G3041" t="inlineStr"/>
-      <c r="H3041" t="inlineStr"/>
+      <c r="F3041" s="0" t="inlineStr">
+        <is>
+          <t>为了赶进度而违背学习规律，结果反而记不牢。</t>
+        </is>
+      </c>
+      <c r="G3041" s="0" t="inlineStr"/>
+      <c r="H3041" s="0" t="inlineStr"/>
     </row>
     <row r="3042">
-      <c r="A3042" t="inlineStr">
+      <c r="A3042" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3042" t="inlineStr">
+      <c r="B3042" s="0" t="inlineStr">
         <is>
           <t>回避</t>
         </is>
       </c>
-      <c r="C3042" t="inlineStr">
+      <c r="C3042" s="0" t="inlineStr">
         <is>
           <t>huíbì</t>
         </is>
       </c>
-      <c r="D3042" t="inlineStr">
+      <c r="D3042" s="0" t="inlineStr">
         <is>
           <t>有意躲开，不正面面对</t>
         </is>
       </c>
-      <c r="E3042" t="inlineStr">
+      <c r="E3042" s="0" t="inlineStr">
         <is>
           <t>né tránh</t>
         </is>
       </c>
-      <c r="F3042" t="inlineStr">
-        <is>
-          <t>不知为什么，他总是回避这个问题。</t>
-        </is>
-      </c>
-      <c r="G3042" t="inlineStr"/>
-      <c r="H3042" t="inlineStr"/>
+      <c r="F3042" s="0" t="inlineStr">
+        <is>
+          <t>遇到不会的语法，我不想回避，而是当场就查清楚。</t>
+        </is>
+      </c>
+      <c r="G3042" s="0" t="inlineStr"/>
+      <c r="H3042" s="0" t="inlineStr"/>
     </row>
     <row r="3043">
-      <c r="A3043" t="inlineStr">
+      <c r="A3043" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3043" t="inlineStr">
+      <c r="B3043" s="0" t="inlineStr">
         <is>
           <t>岔</t>
         </is>
       </c>
-      <c r="C3043" t="inlineStr">
+      <c r="C3043" s="0" t="inlineStr">
         <is>
           <t>chà</t>
         </is>
       </c>
-      <c r="D3043" t="inlineStr">
+      <c r="D3043" s="0" t="inlineStr">
         <is>
           <t>把话题引到别的方向</t>
         </is>
       </c>
-      <c r="E3043" t="inlineStr">
+      <c r="E3043" s="0" t="inlineStr">
         <is>
           <t>lái (chủ đề) sang chỗ khác</t>
         </is>
       </c>
-      <c r="F3043" t="inlineStr">
-        <is>
-          <t>他设法把讨论内容从钱的话题上岔开了。</t>
-        </is>
-      </c>
-      <c r="G3043" t="inlineStr"/>
-      <c r="H3043" t="inlineStr"/>
+      <c r="F3043" s="0" t="inlineStr">
+        <is>
+          <t>每次别人问我工资多少，我都赶紧把话题岔开。</t>
+        </is>
+      </c>
+      <c r="G3043" s="0" t="inlineStr"/>
+      <c r="H3043" s="0" t="inlineStr"/>
     </row>
     <row r="3044">
-      <c r="A3044" t="inlineStr">
+      <c r="A3044" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3044" t="inlineStr">
+      <c r="B3044" s="0" t="inlineStr">
         <is>
           <t>装聋装哑</t>
         </is>
       </c>
-      <c r="C3044" t="inlineStr">
+      <c r="C3044" s="0" t="inlineStr">
         <is>
           <t>zhuānglóngzhuāngyǎ</t>
         </is>
       </c>
-      <c r="D3044" t="inlineStr">
+      <c r="D3044" s="0" t="inlineStr">
         <is>
           <t>假装听不见、说不出，故意不理</t>
         </is>
       </c>
-      <c r="E3044" t="inlineStr">
+      <c r="E3044" s="0" t="inlineStr">
         <is>
           <t>giả câm giả điếc</t>
         </is>
       </c>
-      <c r="F3044" t="inlineStr">
-        <is>
-          <t>有些人一谈到钱的问题就装聋装哑。</t>
-        </is>
-      </c>
-      <c r="G3044" t="inlineStr"/>
-      <c r="H3044" t="inlineStr"/>
+      <c r="F3044" s="0" t="inlineStr">
+        <is>
+          <t>同事之间闹矛盾的时候，我一般装聋装哑，不想卷进去。</t>
+        </is>
+      </c>
+      <c r="G3044" s="0" t="inlineStr"/>
+      <c r="H3044" s="0" t="inlineStr"/>
     </row>
     <row r="3045">
-      <c r="A3045" t="inlineStr">
+      <c r="A3045" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3045" t="inlineStr">
+      <c r="B3045" s="0" t="inlineStr">
         <is>
           <t>画蛇添足</t>
         </is>
       </c>
-      <c r="C3045" t="inlineStr">
+      <c r="C3045" s="0" t="inlineStr">
         <is>
           <t>huàshétiānzú</t>
         </is>
       </c>
-      <c r="D3045" t="inlineStr">
+      <c r="D3045" s="0" t="inlineStr">
         <is>
           <t>做多余的事，反而把事情弄坏</t>
         </is>
       </c>
-      <c r="E3045" t="inlineStr">
+      <c r="E3045" s="0" t="inlineStr">
         <is>
           <t>vẽ rắn thêm chân (làm thừa hỏng việc)</t>
         </is>
       </c>
-      <c r="F3045" t="inlineStr">
-        <is>
-          <t>这幅画已经很完美了，你就不要再画蛇添足了。</t>
-        </is>
-      </c>
-      <c r="G3045" t="inlineStr"/>
-      <c r="H3045" t="inlineStr"/>
+      <c r="F3045" s="0" t="inlineStr">
+        <is>
+          <t>这篇作文本来写得挺好，你再加那句反而画蛇添足了。</t>
+        </is>
+      </c>
+      <c r="G3045" s="0" t="inlineStr"/>
+      <c r="H3045" s="0" t="inlineStr"/>
     </row>
     <row r="3046">
-      <c r="A3046" t="inlineStr">
+      <c r="A3046" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3046" t="inlineStr">
+      <c r="B3046" s="0" t="inlineStr">
         <is>
           <t>机灵</t>
         </is>
       </c>
-      <c r="C3046" t="inlineStr">
+      <c r="C3046" s="0" t="inlineStr">
         <is>
           <t>jīling</t>
         </is>
       </c>
-      <c r="D3046" t="inlineStr">
+      <c r="D3046" s="0" t="inlineStr">
         <is>
           <t>聪明，反应很快</t>
         </is>
       </c>
-      <c r="E3046" t="inlineStr">
+      <c r="E3046" s="0" t="inlineStr">
         <is>
           <t>nhanh trí, lanh lợi</t>
         </is>
       </c>
-      <c r="F3046" t="inlineStr">
-        <is>
-          <t>小松鼠很机灵，听到一点动静就爬到树上去了。</t>
-        </is>
-      </c>
-      <c r="G3046" t="inlineStr"/>
-      <c r="H3046" t="inlineStr"/>
+      <c r="F3046" s="0" t="inlineStr">
+        <is>
+          <t>我班上有个学生特别机灵，一点就通。</t>
+        </is>
+      </c>
+      <c r="G3046" s="0" t="inlineStr"/>
+      <c r="H3046" s="0" t="inlineStr"/>
     </row>
     <row r="3047">
-      <c r="A3047" t="inlineStr">
+      <c r="A3047" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3047" t="inlineStr">
+      <c r="B3047" s="0" t="inlineStr">
         <is>
           <t>肆无忌惮</t>
         </is>
       </c>
-      <c r="C3047" t="inlineStr">
+      <c r="C3047" s="0" t="inlineStr">
         <is>
           <t>sìwújìdàn</t>
         </is>
       </c>
-      <c r="D3047" t="inlineStr">
+      <c r="D3047" s="0" t="inlineStr">
         <is>
           <t>一点也不怕、不顾忌，任意妄为</t>
         </is>
       </c>
-      <c r="E3047" t="inlineStr">
+      <c r="E3047" s="0" t="inlineStr">
         <is>
           <t>ngang nhiên, không kiêng nể gì</t>
         </is>
       </c>
-      <c r="F3047" t="inlineStr">
-        <is>
-          <t>对待坏人，我们越宽容，他们就越肆无忌惮。</t>
-        </is>
-      </c>
-      <c r="G3047" t="inlineStr"/>
-      <c r="H3047" t="inlineStr"/>
+      <c r="F3047" s="0" t="inlineStr">
+        <is>
+          <t>楼上的孩子晚上还肆无忌惮地跑来跑去，吵得我没法背书。</t>
+        </is>
+      </c>
+      <c r="G3047" s="0" t="inlineStr"/>
+      <c r="H3047" s="0" t="inlineStr"/>
     </row>
     <row r="3048">
-      <c r="A3048" t="inlineStr">
+      <c r="A3048" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3048" t="inlineStr">
+      <c r="B3048" s="0" t="inlineStr">
         <is>
           <t>损坏</t>
         </is>
       </c>
-      <c r="C3048" t="inlineStr">
+      <c r="C3048" s="0" t="inlineStr">
         <is>
           <t>sǔnhuài</t>
         </is>
       </c>
-      <c r="D3048" t="inlineStr">
+      <c r="D3048" s="0" t="inlineStr">
         <is>
           <t>使东西受到破坏、变坏</t>
         </is>
       </c>
-      <c r="E3048" t="inlineStr">
+      <c r="E3048" s="0" t="inlineStr">
         <is>
           <t>làm hỏng, hư hại</t>
         </is>
       </c>
-      <c r="F3048" t="inlineStr">
-        <is>
-          <t>机器需要经常维护，这样就不容易损坏。</t>
-        </is>
-      </c>
-      <c r="G3048" t="inlineStr"/>
-      <c r="H3048" t="inlineStr"/>
+      <c r="F3048" s="0" t="inlineStr">
+        <is>
+          <t>电脑突然损坏，我存的备考资料差点全丢了。</t>
+        </is>
+      </c>
+      <c r="G3048" s="0" t="inlineStr"/>
+      <c r="H3048" s="0" t="inlineStr"/>
     </row>
     <row r="3049">
-      <c r="A3049" t="inlineStr">
+      <c r="A3049" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3049" t="inlineStr">
+      <c r="B3049" s="0" t="inlineStr">
         <is>
           <t>倾向</t>
         </is>
       </c>
-      <c r="C3049" t="inlineStr">
+      <c r="C3049" s="0" t="inlineStr">
         <is>
           <t>qīngxiàng</t>
         </is>
       </c>
-      <c r="D3049" t="inlineStr">
+      <c r="D3049" s="0" t="inlineStr">
         <is>
           <t>更喜欢、更赞成某一方</t>
         </is>
       </c>
-      <c r="E3049" t="inlineStr">
+      <c r="E3049" s="0" t="inlineStr">
         <is>
           <t>nghiêng về, xu hướng</t>
         </is>
       </c>
-      <c r="F3049" t="inlineStr">
-        <is>
-          <t>虽然你们都不同意，但我更倾向于作者原意。</t>
-        </is>
-      </c>
-      <c r="G3049" t="inlineStr"/>
-      <c r="H3049" t="inlineStr"/>
+      <c r="F3049" s="0" t="inlineStr">
+        <is>
+          <t>选教材时，我更倾向于例句实用、贴近生活的那一套。</t>
+        </is>
+      </c>
+      <c r="G3049" s="0" t="inlineStr"/>
+      <c r="H3049" s="0" t="inlineStr"/>
     </row>
     <row r="3050">
-      <c r="A3050" t="inlineStr">
+      <c r="A3050" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3050" t="inlineStr">
+      <c r="B3050" s="0" t="inlineStr">
         <is>
           <t>试验</t>
         </is>
       </c>
-      <c r="C3050" t="inlineStr">
+      <c r="C3050" s="0" t="inlineStr">
         <is>
           <t>shìyàn</t>
         </is>
       </c>
-      <c r="D3050" t="inlineStr">
+      <c r="D3050" s="0" t="inlineStr">
         <is>
           <t>为了了解结果而进行的尝试</t>
         </is>
       </c>
-      <c r="E3050" t="inlineStr">
+      <c r="E3050" s="0" t="inlineStr">
         <is>
           <t>thử nghiệm</t>
         </is>
       </c>
-      <c r="F3050" t="inlineStr">
-        <is>
-          <t>那次试验因为准备不足，终于宣告失败。</t>
-        </is>
-      </c>
-      <c r="G3050" t="inlineStr"/>
-      <c r="H3050" t="inlineStr"/>
+      <c r="F3050" s="0" t="inlineStr">
+        <is>
+          <t>我打算试验一种新的背单词方法，看看效果怎么样。</t>
+        </is>
+      </c>
+      <c r="G3050" s="0" t="inlineStr"/>
+      <c r="H3050" s="0" t="inlineStr"/>
     </row>
     <row r="3051">
-      <c r="A3051" t="inlineStr">
+      <c r="A3051" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3051" t="inlineStr">
+      <c r="B3051" s="0" t="inlineStr">
         <is>
           <t>脂肪</t>
         </is>
       </c>
-      <c r="C3051" t="inlineStr">
+      <c r="C3051" s="0" t="inlineStr">
         <is>
           <t>zhīfáng</t>
         </is>
       </c>
-      <c r="D3051" t="inlineStr">
+      <c r="D3051" s="0" t="inlineStr">
         <is>
           <t>动物或人体内的油，肥肉部分</t>
         </is>
       </c>
-      <c r="E3051" t="inlineStr">
+      <c r="E3051" s="0" t="inlineStr">
         <is>
           <t>mỡ, chất béo</t>
         </is>
       </c>
-      <c r="F3051" t="inlineStr">
-        <is>
-          <t>冬天到了，别减肥了，留点儿脂肪抗寒。</t>
-        </is>
-      </c>
-      <c r="G3051" t="inlineStr"/>
-      <c r="H3051" t="inlineStr"/>
+      <c r="F3051" s="0" t="inlineStr">
+        <is>
+          <t>医生说我得多运动，少囤点脂肪。</t>
+        </is>
+      </c>
+      <c r="G3051" s="0" t="inlineStr"/>
+      <c r="H3051" s="0" t="inlineStr"/>
     </row>
     <row r="3052">
-      <c r="A3052" t="inlineStr">
+      <c r="A3052" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3052" t="inlineStr">
+      <c r="B3052" s="0" t="inlineStr">
         <is>
           <t>动脉</t>
         </is>
       </c>
-      <c r="C3052" t="inlineStr">
+      <c r="C3052" s="0" t="inlineStr">
         <is>
           <t>dòngmài</t>
         </is>
       </c>
-      <c r="D3052" t="inlineStr">
+      <c r="D3052" s="0" t="inlineStr">
         <is>
           <t>把血从心脏送到全身的血管</t>
         </is>
       </c>
-      <c r="E3052" t="inlineStr">
+      <c r="E3052" s="0" t="inlineStr">
         <is>
           <t>động mạch</t>
         </is>
       </c>
-      <c r="F3052" t="inlineStr">
-        <is>
-          <t>他激动得脖子旁边的大动脉都看得见跳动。</t>
-        </is>
-      </c>
-      <c r="G3052" t="inlineStr"/>
-      <c r="H3052" t="inlineStr"/>
+      <c r="F3052" s="0" t="inlineStr">
+        <is>
+          <t>我常跟学生说，语法就像句子的动脉，决定整句话通不通。</t>
+        </is>
+      </c>
+      <c r="G3052" s="0" t="inlineStr"/>
+      <c r="H3052" s="0" t="inlineStr"/>
     </row>
     <row r="3053">
-      <c r="A3053" t="inlineStr">
+      <c r="A3053" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3053" t="inlineStr">
+      <c r="B3053" s="0" t="inlineStr">
         <is>
           <t>实质</t>
         </is>
       </c>
-      <c r="C3053" t="inlineStr">
+      <c r="C3053" s="0" t="inlineStr">
         <is>
           <t>shízhì</t>
         </is>
       </c>
-      <c r="D3053" t="inlineStr">
+      <c r="D3053" s="0" t="inlineStr">
         <is>
           <t>事物真正的、本质的内容</t>
         </is>
       </c>
-      <c r="E3053" t="inlineStr">
+      <c r="E3053" s="0" t="inlineStr">
         <is>
           <t>thực chất, bản chất</t>
         </is>
       </c>
-      <c r="F3053" t="inlineStr">
-        <is>
-          <t>大家要认真领会文件的精神实质。</t>
-        </is>
-      </c>
-      <c r="G3053" t="inlineStr"/>
-      <c r="H3053" t="inlineStr"/>
+      <c r="F3053" s="0" t="inlineStr">
+        <is>
+          <t>学语言的实质不是背了多少词，而是能不能真正用出来。</t>
+        </is>
+      </c>
+      <c r="G3053" s="0" t="inlineStr"/>
+      <c r="H3053" s="0" t="inlineStr"/>
     </row>
     <row r="3054">
-      <c r="A3054" t="inlineStr">
+      <c r="A3054" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3054" t="inlineStr">
+      <c r="B3054" s="0" t="inlineStr">
         <is>
           <t>周密</t>
         </is>
       </c>
-      <c r="C3054" t="inlineStr">
+      <c r="C3054" s="0" t="inlineStr">
         <is>
           <t>zhōumì</t>
         </is>
       </c>
-      <c r="D3054" t="inlineStr">
+      <c r="D3054" s="0" t="inlineStr">
         <is>
           <t>考虑得很全面很细致，没有漏洞</t>
         </is>
       </c>
-      <c r="E3054" t="inlineStr">
+      <c r="E3054" s="0" t="inlineStr">
         <is>
           <t>chu đáo, kỹ lưỡng</t>
         </is>
       </c>
-      <c r="F3054" t="inlineStr">
-        <is>
-          <t>公安人员对这个案件做了周密的调查。</t>
-        </is>
-      </c>
-      <c r="G3054" t="inlineStr"/>
-      <c r="H3054" t="inlineStr"/>
+      <c r="F3054" s="0" t="inlineStr">
+        <is>
+          <t>考前我做了一个很周密的复习计划，每天学什么都排好了。</t>
+        </is>
+      </c>
+      <c r="G3054" s="0" t="inlineStr"/>
+      <c r="H3054" s="0" t="inlineStr"/>
     </row>
     <row r="3055">
-      <c r="A3055" t="inlineStr">
+      <c r="A3055" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3055" t="inlineStr">
+      <c r="B3055" s="0" t="inlineStr">
         <is>
           <t>途径</t>
         </is>
       </c>
-      <c r="C3055" t="inlineStr">
+      <c r="C3055" s="0" t="inlineStr">
         <is>
           <t>tújìng</t>
         </is>
       </c>
-      <c r="D3055" t="inlineStr">
+      <c r="D3055" s="0" t="inlineStr">
         <is>
           <t>达到目的的方法、门路</t>
         </is>
       </c>
-      <c r="E3055" t="inlineStr">
+      <c r="E3055" s="0" t="inlineStr">
         <is>
           <t>con đường, phương thức</t>
         </is>
       </c>
-      <c r="F3055" t="inlineStr">
-        <is>
-          <t>教育是提高国民素质的根本途径。</t>
-        </is>
-      </c>
-      <c r="G3055" t="inlineStr"/>
-      <c r="H3055" t="inlineStr"/>
+      <c r="F3055" s="0" t="inlineStr">
+        <is>
+          <t>多跟中国同事聊天，是我提高口语最有效的途径。</t>
+        </is>
+      </c>
+      <c r="G3055" s="0" t="inlineStr"/>
+      <c r="H3055" s="0" t="inlineStr"/>
     </row>
     <row r="3056">
-      <c r="A3056" t="inlineStr">
+      <c r="A3056" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3056" t="inlineStr">
+      <c r="B3056" s="0" t="inlineStr">
         <is>
           <t>虚假</t>
         </is>
       </c>
-      <c r="C3056" t="inlineStr">
+      <c r="C3056" s="0" t="inlineStr">
         <is>
           <t>xūjiǎ</t>
         </is>
       </c>
-      <c r="D3056" t="inlineStr">
+      <c r="D3056" s="0" t="inlineStr">
         <is>
           <t>不真实，假的</t>
         </is>
       </c>
-      <c r="E3056" t="inlineStr">
+      <c r="E3056" s="0" t="inlineStr">
         <is>
           <t>giả, không thật</t>
         </is>
       </c>
-      <c r="F3056" t="inlineStr">
-        <is>
-          <t>新闻报道必须真实，不许有半点虚假。</t>
-        </is>
-      </c>
-      <c r="G3056" t="inlineStr"/>
-      <c r="H3056" t="inlineStr"/>
+      <c r="F3056" s="0" t="inlineStr">
+        <is>
+          <t>网上很多“三个月过HSK6”的广告都很虚假。</t>
+        </is>
+      </c>
+      <c r="G3056" s="0" t="inlineStr"/>
+      <c r="H3056" s="0" t="inlineStr"/>
     </row>
     <row r="3057">
-      <c r="A3057" t="inlineStr">
+      <c r="A3057" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3057" t="inlineStr">
+      <c r="B3057" s="0" t="inlineStr">
         <is>
           <t>意向</t>
         </is>
       </c>
-      <c r="C3057" t="inlineStr">
+      <c r="C3057" s="0" t="inlineStr">
         <is>
           <t>yìxiàng</t>
         </is>
       </c>
-      <c r="D3057" t="inlineStr">
+      <c r="D3057" s="0" t="inlineStr">
         <is>
           <t>心里打算做某事的想法</t>
         </is>
       </c>
-      <c r="E3057" t="inlineStr">
+      <c r="E3057" s="0" t="inlineStr">
         <is>
           <t>ý định, ý hướng</t>
         </is>
       </c>
-      <c r="F3057" t="inlineStr">
-        <is>
-          <t>有多家企业表达了参与收购的意向。</t>
-        </is>
-      </c>
-      <c r="G3057" t="inlineStr"/>
-      <c r="H3057" t="inlineStr"/>
+      <c r="F3057" s="0" t="inlineStr">
+        <is>
+          <t>我跟中心表达了想多带几节口语课的意向。</t>
+        </is>
+      </c>
+      <c r="G3057" s="0" t="inlineStr"/>
+      <c r="H3057" s="0" t="inlineStr"/>
     </row>
     <row r="3058">
-      <c r="A3058" t="inlineStr">
+      <c r="A3058" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3058" t="inlineStr">
+      <c r="B3058" s="0" t="inlineStr">
         <is>
           <t>一丝不苟</t>
         </is>
       </c>
-      <c r="C3058" t="inlineStr">
+      <c r="C3058" s="0" t="inlineStr">
         <is>
           <t>yìsībùgǒu</t>
         </is>
       </c>
-      <c r="D3058" t="inlineStr">
+      <c r="D3058" s="0" t="inlineStr">
         <is>
           <t>做事非常认真，一点也不马虎</t>
         </is>
       </c>
-      <c r="E3058" t="inlineStr">
+      <c r="E3058" s="0" t="inlineStr">
         <is>
           <t>tỉ mỉ, không cẩu thả chút nào</t>
         </is>
       </c>
-      <c r="F3058" t="inlineStr">
-        <is>
-          <t>张老师对待教学工作一向严肃认真，一丝不苟。</t>
-        </is>
-      </c>
-      <c r="G3058" t="inlineStr"/>
-      <c r="H3058" t="inlineStr"/>
+      <c r="F3058" s="0" t="inlineStr">
+        <is>
+          <t>批改学生作业时，我总是一丝不苟，连一个标点都不放过。</t>
+        </is>
+      </c>
+      <c r="G3058" s="0" t="inlineStr"/>
+      <c r="H3058" s="0" t="inlineStr"/>
     </row>
     <row r="3059">
-      <c r="A3059" t="inlineStr">
+      <c r="A3059" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3059" t="inlineStr">
+      <c r="B3059" s="0" t="inlineStr">
         <is>
           <t>收益</t>
         </is>
       </c>
-      <c r="C3059" t="inlineStr">
+      <c r="C3059" s="0" t="inlineStr">
         <is>
           <t>shōuyì</t>
         </is>
       </c>
-      <c r="D3059" t="inlineStr">
+      <c r="D3059" s="0" t="inlineStr">
         <is>
           <t>得到的好处或利润</t>
         </is>
       </c>
-      <c r="E3059" t="inlineStr">
+      <c r="E3059" s="0" t="inlineStr">
         <is>
           <t>lợi ích/lợi nhuận thu về</t>
         </is>
       </c>
-      <c r="F3059" t="inlineStr">
-        <is>
-          <t>理财产品的收益越大，风险就越高。</t>
-        </is>
-      </c>
-      <c r="G3059" t="inlineStr"/>
-      <c r="H3059" t="inlineStr"/>
+      <c r="F3059" s="0" t="inlineStr">
+        <is>
+          <t>每天坚持学两小时，时间一长，收益特别明显。</t>
+        </is>
+      </c>
+      <c r="G3059" s="0" t="inlineStr"/>
+      <c r="H3059" s="0" t="inlineStr"/>
     </row>
     <row r="3060">
-      <c r="A3060" t="inlineStr">
+      <c r="A3060" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3060" t="inlineStr">
+      <c r="B3060" s="0" t="inlineStr">
         <is>
           <t>恰当</t>
         </is>
       </c>
-      <c r="C3060" t="inlineStr">
+      <c r="C3060" s="0" t="inlineStr">
         <is>
           <t>qiàdàng</t>
         </is>
       </c>
-      <c r="D3060" t="inlineStr">
+      <c r="D3060" s="0" t="inlineStr">
         <is>
           <t>正合适，不多不少</t>
         </is>
       </c>
-      <c r="E3060" t="inlineStr">
+      <c r="E3060" s="0" t="inlineStr">
         <is>
           <t>thích đáng, thỏa đáng</t>
         </is>
       </c>
-      <c r="F3060" t="inlineStr">
-        <is>
-          <t>恰当地使用形容词，可以使文章更加生动。</t>
-        </is>
-      </c>
-      <c r="G3060" t="inlineStr"/>
-      <c r="H3060" t="inlineStr"/>
+      <c r="F3060" s="0" t="inlineStr">
+        <is>
+          <t>用词是否恰当，往往决定一篇HSK作文的分数。</t>
+        </is>
+      </c>
+      <c r="G3060" s="0" t="inlineStr"/>
+      <c r="H3060" s="0" t="inlineStr"/>
     </row>
     <row r="3061">
-      <c r="A3061" t="inlineStr">
+      <c r="A3061" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3061" t="inlineStr">
+      <c r="B3061" s="0" t="inlineStr">
         <is>
           <t>特定</t>
         </is>
       </c>
-      <c r="C3061" t="inlineStr">
+      <c r="C3061" s="0" t="inlineStr">
         <is>
           <t>tèdìng</t>
         </is>
       </c>
-      <c r="D3061" t="inlineStr">
+      <c r="D3061" s="0" t="inlineStr">
         <is>
           <t>特别指定的，某一个固定的</t>
         </is>
       </c>
-      <c r="E3061" t="inlineStr">
+      <c r="E3061" s="0" t="inlineStr">
         <is>
           <t>đặc định, nhất định</t>
         </is>
       </c>
-      <c r="F3061" t="inlineStr">
-        <is>
-          <t>在那特定的生活环境里养成了她孤僻的性格。</t>
-        </is>
-      </c>
-      <c r="G3061" t="inlineStr"/>
-      <c r="H3061" t="inlineStr"/>
+      <c r="F3061" s="0" t="inlineStr">
+        <is>
+          <t>有些词只在特定场合才用，用错了会显得很奇怪。</t>
+        </is>
+      </c>
+      <c r="G3061" s="0" t="inlineStr"/>
+      <c r="H3061" s="0" t="inlineStr"/>
     </row>
     <row r="3062">
-      <c r="A3062" t="inlineStr">
+      <c r="A3062" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3062" t="inlineStr">
+      <c r="B3062" s="0" t="inlineStr">
         <is>
           <t>缘故</t>
         </is>
       </c>
-      <c r="C3062" t="inlineStr">
+      <c r="C3062" s="0" t="inlineStr">
         <is>
           <t>yuángù</t>
         </is>
       </c>
-      <c r="D3062" t="inlineStr">
+      <c r="D3062" s="0" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
       </c>
-      <c r="E3062" t="inlineStr">
+      <c r="E3062" s="0" t="inlineStr">
         <is>
           <t>nguyên cớ, lý do</t>
         </is>
       </c>
-      <c r="F3062" t="inlineStr">
-        <is>
-          <t>由于雷雨的缘故，飞机起飞的时间再次变更了。</t>
-        </is>
-      </c>
-      <c r="G3062" t="inlineStr"/>
-      <c r="H3062" t="inlineStr"/>
+      <c r="F3062" s="0" t="inlineStr">
+        <is>
+          <t>不知什么缘故，这几个生词我怎么背都记不住。</t>
+        </is>
+      </c>
+      <c r="G3062" s="0" t="inlineStr"/>
+      <c r="H3062" s="0" t="inlineStr"/>
     </row>
     <row r="3063">
-      <c r="A3063" t="inlineStr">
+      <c r="A3063" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3063" t="inlineStr">
+      <c r="B3063" s="0" t="inlineStr">
         <is>
           <t>诚挚</t>
         </is>
       </c>
-      <c r="C3063" t="inlineStr">
+      <c r="C3063" s="0" t="inlineStr">
         <is>
           <t>chéngzhì</t>
         </is>
       </c>
-      <c r="D3063" t="inlineStr">
+      <c r="D3063" s="0" t="inlineStr">
         <is>
           <t>真诚而恳切</t>
         </is>
       </c>
-      <c r="E3063" t="inlineStr">
+      <c r="E3063" s="0" t="inlineStr">
         <is>
           <t>chân thành, thành khẩn</t>
         </is>
       </c>
-      <c r="F3063" t="inlineStr">
-        <is>
-          <t>会谈是在诚挚友好的气氛中进行的。</t>
-        </is>
-      </c>
-      <c r="G3063" t="inlineStr"/>
-      <c r="H3063" t="inlineStr"/>
+      <c r="F3063" s="0" t="inlineStr">
+        <is>
+          <t>学生毕业时给我写了一段很诚挚的话，我特别感动。</t>
+        </is>
+      </c>
+      <c r="G3063" s="0" t="inlineStr"/>
+      <c r="H3063" s="0" t="inlineStr"/>
     </row>
     <row r="3064">
-      <c r="A3064" t="inlineStr">
+      <c r="A3064" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3064" t="inlineStr">
+      <c r="B3064" s="0" t="inlineStr">
         <is>
           <t>倾听</t>
         </is>
       </c>
-      <c r="C3064" t="inlineStr">
+      <c r="C3064" s="0" t="inlineStr">
         <is>
           <t>qīngtīng</t>
         </is>
       </c>
-      <c r="D3064" t="inlineStr">
+      <c r="D3064" s="0" t="inlineStr">
         <is>
           <t>认真、用心地听别人说</t>
         </is>
       </c>
-      <c r="E3064" t="inlineStr">
+      <c r="E3064" s="0" t="inlineStr">
         <is>
           <t>lắng nghe</t>
         </is>
       </c>
-      <c r="F3064" t="inlineStr">
-        <is>
-          <t>了解别人最好的方式就是倾听。</t>
-        </is>
-      </c>
-      <c r="G3064" t="inlineStr"/>
-      <c r="H3064" t="inlineStr"/>
+      <c r="F3064" s="0" t="inlineStr">
+        <is>
+          <t>教低年级的孩子，耐心倾听有时比急着纠错更重要。</t>
+        </is>
+      </c>
+      <c r="G3064" s="0" t="inlineStr"/>
+      <c r="H3064" s="0" t="inlineStr"/>
     </row>
     <row r="3065">
-      <c r="A3065" t="inlineStr">
+      <c r="A3065" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3065" t="inlineStr">
+      <c r="B3065" s="0" t="inlineStr">
         <is>
           <t>视频</t>
         </is>
       </c>
-      <c r="C3065" t="inlineStr">
+      <c r="C3065" s="0" t="inlineStr">
         <is>
           <t>shìpín</t>
         </is>
       </c>
-      <c r="D3065" t="inlineStr">
+      <c r="D3065" s="0" t="inlineStr">
         <is>
           <t>能看到画面的影像</t>
         </is>
       </c>
-      <c r="E3065" t="inlineStr">
+      <c r="E3065" s="0" t="inlineStr">
         <is>
           <t>video, đoạn phim</t>
         </is>
       </c>
-      <c r="F3065" t="inlineStr">
-        <is>
-          <t>看了关于长江黄河的视频，我真想亲眼去看看。</t>
-        </is>
-      </c>
-      <c r="G3065" t="inlineStr"/>
-      <c r="H3065" t="inlineStr"/>
+      <c r="F3065" s="0" t="inlineStr">
+        <is>
+          <t>每天早上我都会看一段中文视频来练听力。</t>
+        </is>
+      </c>
+      <c r="G3065" s="0" t="inlineStr"/>
+      <c r="H3065" s="0" t="inlineStr"/>
     </row>
     <row r="3066">
-      <c r="A3066" t="inlineStr">
+      <c r="A3066" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3066" t="inlineStr">
+      <c r="B3066" s="0" t="inlineStr">
         <is>
           <t>一目了然</t>
         </is>
       </c>
-      <c r="C3066" t="inlineStr">
+      <c r="C3066" s="0" t="inlineStr">
         <is>
           <t>yímùliǎorán</t>
         </is>
       </c>
-      <c r="D3066" t="inlineStr">
+      <c r="D3066" s="0" t="inlineStr">
         <is>
           <t>一眼就能看清楚</t>
         </is>
       </c>
-      <c r="E3066" t="inlineStr">
+      <c r="E3066" s="0" t="inlineStr">
         <is>
           <t>nhìn là hiểu ngay, rõ mồn một</t>
         </is>
       </c>
-      <c r="F3066" t="inlineStr">
-        <is>
-          <t>陈列室明亮宽敞，展品一目了然。</t>
-        </is>
-      </c>
-      <c r="G3066" t="inlineStr"/>
-      <c r="H3066" t="inlineStr"/>
+      <c r="F3066" s="0" t="inlineStr">
+        <is>
+          <t>我把语法做成表格，学生一看就一目了然。</t>
+        </is>
+      </c>
+      <c r="G3066" s="0" t="inlineStr"/>
+      <c r="H3066" s="0" t="inlineStr"/>
     </row>
     <row r="3067">
-      <c r="A3067" t="inlineStr">
+      <c r="A3067" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3067" t="inlineStr">
+      <c r="B3067" s="0" t="inlineStr">
         <is>
           <t>提炼</t>
         </is>
       </c>
-      <c r="C3067" t="inlineStr">
+      <c r="C3067" s="0" t="inlineStr">
         <is>
           <t>tíliàn</t>
         </is>
       </c>
-      <c r="D3067" t="inlineStr">
+      <c r="D3067" s="0" t="inlineStr">
         <is>
           <t>从原料里提取有用的东西；使更精纯</t>
         </is>
       </c>
-      <c r="E3067" t="inlineStr">
+      <c r="E3067" s="0" t="inlineStr">
         <is>
           <t>chiết luyện, chắt lọc</t>
         </is>
       </c>
-      <c r="F3067" t="inlineStr">
-        <is>
-          <t>橄榄可提炼出珍贵的橄榄油。</t>
-        </is>
-      </c>
-      <c r="G3067" t="inlineStr"/>
-      <c r="H3067" t="inlineStr"/>
+      <c r="F3067" s="0" t="inlineStr">
+        <is>
+          <t>读完一篇文章，我会试着把重点提炼成几句话。</t>
+        </is>
+      </c>
+      <c r="G3067" s="0" t="inlineStr"/>
+      <c r="H3067" s="0" t="inlineStr"/>
     </row>
     <row r="3068">
-      <c r="A3068" t="inlineStr">
+      <c r="A3068" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3068" t="inlineStr">
+      <c r="B3068" s="0" t="inlineStr">
         <is>
           <t>探测</t>
         </is>
       </c>
-      <c r="C3068" t="inlineStr">
+      <c r="C3068" s="0" t="inlineStr">
         <is>
           <t>tàncè</t>
         </is>
       </c>
-      <c r="D3068" t="inlineStr">
+      <c r="D3068" s="0" t="inlineStr">
         <is>
           <t>用仪器去测量、察看看不见的东西</t>
         </is>
       </c>
-      <c r="E3068" t="inlineStr">
+      <c r="E3068" s="0" t="inlineStr">
         <is>
           <t>thăm dò, dò tìm</t>
         </is>
       </c>
-      <c r="F3068" t="inlineStr">
-        <is>
-          <t>这些军用犬可以帮助我们探测到爆炸物。</t>
-        </is>
-      </c>
-      <c r="G3068" t="inlineStr"/>
-      <c r="H3068" t="inlineStr"/>
+      <c r="F3068" s="0" t="inlineStr">
+        <is>
+          <t>上课前我常先探测一下学生已经掌握到什么程度。</t>
+        </is>
+      </c>
+      <c r="G3068" s="0" t="inlineStr"/>
+      <c r="H3068" s="0" t="inlineStr"/>
     </row>
     <row r="3069">
-      <c r="A3069" t="inlineStr">
+      <c r="A3069" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3069" t="inlineStr">
+      <c r="B3069" s="0" t="inlineStr">
         <is>
           <t>智商</t>
         </is>
       </c>
-      <c r="C3069" t="inlineStr">
+      <c r="C3069" s="0" t="inlineStr">
         <is>
           <t>zhìshāng</t>
         </is>
       </c>
-      <c r="D3069" t="inlineStr">
+      <c r="D3069" s="0" t="inlineStr">
         <is>
           <t>衡量聪明程度的指数（IQ）</t>
         </is>
       </c>
-      <c r="E3069" t="inlineStr">
+      <c r="E3069" s="0" t="inlineStr">
         <is>
           <t>chỉ số thông minh (IQ)</t>
         </is>
       </c>
-      <c r="F3069" t="inlineStr">
-        <is>
-          <t>智商就是我们常说的IQ。</t>
-        </is>
-      </c>
-      <c r="G3069" t="inlineStr"/>
-      <c r="H3069" t="inlineStr"/>
+      <c r="F3069" s="0" t="inlineStr">
+        <is>
+          <t>学好一门语言靠的不是高智商，而是每天的坚持。</t>
+        </is>
+      </c>
+      <c r="G3069" s="0" t="inlineStr"/>
+      <c r="H3069" s="0" t="inlineStr"/>
     </row>
     <row r="3070">
-      <c r="A3070" t="inlineStr">
+      <c r="A3070" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3070" t="inlineStr">
+      <c r="B3070" s="0" t="inlineStr">
         <is>
           <t>探讨</t>
         </is>
       </c>
-      <c r="C3070" t="inlineStr">
+      <c r="C3070" s="0" t="inlineStr">
         <is>
           <t>tàntǎo</t>
         </is>
       </c>
-      <c r="D3070" t="inlineStr">
+      <c r="D3070" s="0" t="inlineStr">
         <is>
           <t>一起研究、讨论问题</t>
         </is>
       </c>
-      <c r="E3070" t="inlineStr">
+      <c r="E3070" s="0" t="inlineStr">
         <is>
           <t>thảo luận, tìm tòi</t>
         </is>
       </c>
-      <c r="F3070" t="inlineStr">
-        <is>
-          <t>专家们一起探讨治理污水的问题。</t>
-        </is>
-      </c>
-      <c r="G3070" t="inlineStr"/>
-      <c r="H3070" t="inlineStr"/>
+      <c r="F3070" s="0" t="inlineStr">
+        <is>
+          <t>我常跟同事一起探讨怎么把课上得更有意思。</t>
+        </is>
+      </c>
+      <c r="G3070" s="0" t="inlineStr"/>
+      <c r="H3070" s="0" t="inlineStr"/>
     </row>
     <row r="3071">
-      <c r="A3071" t="inlineStr">
+      <c r="A3071" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3071" t="inlineStr">
+      <c r="B3071" s="0" t="inlineStr">
         <is>
           <t>分寸</t>
         </is>
       </c>
-      <c r="C3071" t="inlineStr">
+      <c r="C3071" s="0" t="inlineStr">
         <is>
           <t>fēncun</t>
         </is>
       </c>
-      <c r="D3071" t="inlineStr">
+      <c r="D3071" s="0" t="inlineStr">
         <is>
           <t>说话做事的适当程度、界限</t>
         </is>
       </c>
-      <c r="E3071" t="inlineStr">
+      <c r="E3071" s="0" t="inlineStr">
         <is>
           <t>chừng mực, mức độ phải chăng</t>
         </is>
       </c>
-      <c r="F3071" t="inlineStr">
-        <is>
-          <t>我们说话、做事都要掌握适当的分寸。</t>
-        </is>
-      </c>
-      <c r="G3071" t="inlineStr"/>
-      <c r="H3071" t="inlineStr"/>
+      <c r="F3071" s="0" t="inlineStr">
+        <is>
+          <t>纠正学生发音的时候也要讲分寸，不能太打击他们。</t>
+        </is>
+      </c>
+      <c r="G3071" s="0" t="inlineStr"/>
+      <c r="H3071" s="0" t="inlineStr"/>
     </row>
     <row r="3072">
-      <c r="A3072" t="inlineStr">
+      <c r="A3072" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3072" t="inlineStr">
+      <c r="B3072" s="0" t="inlineStr">
         <is>
           <t>恰到好处</t>
         </is>
       </c>
-      <c r="C3072" t="inlineStr">
+      <c r="C3072" s="0" t="inlineStr">
         <is>
           <t>qiàdàohǎochù</t>
         </is>
       </c>
-      <c r="D3072" t="inlineStr">
+      <c r="D3072" s="0" t="inlineStr">
         <is>
           <t>正好达到最合适的程度</t>
         </is>
       </c>
-      <c r="E3072" t="inlineStr">
+      <c r="E3072" s="0" t="inlineStr">
         <is>
           <t>vừa vặn, đúng mức</t>
         </is>
       </c>
-      <c r="F3072" t="inlineStr">
-        <is>
-          <t>他用适当的方法，恰到好处地处理了这件事。</t>
-        </is>
-      </c>
-      <c r="G3072" t="inlineStr"/>
-      <c r="H3072" t="inlineStr"/>
+      <c r="F3072" s="0" t="inlineStr">
+        <is>
+          <t>好老师提问的难度总是恰到好处，不会太难也不会太简单。</t>
+        </is>
+      </c>
+      <c r="G3072" s="0" t="inlineStr"/>
+      <c r="H3072" s="0" t="inlineStr"/>
     </row>
     <row r="3073">
-      <c r="A3073" t="inlineStr">
+      <c r="A3073" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3073" t="inlineStr">
+      <c r="B3073" s="0" t="inlineStr">
         <is>
           <t>是非</t>
         </is>
       </c>
-      <c r="C3073" t="inlineStr">
+      <c r="C3073" s="0" t="inlineStr">
         <is>
           <t>shìfēi</t>
         </is>
       </c>
-      <c r="D3073" t="inlineStr">
+      <c r="D3073" s="0" t="inlineStr">
         <is>
           <t>对和错</t>
         </is>
       </c>
-      <c r="E3073" t="inlineStr">
+      <c r="E3073" s="0" t="inlineStr">
         <is>
           <t>thị phi, đúng sai</t>
         </is>
       </c>
-      <c r="F3073" t="inlineStr">
-        <is>
-          <t>我们要努力提高分辨是非的能力。</t>
-        </is>
-      </c>
-      <c r="G3073" t="inlineStr"/>
-      <c r="H3073" t="inlineStr"/>
+      <c r="F3073" s="0" t="inlineStr">
+        <is>
+          <t>办公室里的那些是非我一向不参与，专心做自己的事。</t>
+        </is>
+      </c>
+      <c r="G3073" s="0" t="inlineStr"/>
+      <c r="H3073" s="0" t="inlineStr"/>
     </row>
     <row r="3074">
-      <c r="A3074" t="inlineStr">
+      <c r="A3074" s="0" t="inlineStr">
         <is>
           <t>Bài 29</t>
         </is>
       </c>
-      <c r="B3074" t="inlineStr">
+      <c r="B3074" s="0" t="inlineStr">
         <is>
           <t>起哄</t>
         </is>
       </c>
-      <c r="C3074" t="inlineStr">
+      <c r="C3074" s="0" t="inlineStr">
         <is>
           <t>qǐhòng</t>
         </is>
       </c>
-      <c r="D3074" t="inlineStr">
+      <c r="D3074" s="0" t="inlineStr">
         <is>
           <t>很多人一起吵闹、捣乱</t>
         </is>
       </c>
-      <c r="E3074" t="inlineStr">
+      <c r="E3074" s="0" t="inlineStr">
         <is>
           <t>hùa theo làm ầm ĩ, la ó</t>
         </is>
       </c>
-      <c r="F3074" t="inlineStr">
-        <is>
-          <t>小明没有弄清情况，就跟着人家瞎起哄。</t>
-        </is>
-      </c>
-      <c r="G3074" t="inlineStr"/>
-      <c r="H3074" t="inlineStr"/>
+      <c r="F3074" s="0" t="inlineStr">
+        <is>
+          <t>学生一起哄，课堂纪律一下子就乱了。</t>
+        </is>
+      </c>
+      <c r="G3074" s="0" t="inlineStr"/>
+      <c r="H3074" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H3025">

--- a/raw/Từ vựng.xlsx
+++ b/raw/Từ vựng.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3074"/>
+  <dimension ref="A1:AB3124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="13.13" customWidth="1" style="24" min="1" max="1"/>
@@ -72671,6 +72671,1706 @@
       </c>
       <c r="G3074" s="0" t="inlineStr"/>
       <c r="H3074" s="0" t="inlineStr"/>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3075" t="inlineStr">
+        <is>
+          <t>容忍</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>róngrěn</t>
+        </is>
+      </c>
+      <c r="D3075" t="inlineStr">
+        <is>
+          <t>宽容忍耐，不计较别人的过错</t>
+        </is>
+      </c>
+      <c r="E3075" t="inlineStr">
+        <is>
+          <t>dung thứ, khoan dung</t>
+        </is>
+      </c>
+      <c r="F3075" t="inlineStr">
+        <is>
+          <t>备考HSK6压力大，我尽量容忍自己偶尔想偷懒的心情。</t>
+        </is>
+      </c>
+      <c r="G3075" t="inlineStr"/>
+      <c r="H3075" t="inlineStr"/>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3076" t="inlineStr">
+        <is>
+          <t>蹬</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>dēng</t>
+        </is>
+      </c>
+      <c r="D3076" t="inlineStr">
+        <is>
+          <t>用脚用力踩或踏</t>
+        </is>
+      </c>
+      <c r="E3076" t="inlineStr">
+        <is>
+          <t>đạp (chân)</t>
+        </is>
+      </c>
+      <c r="F3076" t="inlineStr">
+        <is>
+          <t>每天下班我都骑共享单车回家，上坡时得使劲蹬。</t>
+        </is>
+      </c>
+      <c r="G3076" t="inlineStr"/>
+      <c r="H3076" t="inlineStr"/>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3077" t="inlineStr">
+        <is>
+          <t>拳头</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>quántou</t>
+        </is>
+      </c>
+      <c r="D3077" t="inlineStr">
+        <is>
+          <t>手指弯曲合拢握紧的手</t>
+        </is>
+      </c>
+      <c r="E3077" t="inlineStr">
+        <is>
+          <t>nắm đấm</t>
+        </is>
+      </c>
+      <c r="F3077" t="inlineStr">
+        <is>
+          <t>教HSK1的“手”字时，我握起拳头给小朋友做示范。</t>
+        </is>
+      </c>
+      <c r="G3077" t="inlineStr"/>
+      <c r="H3077" t="inlineStr"/>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3078" t="inlineStr">
+        <is>
+          <t>不时</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>bùshí</t>
+        </is>
+      </c>
+      <c r="D3078" t="inlineStr">
+        <is>
+          <t>时常，一次又一次地（多用于书面）</t>
+        </is>
+      </c>
+      <c r="E3078" t="inlineStr">
+        <is>
+          <t>thường xuyên, chốc chốc lại</t>
+        </is>
+      </c>
+      <c r="F3078" t="inlineStr">
+        <is>
+          <t>上中文课时，学生不时举手提问，我很喜欢这种气氛。</t>
+        </is>
+      </c>
+      <c r="G3078" t="inlineStr"/>
+      <c r="H3078" t="inlineStr"/>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3079" t="inlineStr">
+        <is>
+          <t>气色</t>
+        </is>
+      </c>
+      <c r="C3079" t="inlineStr">
+        <is>
+          <t>qìsè</t>
+        </is>
+      </c>
+      <c r="D3079" t="inlineStr">
+        <is>
+          <t>人脸上表现出来的健康状况</t>
+        </is>
+      </c>
+      <c r="E3079" t="inlineStr">
+        <is>
+          <t>sắc mặt, thần sắc</t>
+        </is>
+      </c>
+      <c r="F3079" t="inlineStr">
+        <is>
+          <t>昨晚熬夜背单词，今天同事说我气色不太好。</t>
+        </is>
+      </c>
+      <c r="G3079" t="inlineStr"/>
+      <c r="H3079" t="inlineStr"/>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3080" t="inlineStr">
+        <is>
+          <t>轨道</t>
+        </is>
+      </c>
+      <c r="C3080" t="inlineStr">
+        <is>
+          <t>guǐdào</t>
+        </is>
+      </c>
+      <c r="D3080" t="inlineStr">
+        <is>
+          <t>火车、地铁行驶的路线；也比喻正常发展的路子</t>
+        </is>
+      </c>
+      <c r="E3080" t="inlineStr">
+        <is>
+          <t>đường ray; quỹ đạo</t>
+        </is>
+      </c>
+      <c r="F3080" t="inlineStr">
+        <is>
+          <t>备考计划乱了一阵，现在又回到了正常轨道。</t>
+        </is>
+      </c>
+      <c r="G3080" t="inlineStr"/>
+      <c r="H3080" t="inlineStr"/>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3081" t="inlineStr">
+        <is>
+          <t>酒精</t>
+        </is>
+      </c>
+      <c r="C3081" t="inlineStr">
+        <is>
+          <t>jiǔjīng</t>
+        </is>
+      </c>
+      <c r="D3081" t="inlineStr">
+        <is>
+          <t>酒里能使人醉的成分</t>
+        </is>
+      </c>
+      <c r="E3081" t="inlineStr">
+        <is>
+          <t>cồn, chất cồn (trong rượu)</t>
+        </is>
+      </c>
+      <c r="F3081" t="inlineStr">
+        <is>
+          <t>在中国跟同事聚餐时，我一般不喝酒精含量高的白酒。</t>
+        </is>
+      </c>
+      <c r="G3081" t="inlineStr"/>
+      <c r="H3081" t="inlineStr"/>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3082" t="inlineStr">
+        <is>
+          <t>竭尽全力</t>
+        </is>
+      </c>
+      <c r="C3082" t="inlineStr">
+        <is>
+          <t>jiéjìn quánlì</t>
+        </is>
+      </c>
+      <c r="D3082" t="inlineStr">
+        <is>
+          <t>用尽全部的力量</t>
+        </is>
+      </c>
+      <c r="E3082" t="inlineStr">
+        <is>
+          <t>dốc hết sức, gắng hết sức</t>
+        </is>
+      </c>
+      <c r="F3082" t="inlineStr">
+        <is>
+          <t>为了HSKK拿高分，我竭尽全力每天练口语。</t>
+        </is>
+      </c>
+      <c r="G3082" t="inlineStr"/>
+      <c r="H3082" t="inlineStr"/>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3083" t="inlineStr">
+        <is>
+          <t>根源</t>
+        </is>
+      </c>
+      <c r="C3083" t="inlineStr">
+        <is>
+          <t>gēnyuán</t>
+        </is>
+      </c>
+      <c r="D3083" t="inlineStr">
+        <is>
+          <t>事情产生的根本原因</t>
+        </is>
+      </c>
+      <c r="E3083" t="inlineStr">
+        <is>
+          <t>nguồn gốc, căn nguyên</t>
+        </is>
+      </c>
+      <c r="F3083" t="inlineStr">
+        <is>
+          <t>我发现自己听力差的根源是平时听得太少。</t>
+        </is>
+      </c>
+      <c r="G3083" t="inlineStr"/>
+      <c r="H3083" t="inlineStr"/>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3084" t="inlineStr">
+        <is>
+          <t>对付</t>
+        </is>
+      </c>
+      <c r="C3084" t="inlineStr">
+        <is>
+          <t>duìfu</t>
+        </is>
+      </c>
+      <c r="D3084" t="inlineStr">
+        <is>
+          <t>想办法处理人或事情</t>
+        </is>
+      </c>
+      <c r="E3084" t="inlineStr">
+        <is>
+          <t>đối phó, ứng phó</t>
+        </is>
+      </c>
+      <c r="F3084" t="inlineStr">
+        <is>
+          <t>遇到不会做的HSK6阅读题，我有一套自己对付的办法。</t>
+        </is>
+      </c>
+      <c r="G3084" t="inlineStr"/>
+      <c r="H3084" t="inlineStr"/>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3085" t="inlineStr">
+        <is>
+          <t>纠正</t>
+        </is>
+      </c>
+      <c r="C3085" t="inlineStr">
+        <is>
+          <t>jiūzhèng</t>
+        </is>
+      </c>
+      <c r="D3085" t="inlineStr">
+        <is>
+          <t>改正错误</t>
+        </is>
+      </c>
+      <c r="E3085" t="inlineStr">
+        <is>
+          <t>sửa chữa, uốn nắn</t>
+        </is>
+      </c>
+      <c r="F3085" t="inlineStr">
+        <is>
+          <t>上课时我会及时纠正学生的发音错误。</t>
+        </is>
+      </c>
+      <c r="G3085" t="inlineStr"/>
+      <c r="H3085" t="inlineStr"/>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3086" t="inlineStr">
+        <is>
+          <t>糟蹋</t>
+        </is>
+      </c>
+      <c r="C3086" t="inlineStr">
+        <is>
+          <t>zāotà</t>
+        </is>
+      </c>
+      <c r="D3086" t="inlineStr">
+        <is>
+          <t>浪费或随意损坏（东西、身体等）</t>
+        </is>
+      </c>
+      <c r="E3086" t="inlineStr">
+        <is>
+          <t>phí phạm, tàn phá</t>
+        </is>
+      </c>
+      <c r="F3086" t="inlineStr">
+        <is>
+          <t>经常熬夜其实就是在糟蹋自己的身体。</t>
+        </is>
+      </c>
+      <c r="G3086" t="inlineStr"/>
+      <c r="H3086" t="inlineStr"/>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3087" t="inlineStr">
+        <is>
+          <t>迫害</t>
+        </is>
+      </c>
+      <c r="C3087" t="inlineStr">
+        <is>
+          <t>pòhài</t>
+        </is>
+      </c>
+      <c r="D3087" t="inlineStr">
+        <is>
+          <t>用暴力或权势残酷地压迫、伤害</t>
+        </is>
+      </c>
+      <c r="E3087" t="inlineStr">
+        <is>
+          <t>bức hại</t>
+        </is>
+      </c>
+      <c r="F3087" t="inlineStr">
+        <is>
+          <t>这部纪录片讲的是战争年代很多人遭到迫害的故事。</t>
+        </is>
+      </c>
+      <c r="G3087" t="inlineStr"/>
+      <c r="H3087" t="inlineStr"/>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3088" t="inlineStr">
+        <is>
+          <t>毁灭</t>
+        </is>
+      </c>
+      <c r="C3088" t="inlineStr">
+        <is>
+          <t>huǐmiè</t>
+        </is>
+      </c>
+      <c r="D3088" t="inlineStr">
+        <is>
+          <t>彻底摧毁，使不再存在</t>
+        </is>
+      </c>
+      <c r="E3088" t="inlineStr">
+        <is>
+          <t>hủy diệt, phá hủy</t>
+        </is>
+      </c>
+      <c r="F3088" t="inlineStr">
+        <is>
+          <t>坏习惯会一点一点毁灭一个人的健康。</t>
+        </is>
+      </c>
+      <c r="G3088" t="inlineStr"/>
+      <c r="H3088" t="inlineStr"/>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3089" t="inlineStr">
+        <is>
+          <t>惯例</t>
+        </is>
+      </c>
+      <c r="C3089" t="inlineStr">
+        <is>
+          <t>guànlì</t>
+        </is>
+      </c>
+      <c r="D3089" t="inlineStr">
+        <is>
+          <t>一向的做法，习惯上的规矩</t>
+        </is>
+      </c>
+      <c r="E3089" t="inlineStr">
+        <is>
+          <t>thông lệ, lệ thường</t>
+        </is>
+      </c>
+      <c r="F3089" t="inlineStr">
+        <is>
+          <t>按照惯例，我每天早上先复习昨天学的生词。</t>
+        </is>
+      </c>
+      <c r="G3089" t="inlineStr"/>
+      <c r="H3089" t="inlineStr"/>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3090" t="inlineStr">
+        <is>
+          <t>顽固</t>
+        </is>
+      </c>
+      <c r="C3090" t="inlineStr">
+        <is>
+          <t>wángù</t>
+        </is>
+      </c>
+      <c r="D3090" t="inlineStr">
+        <is>
+          <t>思想保守、不肯改变；（病）难治</t>
+        </is>
+      </c>
+      <c r="E3090" t="inlineStr">
+        <is>
+          <t>ngoan cố; dai dẳng (bệnh)</t>
+        </is>
+      </c>
+      <c r="F3090" t="inlineStr">
+        <is>
+          <t>我有个顽固的坏习惯，就是睡前老爱看手机。</t>
+        </is>
+      </c>
+      <c r="G3090" t="inlineStr"/>
+      <c r="H3090" t="inlineStr"/>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3091" t="inlineStr">
+        <is>
+          <t>奢侈</t>
+        </is>
+      </c>
+      <c r="C3091" t="inlineStr">
+        <is>
+          <t>shēchǐ</t>
+        </is>
+      </c>
+      <c r="D3091" t="inlineStr">
+        <is>
+          <t>花很多钱财追求享受</t>
+        </is>
+      </c>
+      <c r="E3091" t="inlineStr">
+        <is>
+          <t>xa xỉ, xa hoa</t>
+        </is>
+      </c>
+      <c r="F3091" t="inlineStr">
+        <is>
+          <t>对上班族来说，能睡到自然醒简直是一种奢侈。</t>
+        </is>
+      </c>
+      <c r="G3091" t="inlineStr"/>
+      <c r="H3091" t="inlineStr"/>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3092" t="inlineStr">
+        <is>
+          <t>指数</t>
+        </is>
+      </c>
+      <c r="C3092" t="inlineStr">
+        <is>
+          <t>zhǐshù</t>
+        </is>
+      </c>
+      <c r="D3092" t="inlineStr">
+        <is>
+          <t>用来表示某种情况变动的数值</t>
+        </is>
+      </c>
+      <c r="E3092" t="inlineStr">
+        <is>
+          <t>chỉ số</t>
+        </is>
+      </c>
+      <c r="F3092" t="inlineStr">
+        <is>
+          <t>中国发布的睡眠指数显示很多人睡眠质量不高。</t>
+        </is>
+      </c>
+      <c r="G3092" t="inlineStr"/>
+      <c r="H3092" t="inlineStr"/>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3093" t="inlineStr">
+        <is>
+          <t>居民</t>
+        </is>
+      </c>
+      <c r="C3093" t="inlineStr">
+        <is>
+          <t>jūmín</t>
+        </is>
+      </c>
+      <c r="D3093" t="inlineStr">
+        <is>
+          <t>住在某个地方的人</t>
+        </is>
+      </c>
+      <c r="E3093" t="inlineStr">
+        <is>
+          <t>cư dân, dân cư</t>
+        </is>
+      </c>
+      <c r="F3093" t="inlineStr">
+        <is>
+          <t>我住的小区居民大多是年轻上班族。</t>
+        </is>
+      </c>
+      <c r="G3093" t="inlineStr"/>
+      <c r="H3093" t="inlineStr"/>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3094" t="inlineStr">
+        <is>
+          <t>当前</t>
+        </is>
+      </c>
+      <c r="C3094" t="inlineStr">
+        <is>
+          <t>dāngqián</t>
+        </is>
+      </c>
+      <c r="D3094" t="inlineStr">
+        <is>
+          <t>目前，现在这个时候</t>
+        </is>
+      </c>
+      <c r="E3094" t="inlineStr">
+        <is>
+          <t>hiện nay, trước mắt</t>
+        </is>
+      </c>
+      <c r="F3094" t="inlineStr">
+        <is>
+          <t>当前我最重要的任务就是顺利通过HSK6。</t>
+        </is>
+      </c>
+      <c r="G3094" t="inlineStr"/>
+      <c r="H3094" t="inlineStr"/>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3095" t="inlineStr">
+        <is>
+          <t>扰乱</t>
+        </is>
+      </c>
+      <c r="C3095" t="inlineStr">
+        <is>
+          <t>rǎoluàn</t>
+        </is>
+      </c>
+      <c r="D3095" t="inlineStr">
+        <is>
+          <t>打乱，使变得混乱</t>
+        </is>
+      </c>
+      <c r="E3095" t="inlineStr">
+        <is>
+          <t>quấy nhiễu, làm rối loạn</t>
+        </is>
+      </c>
+      <c r="F3095" t="inlineStr">
+        <is>
+          <t>睡前刷手机会扰乱我的作息。</t>
+        </is>
+      </c>
+      <c r="G3095" t="inlineStr"/>
+      <c r="H3095" t="inlineStr"/>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3096" t="inlineStr">
+        <is>
+          <t>折腾</t>
+        </is>
+      </c>
+      <c r="C3096" t="inlineStr">
+        <is>
+          <t>zhēteng</t>
+        </is>
+      </c>
+      <c r="D3096" t="inlineStr">
+        <is>
+          <t>反复做某事；使身心不得安宁</t>
+        </is>
+      </c>
+      <c r="E3096" t="inlineStr">
+        <is>
+          <t>hành hạ; trằn trọc, quần quật</t>
+        </is>
+      </c>
+      <c r="F3096" t="inlineStr">
+        <is>
+          <t>昨晚失眠，我在床上翻来覆去折腾了大半夜。</t>
+        </is>
+      </c>
+      <c r="G3096" t="inlineStr"/>
+      <c r="H3096" t="inlineStr"/>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3097" t="inlineStr">
+        <is>
+          <t>逆行</t>
+        </is>
+      </c>
+      <c r="C3097" t="inlineStr">
+        <is>
+          <t>nìxíng</t>
+        </is>
+      </c>
+      <c r="D3097" t="inlineStr">
+        <is>
+          <t>朝着跟规定相反的方向行进</t>
+        </is>
+      </c>
+      <c r="E3097" t="inlineStr">
+        <is>
+          <t>đi ngược chiều</t>
+        </is>
+      </c>
+      <c r="F3097" t="inlineStr">
+        <is>
+          <t>在中国骑车千万不能逆行，太危险了。</t>
+        </is>
+      </c>
+      <c r="G3097" t="inlineStr"/>
+      <c r="H3097" t="inlineStr"/>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3098" t="inlineStr">
+        <is>
+          <t>茫然</t>
+        </is>
+      </c>
+      <c r="C3098" t="inlineStr">
+        <is>
+          <t>mángrán</t>
+        </is>
+      </c>
+      <c r="D3098" t="inlineStr">
+        <is>
+          <t>完全不知道，心里没有主意的样子</t>
+        </is>
+      </c>
+      <c r="E3098" t="inlineStr">
+        <is>
+          <t>mờ mịt, ngơ ngác</t>
+        </is>
+      </c>
+      <c r="F3098" t="inlineStr">
+        <is>
+          <t>刚开始学HSK6语法时，我常常一脸茫然。</t>
+        </is>
+      </c>
+      <c r="G3098" t="inlineStr"/>
+      <c r="H3098" t="inlineStr"/>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3099" t="inlineStr">
+        <is>
+          <t>丢三落四</t>
+        </is>
+      </c>
+      <c r="C3099" t="inlineStr">
+        <is>
+          <t>diūsān-làsì</t>
+        </is>
+      </c>
+      <c r="D3099" t="inlineStr">
+        <is>
+          <t>做事马虎，常常有遗漏</t>
+        </is>
+      </c>
+      <c r="E3099" t="inlineStr">
+        <is>
+          <t>đầu quên đuôi, hay quên</t>
+        </is>
+      </c>
+      <c r="F3099" t="inlineStr">
+        <is>
+          <t>我记性不好，出门总是丢三落四。</t>
+        </is>
+      </c>
+      <c r="G3099" t="inlineStr"/>
+      <c r="H3099" t="inlineStr"/>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3100" t="inlineStr">
+        <is>
+          <t>起伏</t>
+        </is>
+      </c>
+      <c r="C3100" t="inlineStr">
+        <is>
+          <t>qǐfú</t>
+        </is>
+      </c>
+      <c r="D3100" t="inlineStr">
+        <is>
+          <t>一起一落；（情绪等）变化不定</t>
+        </is>
+      </c>
+      <c r="E3100" t="inlineStr">
+        <is>
+          <t>nhấp nhô; thăng trầm, biến động</t>
+        </is>
+      </c>
+      <c r="F3100" t="inlineStr">
+        <is>
+          <t>备考那段时间我情绪起伏很大，一会儿信心满满，一会儿又想放弃。</t>
+        </is>
+      </c>
+      <c r="G3100" t="inlineStr"/>
+      <c r="H3100" t="inlineStr"/>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3101" t="inlineStr">
+        <is>
+          <t>发呆</t>
+        </is>
+      </c>
+      <c r="C3101" t="inlineStr">
+        <is>
+          <t>fādāi</t>
+        </is>
+      </c>
+      <c r="D3101" t="inlineStr">
+        <is>
+          <t>因为出神而呆呆地不动</t>
+        </is>
+      </c>
+      <c r="E3101" t="inlineStr">
+        <is>
+          <t>thẫn thờ, ngẩn người ra</t>
+        </is>
+      </c>
+      <c r="F3101" t="inlineStr">
+        <is>
+          <t>单词背累了，我常常对着窗外发呆。</t>
+        </is>
+      </c>
+      <c r="G3101" t="inlineStr"/>
+      <c r="H3101" t="inlineStr"/>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3102" t="inlineStr">
+        <is>
+          <t>记性</t>
+        </is>
+      </c>
+      <c r="C3102" t="inlineStr">
+        <is>
+          <t>jìxing</t>
+        </is>
+      </c>
+      <c r="D3102" t="inlineStr">
+        <is>
+          <t>记忆的能力</t>
+        </is>
+      </c>
+      <c r="E3102" t="inlineStr">
+        <is>
+          <t>trí nhớ</t>
+        </is>
+      </c>
+      <c r="F3102" t="inlineStr">
+        <is>
+          <t>睡不好觉，我的记性明显变差了。</t>
+        </is>
+      </c>
+      <c r="G3102" t="inlineStr"/>
+      <c r="H3102" t="inlineStr"/>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3103" t="inlineStr">
+        <is>
+          <t>摧残</t>
+        </is>
+      </c>
+      <c r="C3103" t="inlineStr">
+        <is>
+          <t>cuīcán</t>
+        </is>
+      </c>
+      <c r="D3103" t="inlineStr">
+        <is>
+          <t>使受到严重的损害</t>
+        </is>
+      </c>
+      <c r="E3103" t="inlineStr">
+        <is>
+          <t>tàn phá, dày vò</t>
+        </is>
+      </c>
+      <c r="F3103" t="inlineStr">
+        <is>
+          <t>长期熬夜会摧残身体健康。</t>
+        </is>
+      </c>
+      <c r="G3103" t="inlineStr"/>
+      <c r="H3103" t="inlineStr"/>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3104" t="inlineStr">
+        <is>
+          <t>普及</t>
+        </is>
+      </c>
+      <c r="C3104" t="inlineStr">
+        <is>
+          <t>pǔjí</t>
+        </is>
+      </c>
+      <c r="D3104" t="inlineStr">
+        <is>
+          <t>普遍推广，使大家都有或都懂</t>
+        </is>
+      </c>
+      <c r="E3104" t="inlineStr">
+        <is>
+          <t>phổ cập, phổ biến</t>
+        </is>
+      </c>
+      <c r="F3104" t="inlineStr">
+        <is>
+          <t>智能手机普及以后，很多人睡前都离不开它。</t>
+        </is>
+      </c>
+      <c r="G3104" t="inlineStr"/>
+      <c r="H3104" t="inlineStr"/>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3105" t="inlineStr">
+        <is>
+          <t>盛行</t>
+        </is>
+      </c>
+      <c r="C3105" t="inlineStr">
+        <is>
+          <t>shèngxíng</t>
+        </is>
+      </c>
+      <c r="D3105" t="inlineStr">
+        <is>
+          <t>广泛地流行</t>
+        </is>
+      </c>
+      <c r="E3105" t="inlineStr">
+        <is>
+          <t>thịnh hành, phổ biến rộng</t>
+        </is>
+      </c>
+      <c r="F3105" t="inlineStr">
+        <is>
+          <t>现在睡前上网的习惯很盛行。</t>
+        </is>
+      </c>
+      <c r="G3105" t="inlineStr"/>
+      <c r="H3105" t="inlineStr"/>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3106" t="inlineStr">
+        <is>
+          <t>细胞</t>
+        </is>
+      </c>
+      <c r="C3106" t="inlineStr">
+        <is>
+          <t>xìbāo</t>
+        </is>
+      </c>
+      <c r="D3106" t="inlineStr">
+        <is>
+          <t>生物体结构和功能的基本单位</t>
+        </is>
+      </c>
+      <c r="E3106" t="inlineStr">
+        <is>
+          <t>tế bào</t>
+        </is>
+      </c>
+      <c r="F3106" t="inlineStr">
+        <is>
+          <t>熬夜会影响人体细胞的正常活动。</t>
+        </is>
+      </c>
+      <c r="G3106" t="inlineStr"/>
+      <c r="H3106" t="inlineStr"/>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3107" t="inlineStr">
+        <is>
+          <t>肿瘤</t>
+        </is>
+      </c>
+      <c r="C3107" t="inlineStr">
+        <is>
+          <t>zhǒngliú</t>
+        </is>
+      </c>
+      <c r="D3107" t="inlineStr">
+        <is>
+          <t>身体里不正常增生的组织块</t>
+        </is>
+      </c>
+      <c r="E3107" t="inlineStr">
+        <is>
+          <t>khối u, u bướu</t>
+        </is>
+      </c>
+      <c r="F3107" t="inlineStr">
+        <is>
+          <t>医生说定期体检能早点发现肿瘤。</t>
+        </is>
+      </c>
+      <c r="G3107" t="inlineStr"/>
+      <c r="H3107" t="inlineStr"/>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3108" t="inlineStr">
+        <is>
+          <t>癌症</t>
+        </is>
+      </c>
+      <c r="C3108" t="inlineStr">
+        <is>
+          <t>áizhèng</t>
+        </is>
+      </c>
+      <c r="D3108" t="inlineStr">
+        <is>
+          <t>由恶性肿瘤引起的疾病</t>
+        </is>
+      </c>
+      <c r="E3108" t="inlineStr">
+        <is>
+          <t>bệnh ung thư</t>
+        </is>
+      </c>
+      <c r="F3108" t="inlineStr">
+        <is>
+          <t>不良的生活习惯可能会增加得癌症的风险。</t>
+        </is>
+      </c>
+      <c r="G3108" t="inlineStr"/>
+      <c r="H3108" t="inlineStr"/>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3109" t="inlineStr">
+        <is>
+          <t>呼吁</t>
+        </is>
+      </c>
+      <c r="C3109" t="inlineStr">
+        <is>
+          <t>hūyù</t>
+        </is>
+      </c>
+      <c r="D3109" t="inlineStr">
+        <is>
+          <t>大声向社会请求支持或帮助</t>
+        </is>
+      </c>
+      <c r="E3109" t="inlineStr">
+        <is>
+          <t>kêu gọi</t>
+        </is>
+      </c>
+      <c r="F3109" t="inlineStr">
+        <is>
+          <t>医生呼吁大家不要经常熬夜。</t>
+        </is>
+      </c>
+      <c r="G3109" t="inlineStr"/>
+      <c r="H3109" t="inlineStr"/>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3110" t="inlineStr">
+        <is>
+          <t>无动于衷</t>
+        </is>
+      </c>
+      <c r="C3110" t="inlineStr">
+        <is>
+          <t>wúdòngyúzhōng</t>
+        </is>
+      </c>
+      <c r="D3110" t="inlineStr">
+        <is>
+          <t>心里一点儿也不受触动，毫不在意</t>
+        </is>
+      </c>
+      <c r="E3110" t="inlineStr">
+        <is>
+          <t>thờ ơ, dửng dưng</t>
+        </is>
+      </c>
+      <c r="F3110" t="inlineStr">
+        <is>
+          <t>对自己的坏习惯不能无动于衷，要及时改正。</t>
+        </is>
+      </c>
+      <c r="G3110" t="inlineStr"/>
+      <c r="H3110" t="inlineStr"/>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3111" t="inlineStr">
+        <is>
+          <t>过瘾</t>
+        </is>
+      </c>
+      <c r="C3111" t="inlineStr">
+        <is>
+          <t>guòyǐn</t>
+        </is>
+      </c>
+      <c r="D3111" t="inlineStr">
+        <is>
+          <t>满足了某种爱好，觉得很痛快</t>
+        </is>
+      </c>
+      <c r="E3111" t="inlineStr">
+        <is>
+          <t>đã, thỏa mãn (sở thích)</t>
+        </is>
+      </c>
+      <c r="F3111" t="inlineStr">
+        <is>
+          <t>周末追一整天中文剧，看得特别过瘾。</t>
+        </is>
+      </c>
+      <c r="G3111" t="inlineStr"/>
+      <c r="H3111" t="inlineStr"/>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3112" t="inlineStr">
+        <is>
+          <t>分泌</t>
+        </is>
+      </c>
+      <c r="C3112" t="inlineStr">
+        <is>
+          <t>fēnmì</t>
+        </is>
+      </c>
+      <c r="D3112" t="inlineStr">
+        <is>
+          <t>生物体产生并排出某种物质</t>
+        </is>
+      </c>
+      <c r="E3112" t="inlineStr">
+        <is>
+          <t>tiết ra, bài tiết</t>
+        </is>
+      </c>
+      <c r="F3112" t="inlineStr">
+        <is>
+          <t>光污染会影响人体褪黑素的分泌。</t>
+        </is>
+      </c>
+      <c r="G3112" t="inlineStr"/>
+      <c r="H3112" t="inlineStr"/>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3113" t="inlineStr">
+        <is>
+          <t>职能</t>
+        </is>
+      </c>
+      <c r="C3113" t="inlineStr">
+        <is>
+          <t>zhínéng</t>
+        </is>
+      </c>
+      <c r="D3113" t="inlineStr">
+        <is>
+          <t>事物或机构应有的功能、作用</t>
+        </is>
+      </c>
+      <c r="E3113" t="inlineStr">
+        <is>
+          <t>chức năng</t>
+        </is>
+      </c>
+      <c r="F3113" t="inlineStr">
+        <is>
+          <t>褪黑素的一个重要职能是帮助睡眠。</t>
+        </is>
+      </c>
+      <c r="G3113" t="inlineStr"/>
+      <c r="H3113" t="inlineStr"/>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3114" t="inlineStr">
+        <is>
+          <t>衰老</t>
+        </is>
+      </c>
+      <c r="C3114" t="inlineStr">
+        <is>
+          <t>shuāilǎo</t>
+        </is>
+      </c>
+      <c r="D3114" t="inlineStr">
+        <is>
+          <t>身体机能因年老而衰退</t>
+        </is>
+      </c>
+      <c r="E3114" t="inlineStr">
+        <is>
+          <t>già đi, lão hóa</t>
+        </is>
+      </c>
+      <c r="F3114" t="inlineStr">
+        <is>
+          <t>睡眠不足会让人加速衰老。</t>
+        </is>
+      </c>
+      <c r="G3114" t="inlineStr"/>
+      <c r="H3114" t="inlineStr"/>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3115" t="inlineStr">
+        <is>
+          <t>调剂</t>
+        </is>
+      </c>
+      <c r="C3115" t="inlineStr">
+        <is>
+          <t>tiáojì</t>
+        </is>
+      </c>
+      <c r="D3115" t="inlineStr">
+        <is>
+          <t>调整使合适；调节</t>
+        </is>
+      </c>
+      <c r="E3115" t="inlineStr">
+        <is>
+          <t>điều tiết, điều hòa</t>
+        </is>
+      </c>
+      <c r="F3115" t="inlineStr">
+        <is>
+          <t>学习累了，我会听听音乐调剂一下心情。</t>
+        </is>
+      </c>
+      <c r="G3115" t="inlineStr"/>
+      <c r="H3115" t="inlineStr"/>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3116" t="inlineStr">
+        <is>
+          <t>供不应求</t>
+        </is>
+      </c>
+      <c r="C3116" t="inlineStr">
+        <is>
+          <t>gōngbùyìngqiú</t>
+        </is>
+      </c>
+      <c r="D3116" t="inlineStr">
+        <is>
+          <t>供应满足不了需求</t>
+        </is>
+      </c>
+      <c r="E3116" t="inlineStr">
+        <is>
+          <t>cung không đủ cầu</t>
+        </is>
+      </c>
+      <c r="F3116" t="inlineStr">
+        <is>
+          <t>在中国，好的睡眠门诊医生总是供不应求。</t>
+        </is>
+      </c>
+      <c r="G3116" t="inlineStr"/>
+      <c r="H3116" t="inlineStr"/>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3117" t="inlineStr">
+        <is>
+          <t>不相上下</t>
+        </is>
+      </c>
+      <c r="C3117" t="inlineStr">
+        <is>
+          <t>bùxiāng-shàngxià</t>
+        </is>
+      </c>
+      <c r="D3117" t="inlineStr">
+        <is>
+          <t>分不出高低好坏，程度差不多</t>
+        </is>
+      </c>
+      <c r="E3117" t="inlineStr">
+        <is>
+          <t>ngang tài ngang sức, xấp xỉ</t>
+        </is>
+      </c>
+      <c r="F3117" t="inlineStr">
+        <is>
+          <t>我和同桌的汉语水平不相上下。</t>
+        </is>
+      </c>
+      <c r="G3117" t="inlineStr"/>
+      <c r="H3117" t="inlineStr"/>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3118" t="inlineStr">
+        <is>
+          <t>总而言之</t>
+        </is>
+      </c>
+      <c r="C3118" t="inlineStr">
+        <is>
+          <t>zǒng'éryánzhī</t>
+        </is>
+      </c>
+      <c r="D3118" t="inlineStr">
+        <is>
+          <t>总的说来</t>
+        </is>
+      </c>
+      <c r="E3118" t="inlineStr">
+        <is>
+          <t>tóm lại, nói tóm lại</t>
+        </is>
+      </c>
+      <c r="F3118" t="inlineStr">
+        <is>
+          <t>总而言之，想学好中文，坚持最重要。</t>
+        </is>
+      </c>
+      <c r="G3118" t="inlineStr"/>
+      <c r="H3118" t="inlineStr"/>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3119" t="inlineStr">
+        <is>
+          <t>恶化</t>
+        </is>
+      </c>
+      <c r="C3119" t="inlineStr">
+        <is>
+          <t>èhuà</t>
+        </is>
+      </c>
+      <c r="D3119" t="inlineStr">
+        <is>
+          <t>情况向坏的方向发展</t>
+        </is>
+      </c>
+      <c r="E3119" t="inlineStr">
+        <is>
+          <t>xấu đi, trở nặng</t>
+        </is>
+      </c>
+      <c r="F3119" t="inlineStr">
+        <is>
+          <t>如果一直睡不好，健康状况会慢慢恶化。</t>
+        </is>
+      </c>
+      <c r="G3119" t="inlineStr"/>
+      <c r="H3119" t="inlineStr"/>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3120" t="inlineStr">
+        <is>
+          <t>适宜</t>
+        </is>
+      </c>
+      <c r="C3120" t="inlineStr">
+        <is>
+          <t>shìyí</t>
+        </is>
+      </c>
+      <c r="D3120" t="inlineStr">
+        <is>
+          <t>合适，恰当</t>
+        </is>
+      </c>
+      <c r="E3120" t="inlineStr">
+        <is>
+          <t>thích hợp, phù hợp</t>
+        </is>
+      </c>
+      <c r="F3120" t="inlineStr">
+        <is>
+          <t>睡前听点轻音乐，很适宜放松心情。</t>
+        </is>
+      </c>
+      <c r="G3120" t="inlineStr"/>
+      <c r="H3120" t="inlineStr"/>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3121" t="inlineStr">
+        <is>
+          <t>场合</t>
+        </is>
+      </c>
+      <c r="C3121" t="inlineStr">
+        <is>
+          <t>chǎnghé</t>
+        </is>
+      </c>
+      <c r="D3121" t="inlineStr">
+        <is>
+          <t>一定的时间、地点和情况</t>
+        </is>
+      </c>
+      <c r="E3121" t="inlineStr">
+        <is>
+          <t>trường hợp, dịp, hoàn cảnh</t>
+        </is>
+      </c>
+      <c r="F3121" t="inlineStr">
+        <is>
+          <t>在正式场合，我说中文会更客气一些。</t>
+        </is>
+      </c>
+      <c r="G3121" t="inlineStr"/>
+      <c r="H3121" t="inlineStr"/>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3122" t="inlineStr">
+        <is>
+          <t>地步</t>
+        </is>
+      </c>
+      <c r="C3122" t="inlineStr">
+        <is>
+          <t>dìbù</t>
+        </is>
+      </c>
+      <c r="D3122" t="inlineStr">
+        <is>
+          <t>达到的程度（多指不好的情况）</t>
+        </is>
+      </c>
+      <c r="E3122" t="inlineStr">
+        <is>
+          <t>mức độ, nước (đến nước)</t>
+        </is>
+      </c>
+      <c r="F3122" t="inlineStr">
+        <is>
+          <t>那阵子我忙到连饭都顾不上吃的地步。</t>
+        </is>
+      </c>
+      <c r="G3122" t="inlineStr"/>
+      <c r="H3122" t="inlineStr"/>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3123" t="inlineStr">
+        <is>
+          <t>混乱</t>
+        </is>
+      </c>
+      <c r="C3123" t="inlineStr">
+        <is>
+          <t>hùnluàn</t>
+        </is>
+      </c>
+      <c r="D3123" t="inlineStr">
+        <is>
+          <t>没有条理，乱七八糟</t>
+        </is>
+      </c>
+      <c r="E3123" t="inlineStr">
+        <is>
+          <t>hỗn loạn, lộn xộn</t>
+        </is>
+      </c>
+      <c r="F3123" t="inlineStr">
+        <is>
+          <t>睡不好觉时，我的思路会变得很混乱。</t>
+        </is>
+      </c>
+      <c r="G3123" t="inlineStr"/>
+      <c r="H3123" t="inlineStr"/>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>Bài 30</t>
+        </is>
+      </c>
+      <c r="B3124" t="inlineStr">
+        <is>
+          <t>举足轻重</t>
+        </is>
+      </c>
+      <c r="C3124" t="inlineStr">
+        <is>
+          <t>jǔzú-qīngzhòng</t>
+        </is>
+      </c>
+      <c r="D3124" t="inlineStr">
+        <is>
+          <t>所处地位重要，一举一动都影响全局</t>
+        </is>
+      </c>
+      <c r="E3124" t="inlineStr">
+        <is>
+          <t>có vai trò then chốt, cực kỳ quan trọng</t>
+        </is>
+      </c>
+      <c r="F3124" t="inlineStr">
+        <is>
+          <t>睡眠对健康举足轻重，千万不能忽视。</t>
+        </is>
+      </c>
+      <c r="G3124" t="inlineStr"/>
+      <c r="H3124" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H3025">

--- a/raw/Từ vựng.xlsx
+++ b/raw/Từ vựng.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3124"/>
+  <dimension ref="A1:AB3312"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="13.13" customWidth="1" style="24" min="1" max="1"/>
@@ -72673,1704 +72673,8096 @@
       <c r="H3074" s="0" t="inlineStr"/>
     </row>
     <row r="3075">
-      <c r="A3075" t="inlineStr">
+      <c r="A3075" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3075" t="inlineStr">
+      <c r="B3075" s="0" t="inlineStr">
         <is>
           <t>容忍</t>
         </is>
       </c>
-      <c r="C3075" t="inlineStr">
+      <c r="C3075" s="0" t="inlineStr">
         <is>
           <t>róngrěn</t>
         </is>
       </c>
-      <c r="D3075" t="inlineStr">
+      <c r="D3075" s="0" t="inlineStr">
         <is>
           <t>宽容忍耐，不计较别人的过错</t>
         </is>
       </c>
-      <c r="E3075" t="inlineStr">
+      <c r="E3075" s="0" t="inlineStr">
         <is>
           <t>dung thứ, khoan dung</t>
         </is>
       </c>
-      <c r="F3075" t="inlineStr">
+      <c r="F3075" s="0" t="inlineStr">
         <is>
           <t>备考HSK6压力大，我尽量容忍自己偶尔想偷懒的心情。</t>
         </is>
       </c>
-      <c r="G3075" t="inlineStr"/>
-      <c r="H3075" t="inlineStr"/>
+      <c r="G3075" s="0" t="inlineStr"/>
+      <c r="H3075" s="0" t="inlineStr"/>
     </row>
     <row r="3076">
-      <c r="A3076" t="inlineStr">
+      <c r="A3076" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3076" t="inlineStr">
+      <c r="B3076" s="0" t="inlineStr">
         <is>
           <t>蹬</t>
         </is>
       </c>
-      <c r="C3076" t="inlineStr">
+      <c r="C3076" s="0" t="inlineStr">
         <is>
           <t>dēng</t>
         </is>
       </c>
-      <c r="D3076" t="inlineStr">
+      <c r="D3076" s="0" t="inlineStr">
         <is>
           <t>用脚用力踩或踏</t>
         </is>
       </c>
-      <c r="E3076" t="inlineStr">
+      <c r="E3076" s="0" t="inlineStr">
         <is>
           <t>đạp (chân)</t>
         </is>
       </c>
-      <c r="F3076" t="inlineStr">
+      <c r="F3076" s="0" t="inlineStr">
         <is>
           <t>每天下班我都骑共享单车回家，上坡时得使劲蹬。</t>
         </is>
       </c>
-      <c r="G3076" t="inlineStr"/>
-      <c r="H3076" t="inlineStr"/>
+      <c r="G3076" s="0" t="inlineStr"/>
+      <c r="H3076" s="0" t="inlineStr"/>
     </row>
     <row r="3077">
-      <c r="A3077" t="inlineStr">
+      <c r="A3077" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3077" t="inlineStr">
+      <c r="B3077" s="0" t="inlineStr">
         <is>
           <t>拳头</t>
         </is>
       </c>
-      <c r="C3077" t="inlineStr">
+      <c r="C3077" s="0" t="inlineStr">
         <is>
           <t>quántou</t>
         </is>
       </c>
-      <c r="D3077" t="inlineStr">
+      <c r="D3077" s="0" t="inlineStr">
         <is>
           <t>手指弯曲合拢握紧的手</t>
         </is>
       </c>
-      <c r="E3077" t="inlineStr">
+      <c r="E3077" s="0" t="inlineStr">
         <is>
           <t>nắm đấm</t>
         </is>
       </c>
-      <c r="F3077" t="inlineStr">
+      <c r="F3077" s="0" t="inlineStr">
         <is>
           <t>教HSK1的“手”字时，我握起拳头给小朋友做示范。</t>
         </is>
       </c>
-      <c r="G3077" t="inlineStr"/>
-      <c r="H3077" t="inlineStr"/>
+      <c r="G3077" s="0" t="inlineStr"/>
+      <c r="H3077" s="0" t="inlineStr"/>
     </row>
     <row r="3078">
-      <c r="A3078" t="inlineStr">
+      <c r="A3078" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3078" t="inlineStr">
+      <c r="B3078" s="0" t="inlineStr">
         <is>
           <t>不时</t>
         </is>
       </c>
-      <c r="C3078" t="inlineStr">
+      <c r="C3078" s="0" t="inlineStr">
         <is>
           <t>bùshí</t>
         </is>
       </c>
-      <c r="D3078" t="inlineStr">
+      <c r="D3078" s="0" t="inlineStr">
         <is>
           <t>时常，一次又一次地（多用于书面）</t>
         </is>
       </c>
-      <c r="E3078" t="inlineStr">
+      <c r="E3078" s="0" t="inlineStr">
         <is>
           <t>thường xuyên, chốc chốc lại</t>
         </is>
       </c>
-      <c r="F3078" t="inlineStr">
+      <c r="F3078" s="0" t="inlineStr">
         <is>
           <t>上中文课时，学生不时举手提问，我很喜欢这种气氛。</t>
         </is>
       </c>
-      <c r="G3078" t="inlineStr"/>
-      <c r="H3078" t="inlineStr"/>
+      <c r="G3078" s="0" t="inlineStr"/>
+      <c r="H3078" s="0" t="inlineStr"/>
     </row>
     <row r="3079">
-      <c r="A3079" t="inlineStr">
+      <c r="A3079" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3079" t="inlineStr">
+      <c r="B3079" s="0" t="inlineStr">
         <is>
           <t>气色</t>
         </is>
       </c>
-      <c r="C3079" t="inlineStr">
+      <c r="C3079" s="0" t="inlineStr">
         <is>
           <t>qìsè</t>
         </is>
       </c>
-      <c r="D3079" t="inlineStr">
+      <c r="D3079" s="0" t="inlineStr">
         <is>
           <t>人脸上表现出来的健康状况</t>
         </is>
       </c>
-      <c r="E3079" t="inlineStr">
+      <c r="E3079" s="0" t="inlineStr">
         <is>
           <t>sắc mặt, thần sắc</t>
         </is>
       </c>
-      <c r="F3079" t="inlineStr">
+      <c r="F3079" s="0" t="inlineStr">
         <is>
           <t>昨晚熬夜背单词，今天同事说我气色不太好。</t>
         </is>
       </c>
-      <c r="G3079" t="inlineStr"/>
-      <c r="H3079" t="inlineStr"/>
+      <c r="G3079" s="0" t="inlineStr"/>
+      <c r="H3079" s="0" t="inlineStr"/>
     </row>
     <row r="3080">
-      <c r="A3080" t="inlineStr">
+      <c r="A3080" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3080" t="inlineStr">
+      <c r="B3080" s="0" t="inlineStr">
         <is>
           <t>轨道</t>
         </is>
       </c>
-      <c r="C3080" t="inlineStr">
+      <c r="C3080" s="0" t="inlineStr">
         <is>
           <t>guǐdào</t>
         </is>
       </c>
-      <c r="D3080" t="inlineStr">
+      <c r="D3080" s="0" t="inlineStr">
         <is>
           <t>火车、地铁行驶的路线；也比喻正常发展的路子</t>
         </is>
       </c>
-      <c r="E3080" t="inlineStr">
+      <c r="E3080" s="0" t="inlineStr">
         <is>
           <t>đường ray; quỹ đạo</t>
         </is>
       </c>
-      <c r="F3080" t="inlineStr">
+      <c r="F3080" s="0" t="inlineStr">
         <is>
           <t>备考计划乱了一阵，现在又回到了正常轨道。</t>
         </is>
       </c>
-      <c r="G3080" t="inlineStr"/>
-      <c r="H3080" t="inlineStr"/>
+      <c r="G3080" s="0" t="inlineStr"/>
+      <c r="H3080" s="0" t="inlineStr"/>
     </row>
     <row r="3081">
-      <c r="A3081" t="inlineStr">
+      <c r="A3081" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3081" t="inlineStr">
+      <c r="B3081" s="0" t="inlineStr">
         <is>
           <t>酒精</t>
         </is>
       </c>
-      <c r="C3081" t="inlineStr">
+      <c r="C3081" s="0" t="inlineStr">
         <is>
           <t>jiǔjīng</t>
         </is>
       </c>
-      <c r="D3081" t="inlineStr">
+      <c r="D3081" s="0" t="inlineStr">
         <is>
           <t>酒里能使人醉的成分</t>
         </is>
       </c>
-      <c r="E3081" t="inlineStr">
+      <c r="E3081" s="0" t="inlineStr">
         <is>
           <t>cồn, chất cồn (trong rượu)</t>
         </is>
       </c>
-      <c r="F3081" t="inlineStr">
+      <c r="F3081" s="0" t="inlineStr">
         <is>
           <t>在中国跟同事聚餐时，我一般不喝酒精含量高的白酒。</t>
         </is>
       </c>
-      <c r="G3081" t="inlineStr"/>
-      <c r="H3081" t="inlineStr"/>
+      <c r="G3081" s="0" t="inlineStr"/>
+      <c r="H3081" s="0" t="inlineStr"/>
     </row>
     <row r="3082">
-      <c r="A3082" t="inlineStr">
+      <c r="A3082" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3082" t="inlineStr">
+      <c r="B3082" s="0" t="inlineStr">
         <is>
           <t>竭尽全力</t>
         </is>
       </c>
-      <c r="C3082" t="inlineStr">
+      <c r="C3082" s="0" t="inlineStr">
         <is>
           <t>jiéjìn quánlì</t>
         </is>
       </c>
-      <c r="D3082" t="inlineStr">
+      <c r="D3082" s="0" t="inlineStr">
         <is>
           <t>用尽全部的力量</t>
         </is>
       </c>
-      <c r="E3082" t="inlineStr">
+      <c r="E3082" s="0" t="inlineStr">
         <is>
           <t>dốc hết sức, gắng hết sức</t>
         </is>
       </c>
-      <c r="F3082" t="inlineStr">
+      <c r="F3082" s="0" t="inlineStr">
         <is>
           <t>为了HSKK拿高分，我竭尽全力每天练口语。</t>
         </is>
       </c>
-      <c r="G3082" t="inlineStr"/>
-      <c r="H3082" t="inlineStr"/>
+      <c r="G3082" s="0" t="inlineStr"/>
+      <c r="H3082" s="0" t="inlineStr"/>
     </row>
     <row r="3083">
-      <c r="A3083" t="inlineStr">
+      <c r="A3083" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3083" t="inlineStr">
+      <c r="B3083" s="0" t="inlineStr">
         <is>
           <t>根源</t>
         </is>
       </c>
-      <c r="C3083" t="inlineStr">
+      <c r="C3083" s="0" t="inlineStr">
         <is>
           <t>gēnyuán</t>
         </is>
       </c>
-      <c r="D3083" t="inlineStr">
+      <c r="D3083" s="0" t="inlineStr">
         <is>
           <t>事情产生的根本原因</t>
         </is>
       </c>
-      <c r="E3083" t="inlineStr">
+      <c r="E3083" s="0" t="inlineStr">
         <is>
           <t>nguồn gốc, căn nguyên</t>
         </is>
       </c>
-      <c r="F3083" t="inlineStr">
+      <c r="F3083" s="0" t="inlineStr">
         <is>
           <t>我发现自己听力差的根源是平时听得太少。</t>
         </is>
       </c>
-      <c r="G3083" t="inlineStr"/>
-      <c r="H3083" t="inlineStr"/>
+      <c r="G3083" s="0" t="inlineStr"/>
+      <c r="H3083" s="0" t="inlineStr"/>
     </row>
     <row r="3084">
-      <c r="A3084" t="inlineStr">
+      <c r="A3084" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3084" t="inlineStr">
+      <c r="B3084" s="0" t="inlineStr">
         <is>
           <t>对付</t>
         </is>
       </c>
-      <c r="C3084" t="inlineStr">
+      <c r="C3084" s="0" t="inlineStr">
         <is>
           <t>duìfu</t>
         </is>
       </c>
-      <c r="D3084" t="inlineStr">
+      <c r="D3084" s="0" t="inlineStr">
         <is>
           <t>想办法处理人或事情</t>
         </is>
       </c>
-      <c r="E3084" t="inlineStr">
+      <c r="E3084" s="0" t="inlineStr">
         <is>
           <t>đối phó, ứng phó</t>
         </is>
       </c>
-      <c r="F3084" t="inlineStr">
+      <c r="F3084" s="0" t="inlineStr">
         <is>
           <t>遇到不会做的HSK6阅读题，我有一套自己对付的办法。</t>
         </is>
       </c>
-      <c r="G3084" t="inlineStr"/>
-      <c r="H3084" t="inlineStr"/>
+      <c r="G3084" s="0" t="inlineStr"/>
+      <c r="H3084" s="0" t="inlineStr"/>
     </row>
     <row r="3085">
-      <c r="A3085" t="inlineStr">
+      <c r="A3085" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3085" t="inlineStr">
+      <c r="B3085" s="0" t="inlineStr">
         <is>
           <t>纠正</t>
         </is>
       </c>
-      <c r="C3085" t="inlineStr">
+      <c r="C3085" s="0" t="inlineStr">
         <is>
           <t>jiūzhèng</t>
         </is>
       </c>
-      <c r="D3085" t="inlineStr">
+      <c r="D3085" s="0" t="inlineStr">
         <is>
           <t>改正错误</t>
         </is>
       </c>
-      <c r="E3085" t="inlineStr">
+      <c r="E3085" s="0" t="inlineStr">
         <is>
           <t>sửa chữa, uốn nắn</t>
         </is>
       </c>
-      <c r="F3085" t="inlineStr">
+      <c r="F3085" s="0" t="inlineStr">
         <is>
           <t>上课时我会及时纠正学生的发音错误。</t>
         </is>
       </c>
-      <c r="G3085" t="inlineStr"/>
-      <c r="H3085" t="inlineStr"/>
+      <c r="G3085" s="0" t="inlineStr"/>
+      <c r="H3085" s="0" t="inlineStr"/>
     </row>
     <row r="3086">
-      <c r="A3086" t="inlineStr">
+      <c r="A3086" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3086" t="inlineStr">
+      <c r="B3086" s="0" t="inlineStr">
         <is>
           <t>糟蹋</t>
         </is>
       </c>
-      <c r="C3086" t="inlineStr">
+      <c r="C3086" s="0" t="inlineStr">
         <is>
           <t>zāotà</t>
         </is>
       </c>
-      <c r="D3086" t="inlineStr">
+      <c r="D3086" s="0" t="inlineStr">
         <is>
           <t>浪费或随意损坏（东西、身体等）</t>
         </is>
       </c>
-      <c r="E3086" t="inlineStr">
+      <c r="E3086" s="0" t="inlineStr">
         <is>
           <t>phí phạm, tàn phá</t>
         </is>
       </c>
-      <c r="F3086" t="inlineStr">
+      <c r="F3086" s="0" t="inlineStr">
         <is>
           <t>经常熬夜其实就是在糟蹋自己的身体。</t>
         </is>
       </c>
-      <c r="G3086" t="inlineStr"/>
-      <c r="H3086" t="inlineStr"/>
+      <c r="G3086" s="0" t="inlineStr"/>
+      <c r="H3086" s="0" t="inlineStr"/>
     </row>
     <row r="3087">
-      <c r="A3087" t="inlineStr">
+      <c r="A3087" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3087" t="inlineStr">
+      <c r="B3087" s="0" t="inlineStr">
         <is>
           <t>迫害</t>
         </is>
       </c>
-      <c r="C3087" t="inlineStr">
+      <c r="C3087" s="0" t="inlineStr">
         <is>
           <t>pòhài</t>
         </is>
       </c>
-      <c r="D3087" t="inlineStr">
+      <c r="D3087" s="0" t="inlineStr">
         <is>
           <t>用暴力或权势残酷地压迫、伤害</t>
         </is>
       </c>
-      <c r="E3087" t="inlineStr">
+      <c r="E3087" s="0" t="inlineStr">
         <is>
           <t>bức hại</t>
         </is>
       </c>
-      <c r="F3087" t="inlineStr">
+      <c r="F3087" s="0" t="inlineStr">
         <is>
           <t>这部纪录片讲的是战争年代很多人遭到迫害的故事。</t>
         </is>
       </c>
-      <c r="G3087" t="inlineStr"/>
-      <c r="H3087" t="inlineStr"/>
+      <c r="G3087" s="0" t="inlineStr"/>
+      <c r="H3087" s="0" t="inlineStr"/>
     </row>
     <row r="3088">
-      <c r="A3088" t="inlineStr">
+      <c r="A3088" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3088" t="inlineStr">
+      <c r="B3088" s="0" t="inlineStr">
         <is>
           <t>毁灭</t>
         </is>
       </c>
-      <c r="C3088" t="inlineStr">
+      <c r="C3088" s="0" t="inlineStr">
         <is>
           <t>huǐmiè</t>
         </is>
       </c>
-      <c r="D3088" t="inlineStr">
+      <c r="D3088" s="0" t="inlineStr">
         <is>
           <t>彻底摧毁，使不再存在</t>
         </is>
       </c>
-      <c r="E3088" t="inlineStr">
+      <c r="E3088" s="0" t="inlineStr">
         <is>
           <t>hủy diệt, phá hủy</t>
         </is>
       </c>
-      <c r="F3088" t="inlineStr">
+      <c r="F3088" s="0" t="inlineStr">
         <is>
           <t>坏习惯会一点一点毁灭一个人的健康。</t>
         </is>
       </c>
-      <c r="G3088" t="inlineStr"/>
-      <c r="H3088" t="inlineStr"/>
+      <c r="G3088" s="0" t="inlineStr"/>
+      <c r="H3088" s="0" t="inlineStr"/>
     </row>
     <row r="3089">
-      <c r="A3089" t="inlineStr">
+      <c r="A3089" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3089" t="inlineStr">
+      <c r="B3089" s="0" t="inlineStr">
         <is>
           <t>惯例</t>
         </is>
       </c>
-      <c r="C3089" t="inlineStr">
+      <c r="C3089" s="0" t="inlineStr">
         <is>
           <t>guànlì</t>
         </is>
       </c>
-      <c r="D3089" t="inlineStr">
+      <c r="D3089" s="0" t="inlineStr">
         <is>
           <t>一向的做法，习惯上的规矩</t>
         </is>
       </c>
-      <c r="E3089" t="inlineStr">
+      <c r="E3089" s="0" t="inlineStr">
         <is>
           <t>thông lệ, lệ thường</t>
         </is>
       </c>
-      <c r="F3089" t="inlineStr">
+      <c r="F3089" s="0" t="inlineStr">
         <is>
           <t>按照惯例，我每天早上先复习昨天学的生词。</t>
         </is>
       </c>
-      <c r="G3089" t="inlineStr"/>
-      <c r="H3089" t="inlineStr"/>
+      <c r="G3089" s="0" t="inlineStr"/>
+      <c r="H3089" s="0" t="inlineStr"/>
     </row>
     <row r="3090">
-      <c r="A3090" t="inlineStr">
+      <c r="A3090" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3090" t="inlineStr">
+      <c r="B3090" s="0" t="inlineStr">
         <is>
           <t>顽固</t>
         </is>
       </c>
-      <c r="C3090" t="inlineStr">
+      <c r="C3090" s="0" t="inlineStr">
         <is>
           <t>wángù</t>
         </is>
       </c>
-      <c r="D3090" t="inlineStr">
+      <c r="D3090" s="0" t="inlineStr">
         <is>
           <t>思想保守、不肯改变；（病）难治</t>
         </is>
       </c>
-      <c r="E3090" t="inlineStr">
+      <c r="E3090" s="0" t="inlineStr">
         <is>
           <t>ngoan cố; dai dẳng (bệnh)</t>
         </is>
       </c>
-      <c r="F3090" t="inlineStr">
+      <c r="F3090" s="0" t="inlineStr">
         <is>
           <t>我有个顽固的坏习惯，就是睡前老爱看手机。</t>
         </is>
       </c>
-      <c r="G3090" t="inlineStr"/>
-      <c r="H3090" t="inlineStr"/>
+      <c r="G3090" s="0" t="inlineStr"/>
+      <c r="H3090" s="0" t="inlineStr"/>
     </row>
     <row r="3091">
-      <c r="A3091" t="inlineStr">
+      <c r="A3091" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3091" t="inlineStr">
+      <c r="B3091" s="0" t="inlineStr">
         <is>
           <t>奢侈</t>
         </is>
       </c>
-      <c r="C3091" t="inlineStr">
+      <c r="C3091" s="0" t="inlineStr">
         <is>
           <t>shēchǐ</t>
         </is>
       </c>
-      <c r="D3091" t="inlineStr">
+      <c r="D3091" s="0" t="inlineStr">
         <is>
           <t>花很多钱财追求享受</t>
         </is>
       </c>
-      <c r="E3091" t="inlineStr">
+      <c r="E3091" s="0" t="inlineStr">
         <is>
           <t>xa xỉ, xa hoa</t>
         </is>
       </c>
-      <c r="F3091" t="inlineStr">
+      <c r="F3091" s="0" t="inlineStr">
         <is>
           <t>对上班族来说，能睡到自然醒简直是一种奢侈。</t>
         </is>
       </c>
-      <c r="G3091" t="inlineStr"/>
-      <c r="H3091" t="inlineStr"/>
+      <c r="G3091" s="0" t="inlineStr"/>
+      <c r="H3091" s="0" t="inlineStr"/>
     </row>
     <row r="3092">
-      <c r="A3092" t="inlineStr">
+      <c r="A3092" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3092" t="inlineStr">
+      <c r="B3092" s="0" t="inlineStr">
         <is>
           <t>指数</t>
         </is>
       </c>
-      <c r="C3092" t="inlineStr">
+      <c r="C3092" s="0" t="inlineStr">
         <is>
           <t>zhǐshù</t>
         </is>
       </c>
-      <c r="D3092" t="inlineStr">
+      <c r="D3092" s="0" t="inlineStr">
         <is>
           <t>用来表示某种情况变动的数值</t>
         </is>
       </c>
-      <c r="E3092" t="inlineStr">
+      <c r="E3092" s="0" t="inlineStr">
         <is>
           <t>chỉ số</t>
         </is>
       </c>
-      <c r="F3092" t="inlineStr">
+      <c r="F3092" s="0" t="inlineStr">
         <is>
           <t>中国发布的睡眠指数显示很多人睡眠质量不高。</t>
         </is>
       </c>
-      <c r="G3092" t="inlineStr"/>
-      <c r="H3092" t="inlineStr"/>
+      <c r="G3092" s="0" t="inlineStr"/>
+      <c r="H3092" s="0" t="inlineStr"/>
     </row>
     <row r="3093">
-      <c r="A3093" t="inlineStr">
+      <c r="A3093" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3093" t="inlineStr">
+      <c r="B3093" s="0" t="inlineStr">
         <is>
           <t>居民</t>
         </is>
       </c>
-      <c r="C3093" t="inlineStr">
+      <c r="C3093" s="0" t="inlineStr">
         <is>
           <t>jūmín</t>
         </is>
       </c>
-      <c r="D3093" t="inlineStr">
+      <c r="D3093" s="0" t="inlineStr">
         <is>
           <t>住在某个地方的人</t>
         </is>
       </c>
-      <c r="E3093" t="inlineStr">
+      <c r="E3093" s="0" t="inlineStr">
         <is>
           <t>cư dân, dân cư</t>
         </is>
       </c>
-      <c r="F3093" t="inlineStr">
+      <c r="F3093" s="0" t="inlineStr">
         <is>
           <t>我住的小区居民大多是年轻上班族。</t>
         </is>
       </c>
-      <c r="G3093" t="inlineStr"/>
-      <c r="H3093" t="inlineStr"/>
+      <c r="G3093" s="0" t="inlineStr"/>
+      <c r="H3093" s="0" t="inlineStr"/>
     </row>
     <row r="3094">
-      <c r="A3094" t="inlineStr">
+      <c r="A3094" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3094" t="inlineStr">
+      <c r="B3094" s="0" t="inlineStr">
         <is>
           <t>当前</t>
         </is>
       </c>
-      <c r="C3094" t="inlineStr">
+      <c r="C3094" s="0" t="inlineStr">
         <is>
           <t>dāngqián</t>
         </is>
       </c>
-      <c r="D3094" t="inlineStr">
+      <c r="D3094" s="0" t="inlineStr">
         <is>
           <t>目前，现在这个时候</t>
         </is>
       </c>
-      <c r="E3094" t="inlineStr">
+      <c r="E3094" s="0" t="inlineStr">
         <is>
           <t>hiện nay, trước mắt</t>
         </is>
       </c>
-      <c r="F3094" t="inlineStr">
+      <c r="F3094" s="0" t="inlineStr">
         <is>
           <t>当前我最重要的任务就是顺利通过HSK6。</t>
         </is>
       </c>
-      <c r="G3094" t="inlineStr"/>
-      <c r="H3094" t="inlineStr"/>
+      <c r="G3094" s="0" t="inlineStr"/>
+      <c r="H3094" s="0" t="inlineStr"/>
     </row>
     <row r="3095">
-      <c r="A3095" t="inlineStr">
+      <c r="A3095" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3095" t="inlineStr">
+      <c r="B3095" s="0" t="inlineStr">
         <is>
           <t>扰乱</t>
         </is>
       </c>
-      <c r="C3095" t="inlineStr">
+      <c r="C3095" s="0" t="inlineStr">
         <is>
           <t>rǎoluàn</t>
         </is>
       </c>
-      <c r="D3095" t="inlineStr">
+      <c r="D3095" s="0" t="inlineStr">
         <is>
           <t>打乱，使变得混乱</t>
         </is>
       </c>
-      <c r="E3095" t="inlineStr">
+      <c r="E3095" s="0" t="inlineStr">
         <is>
           <t>quấy nhiễu, làm rối loạn</t>
         </is>
       </c>
-      <c r="F3095" t="inlineStr">
+      <c r="F3095" s="0" t="inlineStr">
         <is>
           <t>睡前刷手机会扰乱我的作息。</t>
         </is>
       </c>
-      <c r="G3095" t="inlineStr"/>
-      <c r="H3095" t="inlineStr"/>
+      <c r="G3095" s="0" t="inlineStr"/>
+      <c r="H3095" s="0" t="inlineStr"/>
     </row>
     <row r="3096">
-      <c r="A3096" t="inlineStr">
+      <c r="A3096" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3096" t="inlineStr">
+      <c r="B3096" s="0" t="inlineStr">
         <is>
           <t>折腾</t>
         </is>
       </c>
-      <c r="C3096" t="inlineStr">
+      <c r="C3096" s="0" t="inlineStr">
         <is>
           <t>zhēteng</t>
         </is>
       </c>
-      <c r="D3096" t="inlineStr">
+      <c r="D3096" s="0" t="inlineStr">
         <is>
           <t>反复做某事；使身心不得安宁</t>
         </is>
       </c>
-      <c r="E3096" t="inlineStr">
+      <c r="E3096" s="0" t="inlineStr">
         <is>
           <t>hành hạ; trằn trọc, quần quật</t>
         </is>
       </c>
-      <c r="F3096" t="inlineStr">
+      <c r="F3096" s="0" t="inlineStr">
         <is>
           <t>昨晚失眠，我在床上翻来覆去折腾了大半夜。</t>
         </is>
       </c>
-      <c r="G3096" t="inlineStr"/>
-      <c r="H3096" t="inlineStr"/>
+      <c r="G3096" s="0" t="inlineStr"/>
+      <c r="H3096" s="0" t="inlineStr"/>
     </row>
     <row r="3097">
-      <c r="A3097" t="inlineStr">
+      <c r="A3097" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3097" t="inlineStr">
+      <c r="B3097" s="0" t="inlineStr">
         <is>
           <t>逆行</t>
         </is>
       </c>
-      <c r="C3097" t="inlineStr">
+      <c r="C3097" s="0" t="inlineStr">
         <is>
           <t>nìxíng</t>
         </is>
       </c>
-      <c r="D3097" t="inlineStr">
+      <c r="D3097" s="0" t="inlineStr">
         <is>
           <t>朝着跟规定相反的方向行进</t>
         </is>
       </c>
-      <c r="E3097" t="inlineStr">
+      <c r="E3097" s="0" t="inlineStr">
         <is>
           <t>đi ngược chiều</t>
         </is>
       </c>
-      <c r="F3097" t="inlineStr">
+      <c r="F3097" s="0" t="inlineStr">
         <is>
           <t>在中国骑车千万不能逆行，太危险了。</t>
         </is>
       </c>
-      <c r="G3097" t="inlineStr"/>
-      <c r="H3097" t="inlineStr"/>
+      <c r="G3097" s="0" t="inlineStr"/>
+      <c r="H3097" s="0" t="inlineStr"/>
     </row>
     <row r="3098">
-      <c r="A3098" t="inlineStr">
+      <c r="A3098" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3098" t="inlineStr">
+      <c r="B3098" s="0" t="inlineStr">
         <is>
           <t>茫然</t>
         </is>
       </c>
-      <c r="C3098" t="inlineStr">
+      <c r="C3098" s="0" t="inlineStr">
         <is>
           <t>mángrán</t>
         </is>
       </c>
-      <c r="D3098" t="inlineStr">
+      <c r="D3098" s="0" t="inlineStr">
         <is>
           <t>完全不知道，心里没有主意的样子</t>
         </is>
       </c>
-      <c r="E3098" t="inlineStr">
+      <c r="E3098" s="0" t="inlineStr">
         <is>
           <t>mờ mịt, ngơ ngác</t>
         </is>
       </c>
-      <c r="F3098" t="inlineStr">
+      <c r="F3098" s="0" t="inlineStr">
         <is>
           <t>刚开始学HSK6语法时，我常常一脸茫然。</t>
         </is>
       </c>
-      <c r="G3098" t="inlineStr"/>
-      <c r="H3098" t="inlineStr"/>
+      <c r="G3098" s="0" t="inlineStr"/>
+      <c r="H3098" s="0" t="inlineStr"/>
     </row>
     <row r="3099">
-      <c r="A3099" t="inlineStr">
+      <c r="A3099" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3099" t="inlineStr">
+      <c r="B3099" s="0" t="inlineStr">
         <is>
           <t>丢三落四</t>
         </is>
       </c>
-      <c r="C3099" t="inlineStr">
+      <c r="C3099" s="0" t="inlineStr">
         <is>
           <t>diūsān-làsì</t>
         </is>
       </c>
-      <c r="D3099" t="inlineStr">
+      <c r="D3099" s="0" t="inlineStr">
         <is>
           <t>做事马虎，常常有遗漏</t>
         </is>
       </c>
-      <c r="E3099" t="inlineStr">
+      <c r="E3099" s="0" t="inlineStr">
         <is>
           <t>đầu quên đuôi, hay quên</t>
         </is>
       </c>
-      <c r="F3099" t="inlineStr">
+      <c r="F3099" s="0" t="inlineStr">
         <is>
           <t>我记性不好，出门总是丢三落四。</t>
         </is>
       </c>
-      <c r="G3099" t="inlineStr"/>
-      <c r="H3099" t="inlineStr"/>
+      <c r="G3099" s="0" t="inlineStr"/>
+      <c r="H3099" s="0" t="inlineStr"/>
     </row>
     <row r="3100">
-      <c r="A3100" t="inlineStr">
+      <c r="A3100" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3100" t="inlineStr">
+      <c r="B3100" s="0" t="inlineStr">
         <is>
           <t>起伏</t>
         </is>
       </c>
-      <c r="C3100" t="inlineStr">
+      <c r="C3100" s="0" t="inlineStr">
         <is>
           <t>qǐfú</t>
         </is>
       </c>
-      <c r="D3100" t="inlineStr">
+      <c r="D3100" s="0" t="inlineStr">
         <is>
           <t>一起一落；（情绪等）变化不定</t>
         </is>
       </c>
-      <c r="E3100" t="inlineStr">
+      <c r="E3100" s="0" t="inlineStr">
         <is>
           <t>nhấp nhô; thăng trầm, biến động</t>
         </is>
       </c>
-      <c r="F3100" t="inlineStr">
+      <c r="F3100" s="0" t="inlineStr">
         <is>
           <t>备考那段时间我情绪起伏很大，一会儿信心满满，一会儿又想放弃。</t>
         </is>
       </c>
-      <c r="G3100" t="inlineStr"/>
-      <c r="H3100" t="inlineStr"/>
+      <c r="G3100" s="0" t="inlineStr"/>
+      <c r="H3100" s="0" t="inlineStr"/>
     </row>
     <row r="3101">
-      <c r="A3101" t="inlineStr">
+      <c r="A3101" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3101" t="inlineStr">
+      <c r="B3101" s="0" t="inlineStr">
         <is>
           <t>发呆</t>
         </is>
       </c>
-      <c r="C3101" t="inlineStr">
+      <c r="C3101" s="0" t="inlineStr">
         <is>
           <t>fādāi</t>
         </is>
       </c>
-      <c r="D3101" t="inlineStr">
+      <c r="D3101" s="0" t="inlineStr">
         <is>
           <t>因为出神而呆呆地不动</t>
         </is>
       </c>
-      <c r="E3101" t="inlineStr">
+      <c r="E3101" s="0" t="inlineStr">
         <is>
           <t>thẫn thờ, ngẩn người ra</t>
         </is>
       </c>
-      <c r="F3101" t="inlineStr">
+      <c r="F3101" s="0" t="inlineStr">
         <is>
           <t>单词背累了，我常常对着窗外发呆。</t>
         </is>
       </c>
-      <c r="G3101" t="inlineStr"/>
-      <c r="H3101" t="inlineStr"/>
+      <c r="G3101" s="0" t="inlineStr"/>
+      <c r="H3101" s="0" t="inlineStr"/>
     </row>
     <row r="3102">
-      <c r="A3102" t="inlineStr">
+      <c r="A3102" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3102" t="inlineStr">
+      <c r="B3102" s="0" t="inlineStr">
         <is>
           <t>记性</t>
         </is>
       </c>
-      <c r="C3102" t="inlineStr">
+      <c r="C3102" s="0" t="inlineStr">
         <is>
           <t>jìxing</t>
         </is>
       </c>
-      <c r="D3102" t="inlineStr">
+      <c r="D3102" s="0" t="inlineStr">
         <is>
           <t>记忆的能力</t>
         </is>
       </c>
-      <c r="E3102" t="inlineStr">
+      <c r="E3102" s="0" t="inlineStr">
         <is>
           <t>trí nhớ</t>
         </is>
       </c>
-      <c r="F3102" t="inlineStr">
+      <c r="F3102" s="0" t="inlineStr">
         <is>
           <t>睡不好觉，我的记性明显变差了。</t>
         </is>
       </c>
-      <c r="G3102" t="inlineStr"/>
-      <c r="H3102" t="inlineStr"/>
+      <c r="G3102" s="0" t="inlineStr"/>
+      <c r="H3102" s="0" t="inlineStr"/>
     </row>
     <row r="3103">
-      <c r="A3103" t="inlineStr">
+      <c r="A3103" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3103" t="inlineStr">
+      <c r="B3103" s="0" t="inlineStr">
         <is>
           <t>摧残</t>
         </is>
       </c>
-      <c r="C3103" t="inlineStr">
+      <c r="C3103" s="0" t="inlineStr">
         <is>
           <t>cuīcán</t>
         </is>
       </c>
-      <c r="D3103" t="inlineStr">
+      <c r="D3103" s="0" t="inlineStr">
         <is>
           <t>使受到严重的损害</t>
         </is>
       </c>
-      <c r="E3103" t="inlineStr">
+      <c r="E3103" s="0" t="inlineStr">
         <is>
           <t>tàn phá, dày vò</t>
         </is>
       </c>
-      <c r="F3103" t="inlineStr">
+      <c r="F3103" s="0" t="inlineStr">
         <is>
           <t>长期熬夜会摧残身体健康。</t>
         </is>
       </c>
-      <c r="G3103" t="inlineStr"/>
-      <c r="H3103" t="inlineStr"/>
+      <c r="G3103" s="0" t="inlineStr"/>
+      <c r="H3103" s="0" t="inlineStr"/>
     </row>
     <row r="3104">
-      <c r="A3104" t="inlineStr">
+      <c r="A3104" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3104" t="inlineStr">
+      <c r="B3104" s="0" t="inlineStr">
         <is>
           <t>普及</t>
         </is>
       </c>
-      <c r="C3104" t="inlineStr">
+      <c r="C3104" s="0" t="inlineStr">
         <is>
           <t>pǔjí</t>
         </is>
       </c>
-      <c r="D3104" t="inlineStr">
+      <c r="D3104" s="0" t="inlineStr">
         <is>
           <t>普遍推广，使大家都有或都懂</t>
         </is>
       </c>
-      <c r="E3104" t="inlineStr">
+      <c r="E3104" s="0" t="inlineStr">
         <is>
           <t>phổ cập, phổ biến</t>
         </is>
       </c>
-      <c r="F3104" t="inlineStr">
+      <c r="F3104" s="0" t="inlineStr">
         <is>
           <t>智能手机普及以后，很多人睡前都离不开它。</t>
         </is>
       </c>
-      <c r="G3104" t="inlineStr"/>
-      <c r="H3104" t="inlineStr"/>
+      <c r="G3104" s="0" t="inlineStr"/>
+      <c r="H3104" s="0" t="inlineStr"/>
     </row>
     <row r="3105">
-      <c r="A3105" t="inlineStr">
+      <c r="A3105" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3105" t="inlineStr">
+      <c r="B3105" s="0" t="inlineStr">
         <is>
           <t>盛行</t>
         </is>
       </c>
-      <c r="C3105" t="inlineStr">
+      <c r="C3105" s="0" t="inlineStr">
         <is>
           <t>shèngxíng</t>
         </is>
       </c>
-      <c r="D3105" t="inlineStr">
+      <c r="D3105" s="0" t="inlineStr">
         <is>
           <t>广泛地流行</t>
         </is>
       </c>
-      <c r="E3105" t="inlineStr">
+      <c r="E3105" s="0" t="inlineStr">
         <is>
           <t>thịnh hành, phổ biến rộng</t>
         </is>
       </c>
-      <c r="F3105" t="inlineStr">
+      <c r="F3105" s="0" t="inlineStr">
         <is>
           <t>现在睡前上网的习惯很盛行。</t>
         </is>
       </c>
-      <c r="G3105" t="inlineStr"/>
-      <c r="H3105" t="inlineStr"/>
+      <c r="G3105" s="0" t="inlineStr"/>
+      <c r="H3105" s="0" t="inlineStr"/>
     </row>
     <row r="3106">
-      <c r="A3106" t="inlineStr">
+      <c r="A3106" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3106" t="inlineStr">
+      <c r="B3106" s="0" t="inlineStr">
         <is>
           <t>细胞</t>
         </is>
       </c>
-      <c r="C3106" t="inlineStr">
+      <c r="C3106" s="0" t="inlineStr">
         <is>
           <t>xìbāo</t>
         </is>
       </c>
-      <c r="D3106" t="inlineStr">
+      <c r="D3106" s="0" t="inlineStr">
         <is>
           <t>生物体结构和功能的基本单位</t>
         </is>
       </c>
-      <c r="E3106" t="inlineStr">
+      <c r="E3106" s="0" t="inlineStr">
         <is>
           <t>tế bào</t>
         </is>
       </c>
-      <c r="F3106" t="inlineStr">
+      <c r="F3106" s="0" t="inlineStr">
         <is>
           <t>熬夜会影响人体细胞的正常活动。</t>
         </is>
       </c>
-      <c r="G3106" t="inlineStr"/>
-      <c r="H3106" t="inlineStr"/>
+      <c r="G3106" s="0" t="inlineStr"/>
+      <c r="H3106" s="0" t="inlineStr"/>
     </row>
     <row r="3107">
-      <c r="A3107" t="inlineStr">
+      <c r="A3107" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3107" t="inlineStr">
+      <c r="B3107" s="0" t="inlineStr">
         <is>
           <t>肿瘤</t>
         </is>
       </c>
-      <c r="C3107" t="inlineStr">
+      <c r="C3107" s="0" t="inlineStr">
         <is>
           <t>zhǒngliú</t>
         </is>
       </c>
-      <c r="D3107" t="inlineStr">
+      <c r="D3107" s="0" t="inlineStr">
         <is>
           <t>身体里不正常增生的组织块</t>
         </is>
       </c>
-      <c r="E3107" t="inlineStr">
+      <c r="E3107" s="0" t="inlineStr">
         <is>
           <t>khối u, u bướu</t>
         </is>
       </c>
-      <c r="F3107" t="inlineStr">
+      <c r="F3107" s="0" t="inlineStr">
         <is>
           <t>医生说定期体检能早点发现肿瘤。</t>
         </is>
       </c>
-      <c r="G3107" t="inlineStr"/>
-      <c r="H3107" t="inlineStr"/>
+      <c r="G3107" s="0" t="inlineStr"/>
+      <c r="H3107" s="0" t="inlineStr"/>
     </row>
     <row r="3108">
-      <c r="A3108" t="inlineStr">
+      <c r="A3108" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3108" t="inlineStr">
+      <c r="B3108" s="0" t="inlineStr">
         <is>
           <t>癌症</t>
         </is>
       </c>
-      <c r="C3108" t="inlineStr">
+      <c r="C3108" s="0" t="inlineStr">
         <is>
           <t>áizhèng</t>
         </is>
       </c>
-      <c r="D3108" t="inlineStr">
+      <c r="D3108" s="0" t="inlineStr">
         <is>
           <t>由恶性肿瘤引起的疾病</t>
         </is>
       </c>
-      <c r="E3108" t="inlineStr">
+      <c r="E3108" s="0" t="inlineStr">
         <is>
           <t>bệnh ung thư</t>
         </is>
       </c>
-      <c r="F3108" t="inlineStr">
+      <c r="F3108" s="0" t="inlineStr">
         <is>
           <t>不良的生活习惯可能会增加得癌症的风险。</t>
         </is>
       </c>
-      <c r="G3108" t="inlineStr"/>
-      <c r="H3108" t="inlineStr"/>
+      <c r="G3108" s="0" t="inlineStr"/>
+      <c r="H3108" s="0" t="inlineStr"/>
     </row>
     <row r="3109">
-      <c r="A3109" t="inlineStr">
+      <c r="A3109" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3109" t="inlineStr">
+      <c r="B3109" s="0" t="inlineStr">
         <is>
           <t>呼吁</t>
         </is>
       </c>
-      <c r="C3109" t="inlineStr">
+      <c r="C3109" s="0" t="inlineStr">
         <is>
           <t>hūyù</t>
         </is>
       </c>
-      <c r="D3109" t="inlineStr">
+      <c r="D3109" s="0" t="inlineStr">
         <is>
           <t>大声向社会请求支持或帮助</t>
         </is>
       </c>
-      <c r="E3109" t="inlineStr">
+      <c r="E3109" s="0" t="inlineStr">
         <is>
           <t>kêu gọi</t>
         </is>
       </c>
-      <c r="F3109" t="inlineStr">
+      <c r="F3109" s="0" t="inlineStr">
         <is>
           <t>医生呼吁大家不要经常熬夜。</t>
         </is>
       </c>
-      <c r="G3109" t="inlineStr"/>
-      <c r="H3109" t="inlineStr"/>
+      <c r="G3109" s="0" t="inlineStr"/>
+      <c r="H3109" s="0" t="inlineStr"/>
     </row>
     <row r="3110">
-      <c r="A3110" t="inlineStr">
+      <c r="A3110" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3110" t="inlineStr">
+      <c r="B3110" s="0" t="inlineStr">
         <is>
           <t>无动于衷</t>
         </is>
       </c>
-      <c r="C3110" t="inlineStr">
+      <c r="C3110" s="0" t="inlineStr">
         <is>
           <t>wúdòngyúzhōng</t>
         </is>
       </c>
-      <c r="D3110" t="inlineStr">
+      <c r="D3110" s="0" t="inlineStr">
         <is>
           <t>心里一点儿也不受触动，毫不在意</t>
         </is>
       </c>
-      <c r="E3110" t="inlineStr">
+      <c r="E3110" s="0" t="inlineStr">
         <is>
           <t>thờ ơ, dửng dưng</t>
         </is>
       </c>
-      <c r="F3110" t="inlineStr">
+      <c r="F3110" s="0" t="inlineStr">
         <is>
           <t>对自己的坏习惯不能无动于衷，要及时改正。</t>
         </is>
       </c>
-      <c r="G3110" t="inlineStr"/>
-      <c r="H3110" t="inlineStr"/>
+      <c r="G3110" s="0" t="inlineStr"/>
+      <c r="H3110" s="0" t="inlineStr"/>
     </row>
     <row r="3111">
-      <c r="A3111" t="inlineStr">
+      <c r="A3111" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3111" t="inlineStr">
+      <c r="B3111" s="0" t="inlineStr">
         <is>
           <t>过瘾</t>
         </is>
       </c>
-      <c r="C3111" t="inlineStr">
+      <c r="C3111" s="0" t="inlineStr">
         <is>
           <t>guòyǐn</t>
         </is>
       </c>
-      <c r="D3111" t="inlineStr">
+      <c r="D3111" s="0" t="inlineStr">
         <is>
           <t>满足了某种爱好，觉得很痛快</t>
         </is>
       </c>
-      <c r="E3111" t="inlineStr">
+      <c r="E3111" s="0" t="inlineStr">
         <is>
           <t>đã, thỏa mãn (sở thích)</t>
         </is>
       </c>
-      <c r="F3111" t="inlineStr">
+      <c r="F3111" s="0" t="inlineStr">
         <is>
           <t>周末追一整天中文剧，看得特别过瘾。</t>
         </is>
       </c>
-      <c r="G3111" t="inlineStr"/>
-      <c r="H3111" t="inlineStr"/>
+      <c r="G3111" s="0" t="inlineStr"/>
+      <c r="H3111" s="0" t="inlineStr"/>
     </row>
     <row r="3112">
-      <c r="A3112" t="inlineStr">
+      <c r="A3112" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3112" t="inlineStr">
+      <c r="B3112" s="0" t="inlineStr">
         <is>
           <t>分泌</t>
         </is>
       </c>
-      <c r="C3112" t="inlineStr">
+      <c r="C3112" s="0" t="inlineStr">
         <is>
           <t>fēnmì</t>
         </is>
       </c>
-      <c r="D3112" t="inlineStr">
+      <c r="D3112" s="0" t="inlineStr">
         <is>
           <t>生物体产生并排出某种物质</t>
         </is>
       </c>
-      <c r="E3112" t="inlineStr">
+      <c r="E3112" s="0" t="inlineStr">
         <is>
           <t>tiết ra, bài tiết</t>
         </is>
       </c>
-      <c r="F3112" t="inlineStr">
+      <c r="F3112" s="0" t="inlineStr">
         <is>
           <t>光污染会影响人体褪黑素的分泌。</t>
         </is>
       </c>
-      <c r="G3112" t="inlineStr"/>
-      <c r="H3112" t="inlineStr"/>
+      <c r="G3112" s="0" t="inlineStr"/>
+      <c r="H3112" s="0" t="inlineStr"/>
     </row>
     <row r="3113">
-      <c r="A3113" t="inlineStr">
+      <c r="A3113" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3113" t="inlineStr">
+      <c r="B3113" s="0" t="inlineStr">
         <is>
           <t>职能</t>
         </is>
       </c>
-      <c r="C3113" t="inlineStr">
+      <c r="C3113" s="0" t="inlineStr">
         <is>
           <t>zhínéng</t>
         </is>
       </c>
-      <c r="D3113" t="inlineStr">
+      <c r="D3113" s="0" t="inlineStr">
         <is>
           <t>事物或机构应有的功能、作用</t>
         </is>
       </c>
-      <c r="E3113" t="inlineStr">
+      <c r="E3113" s="0" t="inlineStr">
         <is>
           <t>chức năng</t>
         </is>
       </c>
-      <c r="F3113" t="inlineStr">
+      <c r="F3113" s="0" t="inlineStr">
         <is>
           <t>褪黑素的一个重要职能是帮助睡眠。</t>
         </is>
       </c>
-      <c r="G3113" t="inlineStr"/>
-      <c r="H3113" t="inlineStr"/>
+      <c r="G3113" s="0" t="inlineStr"/>
+      <c r="H3113" s="0" t="inlineStr"/>
     </row>
     <row r="3114">
-      <c r="A3114" t="inlineStr">
+      <c r="A3114" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3114" t="inlineStr">
+      <c r="B3114" s="0" t="inlineStr">
         <is>
           <t>衰老</t>
         </is>
       </c>
-      <c r="C3114" t="inlineStr">
+      <c r="C3114" s="0" t="inlineStr">
         <is>
           <t>shuāilǎo</t>
         </is>
       </c>
-      <c r="D3114" t="inlineStr">
+      <c r="D3114" s="0" t="inlineStr">
         <is>
           <t>身体机能因年老而衰退</t>
         </is>
       </c>
-      <c r="E3114" t="inlineStr">
+      <c r="E3114" s="0" t="inlineStr">
         <is>
           <t>già đi, lão hóa</t>
         </is>
       </c>
-      <c r="F3114" t="inlineStr">
+      <c r="F3114" s="0" t="inlineStr">
         <is>
           <t>睡眠不足会让人加速衰老。</t>
         </is>
       </c>
-      <c r="G3114" t="inlineStr"/>
-      <c r="H3114" t="inlineStr"/>
+      <c r="G3114" s="0" t="inlineStr"/>
+      <c r="H3114" s="0" t="inlineStr"/>
     </row>
     <row r="3115">
-      <c r="A3115" t="inlineStr">
+      <c r="A3115" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3115" t="inlineStr">
+      <c r="B3115" s="0" t="inlineStr">
         <is>
           <t>调剂</t>
         </is>
       </c>
-      <c r="C3115" t="inlineStr">
+      <c r="C3115" s="0" t="inlineStr">
         <is>
           <t>tiáojì</t>
         </is>
       </c>
-      <c r="D3115" t="inlineStr">
+      <c r="D3115" s="0" t="inlineStr">
         <is>
           <t>调整使合适；调节</t>
         </is>
       </c>
-      <c r="E3115" t="inlineStr">
+      <c r="E3115" s="0" t="inlineStr">
         <is>
           <t>điều tiết, điều hòa</t>
         </is>
       </c>
-      <c r="F3115" t="inlineStr">
+      <c r="F3115" s="0" t="inlineStr">
         <is>
           <t>学习累了，我会听听音乐调剂一下心情。</t>
         </is>
       </c>
-      <c r="G3115" t="inlineStr"/>
-      <c r="H3115" t="inlineStr"/>
+      <c r="G3115" s="0" t="inlineStr"/>
+      <c r="H3115" s="0" t="inlineStr"/>
     </row>
     <row r="3116">
-      <c r="A3116" t="inlineStr">
+      <c r="A3116" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3116" t="inlineStr">
+      <c r="B3116" s="0" t="inlineStr">
         <is>
           <t>供不应求</t>
         </is>
       </c>
-      <c r="C3116" t="inlineStr">
+      <c r="C3116" s="0" t="inlineStr">
         <is>
           <t>gōngbùyìngqiú</t>
         </is>
       </c>
-      <c r="D3116" t="inlineStr">
+      <c r="D3116" s="0" t="inlineStr">
         <is>
           <t>供应满足不了需求</t>
         </is>
       </c>
-      <c r="E3116" t="inlineStr">
+      <c r="E3116" s="0" t="inlineStr">
         <is>
           <t>cung không đủ cầu</t>
         </is>
       </c>
-      <c r="F3116" t="inlineStr">
+      <c r="F3116" s="0" t="inlineStr">
         <is>
           <t>在中国，好的睡眠门诊医生总是供不应求。</t>
         </is>
       </c>
-      <c r="G3116" t="inlineStr"/>
-      <c r="H3116" t="inlineStr"/>
+      <c r="G3116" s="0" t="inlineStr"/>
+      <c r="H3116" s="0" t="inlineStr"/>
     </row>
     <row r="3117">
-      <c r="A3117" t="inlineStr">
+      <c r="A3117" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3117" t="inlineStr">
+      <c r="B3117" s="0" t="inlineStr">
         <is>
           <t>不相上下</t>
         </is>
       </c>
-      <c r="C3117" t="inlineStr">
+      <c r="C3117" s="0" t="inlineStr">
         <is>
           <t>bùxiāng-shàngxià</t>
         </is>
       </c>
-      <c r="D3117" t="inlineStr">
+      <c r="D3117" s="0" t="inlineStr">
         <is>
           <t>分不出高低好坏，程度差不多</t>
         </is>
       </c>
-      <c r="E3117" t="inlineStr">
+      <c r="E3117" s="0" t="inlineStr">
         <is>
           <t>ngang tài ngang sức, xấp xỉ</t>
         </is>
       </c>
-      <c r="F3117" t="inlineStr">
+      <c r="F3117" s="0" t="inlineStr">
         <is>
           <t>我和同桌的汉语水平不相上下。</t>
         </is>
       </c>
-      <c r="G3117" t="inlineStr"/>
-      <c r="H3117" t="inlineStr"/>
+      <c r="G3117" s="0" t="inlineStr"/>
+      <c r="H3117" s="0" t="inlineStr"/>
     </row>
     <row r="3118">
-      <c r="A3118" t="inlineStr">
+      <c r="A3118" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3118" t="inlineStr">
+      <c r="B3118" s="0" t="inlineStr">
         <is>
           <t>总而言之</t>
         </is>
       </c>
-      <c r="C3118" t="inlineStr">
+      <c r="C3118" s="0" t="inlineStr">
         <is>
           <t>zǒng'éryánzhī</t>
         </is>
       </c>
-      <c r="D3118" t="inlineStr">
+      <c r="D3118" s="0" t="inlineStr">
         <is>
           <t>总的说来</t>
         </is>
       </c>
-      <c r="E3118" t="inlineStr">
+      <c r="E3118" s="0" t="inlineStr">
         <is>
           <t>tóm lại, nói tóm lại</t>
         </is>
       </c>
-      <c r="F3118" t="inlineStr">
+      <c r="F3118" s="0" t="inlineStr">
         <is>
           <t>总而言之，想学好中文，坚持最重要。</t>
         </is>
       </c>
-      <c r="G3118" t="inlineStr"/>
-      <c r="H3118" t="inlineStr"/>
+      <c r="G3118" s="0" t="inlineStr"/>
+      <c r="H3118" s="0" t="inlineStr"/>
     </row>
     <row r="3119">
-      <c r="A3119" t="inlineStr">
+      <c r="A3119" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3119" t="inlineStr">
+      <c r="B3119" s="0" t="inlineStr">
         <is>
           <t>恶化</t>
         </is>
       </c>
-      <c r="C3119" t="inlineStr">
+      <c r="C3119" s="0" t="inlineStr">
         <is>
           <t>èhuà</t>
         </is>
       </c>
-      <c r="D3119" t="inlineStr">
+      <c r="D3119" s="0" t="inlineStr">
         <is>
           <t>情况向坏的方向发展</t>
         </is>
       </c>
-      <c r="E3119" t="inlineStr">
+      <c r="E3119" s="0" t="inlineStr">
         <is>
           <t>xấu đi, trở nặng</t>
         </is>
       </c>
-      <c r="F3119" t="inlineStr">
+      <c r="F3119" s="0" t="inlineStr">
         <is>
           <t>如果一直睡不好，健康状况会慢慢恶化。</t>
         </is>
       </c>
-      <c r="G3119" t="inlineStr"/>
-      <c r="H3119" t="inlineStr"/>
+      <c r="G3119" s="0" t="inlineStr"/>
+      <c r="H3119" s="0" t="inlineStr"/>
     </row>
     <row r="3120">
-      <c r="A3120" t="inlineStr">
+      <c r="A3120" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3120" t="inlineStr">
+      <c r="B3120" s="0" t="inlineStr">
         <is>
           <t>适宜</t>
         </is>
       </c>
-      <c r="C3120" t="inlineStr">
+      <c r="C3120" s="0" t="inlineStr">
         <is>
           <t>shìyí</t>
         </is>
       </c>
-      <c r="D3120" t="inlineStr">
+      <c r="D3120" s="0" t="inlineStr">
         <is>
           <t>合适，恰当</t>
         </is>
       </c>
-      <c r="E3120" t="inlineStr">
+      <c r="E3120" s="0" t="inlineStr">
         <is>
           <t>thích hợp, phù hợp</t>
         </is>
       </c>
-      <c r="F3120" t="inlineStr">
+      <c r="F3120" s="0" t="inlineStr">
         <is>
           <t>睡前听点轻音乐，很适宜放松心情。</t>
         </is>
       </c>
-      <c r="G3120" t="inlineStr"/>
-      <c r="H3120" t="inlineStr"/>
+      <c r="G3120" s="0" t="inlineStr"/>
+      <c r="H3120" s="0" t="inlineStr"/>
     </row>
     <row r="3121">
-      <c r="A3121" t="inlineStr">
+      <c r="A3121" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3121" t="inlineStr">
+      <c r="B3121" s="0" t="inlineStr">
         <is>
           <t>场合</t>
         </is>
       </c>
-      <c r="C3121" t="inlineStr">
+      <c r="C3121" s="0" t="inlineStr">
         <is>
           <t>chǎnghé</t>
         </is>
       </c>
-      <c r="D3121" t="inlineStr">
+      <c r="D3121" s="0" t="inlineStr">
         <is>
           <t>一定的时间、地点和情况</t>
         </is>
       </c>
-      <c r="E3121" t="inlineStr">
+      <c r="E3121" s="0" t="inlineStr">
         <is>
           <t>trường hợp, dịp, hoàn cảnh</t>
         </is>
       </c>
-      <c r="F3121" t="inlineStr">
+      <c r="F3121" s="0" t="inlineStr">
         <is>
           <t>在正式场合，我说中文会更客气一些。</t>
         </is>
       </c>
-      <c r="G3121" t="inlineStr"/>
-      <c r="H3121" t="inlineStr"/>
+      <c r="G3121" s="0" t="inlineStr"/>
+      <c r="H3121" s="0" t="inlineStr"/>
     </row>
     <row r="3122">
-      <c r="A3122" t="inlineStr">
+      <c r="A3122" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3122" t="inlineStr">
+      <c r="B3122" s="0" t="inlineStr">
         <is>
           <t>地步</t>
         </is>
       </c>
-      <c r="C3122" t="inlineStr">
+      <c r="C3122" s="0" t="inlineStr">
         <is>
           <t>dìbù</t>
         </is>
       </c>
-      <c r="D3122" t="inlineStr">
+      <c r="D3122" s="0" t="inlineStr">
         <is>
           <t>达到的程度（多指不好的情况）</t>
         </is>
       </c>
-      <c r="E3122" t="inlineStr">
+      <c r="E3122" s="0" t="inlineStr">
         <is>
           <t>mức độ, nước (đến nước)</t>
         </is>
       </c>
-      <c r="F3122" t="inlineStr">
+      <c r="F3122" s="0" t="inlineStr">
         <is>
           <t>那阵子我忙到连饭都顾不上吃的地步。</t>
         </is>
       </c>
-      <c r="G3122" t="inlineStr"/>
-      <c r="H3122" t="inlineStr"/>
+      <c r="G3122" s="0" t="inlineStr"/>
+      <c r="H3122" s="0" t="inlineStr"/>
     </row>
     <row r="3123">
-      <c r="A3123" t="inlineStr">
+      <c r="A3123" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3123" t="inlineStr">
+      <c r="B3123" s="0" t="inlineStr">
         <is>
           <t>混乱</t>
         </is>
       </c>
-      <c r="C3123" t="inlineStr">
+      <c r="C3123" s="0" t="inlineStr">
         <is>
           <t>hùnluàn</t>
         </is>
       </c>
-      <c r="D3123" t="inlineStr">
+      <c r="D3123" s="0" t="inlineStr">
         <is>
           <t>没有条理，乱七八糟</t>
         </is>
       </c>
-      <c r="E3123" t="inlineStr">
+      <c r="E3123" s="0" t="inlineStr">
         <is>
           <t>hỗn loạn, lộn xộn</t>
         </is>
       </c>
-      <c r="F3123" t="inlineStr">
+      <c r="F3123" s="0" t="inlineStr">
         <is>
           <t>睡不好觉时，我的思路会变得很混乱。</t>
         </is>
       </c>
-      <c r="G3123" t="inlineStr"/>
-      <c r="H3123" t="inlineStr"/>
+      <c r="G3123" s="0" t="inlineStr"/>
+      <c r="H3123" s="0" t="inlineStr"/>
     </row>
     <row r="3124">
-      <c r="A3124" t="inlineStr">
+      <c r="A3124" s="0" t="inlineStr">
         <is>
           <t>Bài 30</t>
         </is>
       </c>
-      <c r="B3124" t="inlineStr">
+      <c r="B3124" s="0" t="inlineStr">
         <is>
           <t>举足轻重</t>
         </is>
       </c>
-      <c r="C3124" t="inlineStr">
+      <c r="C3124" s="0" t="inlineStr">
         <is>
           <t>jǔzú-qīngzhòng</t>
         </is>
       </c>
-      <c r="D3124" t="inlineStr">
+      <c r="D3124" s="0" t="inlineStr">
         <is>
           <t>所处地位重要，一举一动都影响全局</t>
         </is>
       </c>
-      <c r="E3124" t="inlineStr">
+      <c r="E3124" s="0" t="inlineStr">
         <is>
           <t>có vai trò then chốt, cực kỳ quan trọng</t>
         </is>
       </c>
-      <c r="F3124" t="inlineStr">
+      <c r="F3124" s="0" t="inlineStr">
         <is>
           <t>睡眠对健康举足轻重，千万不能忽视。</t>
         </is>
       </c>
-      <c r="G3124" t="inlineStr"/>
-      <c r="H3124" t="inlineStr"/>
+      <c r="G3124" s="0" t="inlineStr"/>
+      <c r="H3124" s="0" t="inlineStr"/>
+    </row>
+    <row r="3125">
+      <c r="A3125" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3125" s="0" t="inlineStr">
+        <is>
+          <t>忠实</t>
+        </is>
+      </c>
+      <c r="C3125" s="0" t="inlineStr">
+        <is>
+          <t>zhōngshí</t>
+        </is>
+      </c>
+      <c r="D3125" s="0" t="inlineStr">
+        <is>
+          <t>对人或事很真诚，一直不变心。</t>
+        </is>
+      </c>
+      <c r="E3125" s="0" t="inlineStr">
+        <is>
+          <t>trung thực, trung thành</t>
+        </is>
+      </c>
+      <c r="F3125" s="0" t="inlineStr">
+        <is>
+          <t>虽然工作很忙，我还是每天忠实地坚持背单词，准备HSK6考试。</t>
+        </is>
+      </c>
+      <c r="G3125" s="0" t="inlineStr"/>
+      <c r="H3125" s="0" t="inlineStr"/>
+    </row>
+    <row r="3126">
+      <c r="A3126" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3126" s="0" t="inlineStr">
+        <is>
+          <t>不敢当</t>
+        </is>
+      </c>
+      <c r="C3126" s="0" t="inlineStr">
+        <is>
+          <t>bùgǎndāng</t>
+        </is>
+      </c>
+      <c r="D3126" s="0" t="inlineStr">
+        <is>
+          <t>别人夸奖自己的时候，谦虚地说自己配不上这样的夸奖。</t>
+        </is>
+      </c>
+      <c r="E3126" s="0" t="inlineStr">
+        <is>
+          <t>không dám nhận (lời khen), quá khen rồi</t>
+        </is>
+      </c>
+      <c r="F3126" s="0" t="inlineStr">
+        <is>
+          <t>老板夸我中文说得像中国人一样，我连忙说："不敢当，不敢当，我还差得远呢。"</t>
+        </is>
+      </c>
+      <c r="G3126" s="0" t="inlineStr"/>
+      <c r="H3126" s="0" t="inlineStr"/>
+    </row>
+    <row r="3127">
+      <c r="A3127" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3127" s="0" t="inlineStr">
+        <is>
+          <t>走廊</t>
+        </is>
+      </c>
+      <c r="C3127" s="0" t="inlineStr">
+        <is>
+          <t>zǒuláng</t>
+        </is>
+      </c>
+      <c r="D3127" s="0" t="inlineStr">
+        <is>
+          <t>房子里连接各个房间的长长的通道。</t>
+        </is>
+      </c>
+      <c r="E3127" s="0" t="inlineStr">
+        <is>
+          <t>hành lang</t>
+        </is>
+      </c>
+      <c r="F3127" s="0" t="inlineStr">
+        <is>
+          <t>公司的走廊上贴满了员工旅游的照片，每次经过我都会看一看。</t>
+        </is>
+      </c>
+      <c r="G3127" s="0" t="inlineStr"/>
+      <c r="H3127" s="0" t="inlineStr"/>
+    </row>
+    <row r="3128">
+      <c r="A3128" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3128" s="0" t="inlineStr">
+        <is>
+          <t>徒弟</t>
+        </is>
+      </c>
+      <c r="C3128" s="0" t="inlineStr">
+        <is>
+          <t>túdì</t>
+        </is>
+      </c>
+      <c r="D3128" s="0" t="inlineStr">
+        <is>
+          <t>跟着师父学手艺或本领的人。</t>
+        </is>
+      </c>
+      <c r="E3128" s="0" t="inlineStr">
+        <is>
+          <t>đồ đệ, học trò (học nghề)</t>
+        </is>
+      </c>
+      <c r="F3128" s="0" t="inlineStr">
+        <is>
+          <t>我教中文的时候，学生们总说自己是我的徒弟，让我教他们说地道的中文。</t>
+        </is>
+      </c>
+      <c r="G3128" s="0" t="inlineStr"/>
+      <c r="H3128" s="0" t="inlineStr"/>
+    </row>
+    <row r="3129">
+      <c r="A3129" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3129" s="0" t="inlineStr">
+        <is>
+          <t>气功</t>
+        </is>
+      </c>
+      <c r="C3129" s="0" t="inlineStr">
+        <is>
+          <t>qìgōng</t>
+        </is>
+      </c>
+      <c r="D3129" s="0" t="inlineStr">
+        <is>
+          <t>中国传统的一种通过呼吸和动作来锻炼身体的方法。</t>
+        </is>
+      </c>
+      <c r="E3129" s="0" t="inlineStr">
+        <is>
+          <t>khí công</t>
+        </is>
+      </c>
+      <c r="F3129" s="0" t="inlineStr">
+        <is>
+          <t>我们公司楼下的公园里，每天早上都有一群中国同事在练气功。</t>
+        </is>
+      </c>
+      <c r="G3129" s="0" t="inlineStr"/>
+      <c r="H3129" s="0" t="inlineStr"/>
+    </row>
+    <row r="3130">
+      <c r="A3130" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3130" s="0" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="C3130" s="0" t="inlineStr">
+        <is>
+          <t>jiàn</t>
+        </is>
+      </c>
+      <c r="D3130" s="0" t="inlineStr">
+        <is>
+          <t>一种古代的兵器，两边都很锋利。</t>
+        </is>
+      </c>
+      <c r="E3130" s="0" t="inlineStr">
+        <is>
+          <t>kiếm</t>
+        </is>
+      </c>
+      <c r="F3130" s="0" t="inlineStr">
+        <is>
+          <t>我在中国旅游的时候，在博物馆里看到了一把很古老的剑。</t>
+        </is>
+      </c>
+      <c r="G3130" s="0" t="inlineStr"/>
+      <c r="H3130" s="0" t="inlineStr"/>
+    </row>
+    <row r="3131">
+      <c r="A3131" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3131" s="0" t="inlineStr">
+        <is>
+          <t>协会</t>
+        </is>
+      </c>
+      <c r="C3131" s="0" t="inlineStr">
+        <is>
+          <t>xiéhuì</t>
+        </is>
+      </c>
+      <c r="D3131" s="0" t="inlineStr">
+        <is>
+          <t>一群有相同兴趣或目的的人组成的组织。</t>
+        </is>
+      </c>
+      <c r="E3131" s="0" t="inlineStr">
+        <is>
+          <t>hiệp hội</t>
+        </is>
+      </c>
+      <c r="F3131" s="0" t="inlineStr">
+        <is>
+          <t>我打算准备完HSK6之后加入汉语教师协会，认识更多同行。</t>
+        </is>
+      </c>
+      <c r="G3131" s="0" t="inlineStr"/>
+      <c r="H3131" s="0" t="inlineStr"/>
+    </row>
+    <row r="3132">
+      <c r="A3132" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3132" s="0" t="inlineStr">
+        <is>
+          <t>爆发</t>
+        </is>
+      </c>
+      <c r="C3132" s="0" t="inlineStr">
+        <is>
+          <t>bàofā</t>
+        </is>
+      </c>
+      <c r="D3132" s="0" t="inlineStr">
+        <is>
+          <t>突然猛烈地发生。</t>
+        </is>
+      </c>
+      <c r="E3132" s="0" t="inlineStr">
+        <is>
+          <t>bùng nổ, bộc phát</t>
+        </is>
+      </c>
+      <c r="F3132" s="0" t="inlineStr">
+        <is>
+          <t>上个月公司里因为一个项目的问题，同事之间的矛盾一下子爆发了。</t>
+        </is>
+      </c>
+      <c r="G3132" s="0" t="inlineStr"/>
+      <c r="H3132" s="0" t="inlineStr"/>
+    </row>
+    <row r="3133">
+      <c r="A3133" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3133" s="0" t="inlineStr">
+        <is>
+          <t>劈</t>
+        </is>
+      </c>
+      <c r="C3133" s="0" t="inlineStr">
+        <is>
+          <t>pī</t>
+        </is>
+      </c>
+      <c r="D3133" s="0" t="inlineStr">
+        <is>
+          <t>用刀、斧等工具把东西从中间用力分开。</t>
+        </is>
+      </c>
+      <c r="E3133" s="0" t="inlineStr">
+        <is>
+          <t>chẻ, bổ (củi...)</t>
+        </is>
+      </c>
+      <c r="F3133" s="0" t="inlineStr">
+        <is>
+          <t>小时候在乡下，我经常帮爷爷劈柴生火做饭。</t>
+        </is>
+      </c>
+      <c r="G3133" s="0" t="inlineStr"/>
+      <c r="H3133" s="0" t="inlineStr"/>
+    </row>
+    <row r="3134">
+      <c r="A3134" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3134" s="0" t="inlineStr">
+        <is>
+          <t>误解</t>
+        </is>
+      </c>
+      <c r="C3134" s="0" t="inlineStr">
+        <is>
+          <t>wùjiě</t>
+        </is>
+      </c>
+      <c r="D3134" s="0" t="inlineStr">
+        <is>
+          <t>理解得不对，把意思弄错了。</t>
+        </is>
+      </c>
+      <c r="E3134" s="0" t="inlineStr">
+        <is>
+          <t>hiểu lầm</t>
+        </is>
+      </c>
+      <c r="F3134" s="0" t="inlineStr">
+        <is>
+          <t>因为我的中文表达不够清楚，同事误解了我的意思，还好后来解释清楚了。</t>
+        </is>
+      </c>
+      <c r="G3134" s="0" t="inlineStr"/>
+      <c r="H3134" s="0" t="inlineStr"/>
+    </row>
+    <row r="3135">
+      <c r="A3135" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3135" s="0" t="inlineStr">
+        <is>
+          <t>群众</t>
+        </is>
+      </c>
+      <c r="C3135" s="0" t="inlineStr">
+        <is>
+          <t>qúnzhòng</t>
+        </is>
+      </c>
+      <c r="D3135" s="0" t="inlineStr">
+        <is>
+          <t>普通的老百姓，人民大众。</t>
+        </is>
+      </c>
+      <c r="E3135" s="0" t="inlineStr">
+        <is>
+          <t>quần chúng, dân chúng</t>
+        </is>
+      </c>
+      <c r="F3135" s="0" t="inlineStr">
+        <is>
+          <t>政府这次的新政策得到了广大群众的支持。</t>
+        </is>
+      </c>
+      <c r="G3135" s="0" t="inlineStr"/>
+      <c r="H3135" s="0" t="inlineStr"/>
+    </row>
+    <row r="3136">
+      <c r="A3136" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3136" s="0" t="inlineStr">
+        <is>
+          <t>逐年</t>
+        </is>
+      </c>
+      <c r="C3136" s="0" t="inlineStr">
+        <is>
+          <t>zhúnián</t>
+        </is>
+      </c>
+      <c r="D3136" s="0" t="inlineStr">
+        <is>
+          <t>一年一年地（变化）。</t>
+        </is>
+      </c>
+      <c r="E3136" s="0" t="inlineStr">
+        <is>
+          <t>từng năm, theo từng năm</t>
+        </is>
+      </c>
+      <c r="F3136" s="0" t="inlineStr">
+        <is>
+          <t>我的中文水平在这几年逐年提高，现在已经能和中国同事无障碍交流了。</t>
+        </is>
+      </c>
+      <c r="G3136" s="0" t="inlineStr"/>
+      <c r="H3136" s="0" t="inlineStr"/>
+    </row>
+    <row r="3137">
+      <c r="A3137" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3137" s="0" t="inlineStr">
+        <is>
+          <t>要素</t>
+        </is>
+      </c>
+      <c r="C3137" s="0" t="inlineStr">
+        <is>
+          <t>yàosù</t>
+        </is>
+      </c>
+      <c r="D3137" s="0" t="inlineStr">
+        <is>
+          <t>构成事物不可缺少的重要部分。</t>
+        </is>
+      </c>
+      <c r="E3137" s="0" t="inlineStr">
+        <is>
+          <t>yếu tố</t>
+        </is>
+      </c>
+      <c r="F3137" s="0" t="inlineStr">
+        <is>
+          <t>词汇量、语法和语感是学好HSK6的三个重要要素。</t>
+        </is>
+      </c>
+      <c r="G3137" s="0" t="inlineStr"/>
+      <c r="H3137" s="0" t="inlineStr"/>
+    </row>
+    <row r="3138">
+      <c r="A3138" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3138" s="0" t="inlineStr">
+        <is>
+          <t>智力</t>
+        </is>
+      </c>
+      <c r="C3138" s="0" t="inlineStr">
+        <is>
+          <t>zhìlì</t>
+        </is>
+      </c>
+      <c r="D3138" s="0" t="inlineStr">
+        <is>
+          <t>人认识、理解和解决问题的能力。</t>
+        </is>
+      </c>
+      <c r="E3138" s="0" t="inlineStr">
+        <is>
+          <t>trí lực, trí tuệ</t>
+        </is>
+      </c>
+      <c r="F3138" s="0" t="inlineStr">
+        <is>
+          <t>学外语不但需要努力，也需要一定的智力和好的学习方法。</t>
+        </is>
+      </c>
+      <c r="G3138" s="0" t="inlineStr"/>
+      <c r="H3138" s="0" t="inlineStr"/>
+    </row>
+    <row r="3139">
+      <c r="A3139" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3139" s="0" t="inlineStr">
+        <is>
+          <t>预期</t>
+        </is>
+      </c>
+      <c r="C3139" s="0" t="inlineStr">
+        <is>
+          <t>yùqī</t>
+        </is>
+      </c>
+      <c r="D3139" s="0" t="inlineStr">
+        <is>
+          <t>事先期望或估计会发生的情况。</t>
+        </is>
+      </c>
+      <c r="E3139" s="0" t="inlineStr">
+        <is>
+          <t>dự kiến, kỳ vọng trước</t>
+        </is>
+      </c>
+      <c r="F3139" s="0" t="inlineStr">
+        <is>
+          <t>这次HSK6考试的成绩比我预期的要好，我很开心。</t>
+        </is>
+      </c>
+      <c r="G3139" s="0" t="inlineStr"/>
+      <c r="H3139" s="0" t="inlineStr"/>
+    </row>
+    <row r="3140">
+      <c r="A3140" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3140" s="0" t="inlineStr">
+        <is>
+          <t>首要</t>
+        </is>
+      </c>
+      <c r="C3140" s="0" t="inlineStr">
+        <is>
+          <t>shǒuyào</t>
+        </is>
+      </c>
+      <c r="D3140" s="0" t="inlineStr">
+        <is>
+          <t>排在第一位的，最重要的。</t>
+        </is>
+      </c>
+      <c r="E3140" s="0" t="inlineStr">
+        <is>
+          <t>hàng đầu, quan trọng nhất</t>
+        </is>
+      </c>
+      <c r="F3140" s="0" t="inlineStr">
+        <is>
+          <t>对我来说，提高口语的自然度是目前学习中文的首要任务。</t>
+        </is>
+      </c>
+      <c r="G3140" s="0" t="inlineStr"/>
+      <c r="H3140" s="0" t="inlineStr"/>
+    </row>
+    <row r="3141">
+      <c r="A3141" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3141" s="0" t="inlineStr">
+        <is>
+          <t>生锈</t>
+        </is>
+      </c>
+      <c r="C3141" s="0" t="inlineStr">
+        <is>
+          <t>shēngxiù</t>
+        </is>
+      </c>
+      <c r="D3141" s="0" t="inlineStr">
+        <is>
+          <t>金属因为潮湿或长期接触空气而表面变质、变色。</t>
+        </is>
+      </c>
+      <c r="E3141" s="0" t="inlineStr">
+        <is>
+          <t>gỉ sét, hoen gỉ</t>
+        </is>
+      </c>
+      <c r="F3141" s="0" t="inlineStr">
+        <is>
+          <t>好久不用中文，我感觉自己的口语都要生锈了，得赶紧多练习。</t>
+        </is>
+      </c>
+      <c r="G3141" s="0" t="inlineStr"/>
+      <c r="H3141" s="0" t="inlineStr"/>
+    </row>
+    <row r="3142">
+      <c r="A3142" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3142" s="0" t="inlineStr">
+        <is>
+          <t>放射</t>
+        </is>
+      </c>
+      <c r="C3142" s="0" t="inlineStr">
+        <is>
+          <t>fàngshè</t>
+        </is>
+      </c>
+      <c r="D3142" s="0" t="inlineStr">
+        <is>
+          <t>向四周发出光、热等能量。</t>
+        </is>
+      </c>
+      <c r="E3142" s="0" t="inlineStr">
+        <is>
+          <t>phóng xạ, tỏa ra (ánh sáng...)</t>
+        </is>
+      </c>
+      <c r="F3142" s="0" t="inlineStr">
+        <is>
+          <t>老师讲课的时候眼睛里放射出对语言的热爱，让我也很受感染。</t>
+        </is>
+      </c>
+      <c r="G3142" s="0" t="inlineStr"/>
+      <c r="H3142" s="0" t="inlineStr"/>
+    </row>
+    <row r="3143">
+      <c r="A3143" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3143" s="0" t="inlineStr">
+        <is>
+          <t>夫人</t>
+        </is>
+      </c>
+      <c r="C3143" s="0" t="inlineStr">
+        <is>
+          <t>fūrén</t>
+        </is>
+      </c>
+      <c r="D3143" s="0" t="inlineStr">
+        <is>
+          <t>对已婚女人的尊称，也指自己或别人的妻子。</t>
+        </is>
+      </c>
+      <c r="E3143" s="0" t="inlineStr">
+        <is>
+          <t>phu nhân, vợ (cách gọi trang trọng)</t>
+        </is>
+      </c>
+      <c r="F3143" s="0" t="inlineStr">
+        <is>
+          <t>我们公司中国老板的夫人也是一位很优秀的汉语老师。</t>
+        </is>
+      </c>
+      <c r="G3143" s="0" t="inlineStr"/>
+      <c r="H3143" s="0" t="inlineStr"/>
+    </row>
+    <row r="3144">
+      <c r="A3144" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3144" s="0" t="inlineStr">
+        <is>
+          <t>归根到底</t>
+        </is>
+      </c>
+      <c r="C3144" s="0" t="inlineStr">
+        <is>
+          <t>guīgēndàodǐ</t>
+        </is>
+      </c>
+      <c r="D3144" s="0" t="inlineStr">
+        <is>
+          <t>从最根本的地方说，总结起来说。</t>
+        </is>
+      </c>
+      <c r="E3144" s="0" t="inlineStr">
+        <is>
+          <t>xét cho cùng, rốt cuộc</t>
+        </is>
+      </c>
+      <c r="F3144" s="0" t="inlineStr">
+        <is>
+          <t>归根到底，学好中文靠的还是每天坚持练习，而不是三天打鱼两天晒网。</t>
+        </is>
+      </c>
+      <c r="G3144" s="0" t="inlineStr"/>
+      <c r="H3144" s="0" t="inlineStr"/>
+    </row>
+    <row r="3145">
+      <c r="A3145" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3145" s="0" t="inlineStr">
+        <is>
+          <t>潜力</t>
+        </is>
+      </c>
+      <c r="C3145" s="0" t="inlineStr">
+        <is>
+          <t>qiánlì</t>
+        </is>
+      </c>
+      <c r="D3145" s="0" t="inlineStr">
+        <is>
+          <t>隐藏着的、还没有完全发挥出来的能力。</t>
+        </is>
+      </c>
+      <c r="E3145" s="0" t="inlineStr">
+        <is>
+          <t>tiềm lực, tiềm năng</t>
+        </is>
+      </c>
+      <c r="F3145" s="0" t="inlineStr">
+        <is>
+          <t>我的学生虽然现在只是HSK3水平，但我看得出他在口语方面很有潜力。</t>
+        </is>
+      </c>
+      <c r="G3145" s="0" t="inlineStr"/>
+      <c r="H3145" s="0" t="inlineStr"/>
+    </row>
+    <row r="3146">
+      <c r="A3146" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3146" s="0" t="inlineStr">
+        <is>
+          <t>端端正正</t>
+        </is>
+      </c>
+      <c r="C3146" s="0" t="inlineStr">
+        <is>
+          <t>duānduānzhèngzhèng</t>
+        </is>
+      </c>
+      <c r="D3146" s="0" t="inlineStr">
+        <is>
+          <t>形容摆放得很整齐、很正，一点儿也不歪斜（也形容坐、站的姿势很正）。</t>
+        </is>
+      </c>
+      <c r="E3146" s="0" t="inlineStr">
+        <is>
+          <t>ngay ngắn, đàng hoàng (dạng láy nhấn mạnh)</t>
+        </is>
+      </c>
+      <c r="F3146" s="0" t="inlineStr">
+        <is>
+          <t>我要求学生写汉字的时候一定要端端正正的，不能马虎。</t>
+        </is>
+      </c>
+      <c r="G3146" s="0" t="inlineStr"/>
+      <c r="H3146" s="0" t="inlineStr"/>
+    </row>
+    <row r="3147">
+      <c r="A3147" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3147" s="0" t="inlineStr">
+        <is>
+          <t>端正</t>
+        </is>
+      </c>
+      <c r="C3147" s="0" t="inlineStr">
+        <is>
+          <t>duānzhèng</t>
+        </is>
+      </c>
+      <c r="D3147" s="0" t="inlineStr">
+        <is>
+          <t>不歪斜，正；也指人的态度或品行正派。</t>
+        </is>
+      </c>
+      <c r="E3147" s="0" t="inlineStr">
+        <is>
+          <t>ngay ngắn, đứng đắn</t>
+        </is>
+      </c>
+      <c r="F3147" s="0" t="inlineStr">
+        <is>
+          <t>老师常常提醒我们坐姿要端正，学习态度也要端正。</t>
+        </is>
+      </c>
+      <c r="G3147" s="0" t="inlineStr"/>
+      <c r="H3147" s="0" t="inlineStr"/>
+    </row>
+    <row r="3148">
+      <c r="A3148" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3148" s="0" t="inlineStr">
+        <is>
+          <t>胡乱</t>
+        </is>
+      </c>
+      <c r="C3148" s="0" t="inlineStr">
+        <is>
+          <t>húluàn</t>
+        </is>
+      </c>
+      <c r="D3148" s="0" t="inlineStr">
+        <is>
+          <t>随随便便地、不认真、没有经过思考地（做事）。</t>
+        </is>
+      </c>
+      <c r="E3148" s="0" t="inlineStr">
+        <is>
+          <t>bừa bãi, tùy tiện, cẩu thả</t>
+        </is>
+      </c>
+      <c r="F3148" s="0" t="inlineStr">
+        <is>
+          <t>考试的时候不能胡乱写答案，一定要认真思考再作答。</t>
+        </is>
+      </c>
+      <c r="G3148" s="0" t="inlineStr"/>
+      <c r="H3148" s="0" t="inlineStr"/>
+    </row>
+    <row r="3149">
+      <c r="A3149" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3149" s="0" t="inlineStr">
+        <is>
+          <t>间接</t>
+        </is>
+      </c>
+      <c r="C3149" s="0" t="inlineStr">
+        <is>
+          <t>jiànjiē</t>
+        </is>
+      </c>
+      <c r="D3149" s="0" t="inlineStr">
+        <is>
+          <t>不是直接发生关系的，中间还经过别的环节。</t>
+        </is>
+      </c>
+      <c r="E3149" s="0" t="inlineStr">
+        <is>
+          <t>gián tiếp</t>
+        </is>
+      </c>
+      <c r="F3149" s="0" t="inlineStr">
+        <is>
+          <t>我是通过朋友介绍间接认识了现在的中文老师的。</t>
+        </is>
+      </c>
+      <c r="G3149" s="0" t="inlineStr"/>
+      <c r="H3149" s="0" t="inlineStr"/>
+    </row>
+    <row r="3150">
+      <c r="A3150" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3150" s="0" t="inlineStr">
+        <is>
+          <t>品行</t>
+        </is>
+      </c>
+      <c r="C3150" s="0" t="inlineStr">
+        <is>
+          <t>pǐnxíng</t>
+        </is>
+      </c>
+      <c r="D3150" s="0" t="inlineStr">
+        <is>
+          <t>一个人的道德行为和品质。</t>
+        </is>
+      </c>
+      <c r="E3150" s="0" t="inlineStr">
+        <is>
+          <t>phẩm hạnh, đạo đức</t>
+        </is>
+      </c>
+      <c r="F3150" s="0" t="inlineStr">
+        <is>
+          <t>我常常告诉学生，学好中文固然重要，但品行端正才是做人的根本。</t>
+        </is>
+      </c>
+      <c r="G3150" s="0" t="inlineStr"/>
+      <c r="H3150" s="0" t="inlineStr"/>
+    </row>
+    <row r="3151">
+      <c r="A3151" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3151" s="0" t="inlineStr">
+        <is>
+          <t>紫外线</t>
+        </is>
+      </c>
+      <c r="C3151" s="0" t="inlineStr">
+        <is>
+          <t>zǐwàixiàn</t>
+        </is>
+      </c>
+      <c r="D3151" s="0" t="inlineStr">
+        <is>
+          <t>太阳光里一种人的眼睛看不见、对皮肤有影响的光线。</t>
+        </is>
+      </c>
+      <c r="E3151" s="0" t="inlineStr">
+        <is>
+          <t>tia cực tím, tia tử ngoại</t>
+        </is>
+      </c>
+      <c r="F3151" s="0" t="inlineStr">
+        <is>
+          <t>夏天在外面运动，一定要做好防晒，避免紫外线伤害皮肤。</t>
+        </is>
+      </c>
+      <c r="G3151" s="0" t="inlineStr"/>
+      <c r="H3151" s="0" t="inlineStr"/>
+    </row>
+    <row r="3152">
+      <c r="A3152" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3152" s="0" t="inlineStr">
+        <is>
+          <t>消毒</t>
+        </is>
+      </c>
+      <c r="C3152" s="0" t="inlineStr">
+        <is>
+          <t>xiāodú</t>
+        </is>
+      </c>
+      <c r="D3152" s="0" t="inlineStr">
+        <is>
+          <t>用药物或高温等方法去掉物体上的细菌。</t>
+        </is>
+      </c>
+      <c r="E3152" s="0" t="inlineStr">
+        <is>
+          <t>khử trùng, tiệt trùng</t>
+        </is>
+      </c>
+      <c r="F3152" s="0" t="inlineStr">
+        <is>
+          <t>疫情期间，公司每天都会对办公室的桌椅进行消毒。</t>
+        </is>
+      </c>
+      <c r="G3152" s="0" t="inlineStr"/>
+      <c r="H3152" s="0" t="inlineStr"/>
+    </row>
+    <row r="3153">
+      <c r="A3153" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3153" s="0" t="inlineStr">
+        <is>
+          <t>钙</t>
+        </is>
+      </c>
+      <c r="C3153" s="0" t="inlineStr">
+        <is>
+          <t>gài</t>
+        </is>
+      </c>
+      <c r="D3153" s="0" t="inlineStr">
+        <is>
+          <t>一种人体骨骼需要的矿物质元素。</t>
+        </is>
+      </c>
+      <c r="E3153" s="0" t="inlineStr">
+        <is>
+          <t>canxi</t>
+        </is>
+      </c>
+      <c r="F3153" s="0" t="inlineStr">
+        <is>
+          <t>医生建议我多补钙，多喝牛奶，多晒太阳。</t>
+        </is>
+      </c>
+      <c r="G3153" s="0" t="inlineStr"/>
+      <c r="H3153" s="0" t="inlineStr"/>
+    </row>
+    <row r="3154">
+      <c r="A3154" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3154" s="0" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="C3154" s="0" t="inlineStr">
+        <is>
+          <t>èryǎnghuàtàn</t>
+        </is>
+      </c>
+      <c r="D3154" s="0" t="inlineStr">
+        <is>
+          <t>一种没有颜色的气体，人呼气时会排出这种气体。</t>
+        </is>
+      </c>
+      <c r="E3154" s="0" t="inlineStr">
+        <is>
+          <t>khí carbon dioxide (CO2)</t>
+        </is>
+      </c>
+      <c r="F3154" s="0" t="inlineStr">
+        <is>
+          <t>植物在白天会吸收二氧化碳，释放氧气。</t>
+        </is>
+      </c>
+      <c r="G3154" s="0" t="inlineStr"/>
+      <c r="H3154" s="0" t="inlineStr"/>
+    </row>
+    <row r="3155">
+      <c r="A3155" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3155" s="0" t="inlineStr">
+        <is>
+          <t>舒畅</t>
+        </is>
+      </c>
+      <c r="C3155" s="0" t="inlineStr">
+        <is>
+          <t>shūchàng</t>
+        </is>
+      </c>
+      <c r="D3155" s="0" t="inlineStr">
+        <is>
+          <t>心情很轻松、很愉快，没有烦恼。</t>
+        </is>
+      </c>
+      <c r="E3155" s="0" t="inlineStr">
+        <is>
+          <t>thoải mái, dễ chịu (tâm trạng)</t>
+        </is>
+      </c>
+      <c r="F3155" s="0" t="inlineStr">
+        <is>
+          <t>每次教完一堂课，看到学生学会了新知识，我心里就特别舒畅。</t>
+        </is>
+      </c>
+      <c r="G3155" s="0" t="inlineStr"/>
+      <c r="H3155" s="0" t="inlineStr"/>
+    </row>
+    <row r="3156">
+      <c r="A3156" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3156" s="0" t="inlineStr">
+        <is>
+          <t>宣扬</t>
+        </is>
+      </c>
+      <c r="C3156" s="0" t="inlineStr">
+        <is>
+          <t>xuānyáng</t>
+        </is>
+      </c>
+      <c r="D3156" s="0" t="inlineStr">
+        <is>
+          <t>广泛地宣传，让很多人知道（多指好的方面）。</t>
+        </is>
+      </c>
+      <c r="E3156" s="0" t="inlineStr">
+        <is>
+          <t>tuyên truyền, truyền bá, ca ngợi rộng rãi</t>
+        </is>
+      </c>
+      <c r="F3156" s="0" t="inlineStr">
+        <is>
+          <t>公司这次特意在朋友圈里宣扬新员工培训项目，希望吸引更多人才。</t>
+        </is>
+      </c>
+      <c r="G3156" s="0" t="inlineStr"/>
+      <c r="H3156" s="0" t="inlineStr"/>
+    </row>
+    <row r="3157">
+      <c r="A3157" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3157" s="0" t="inlineStr">
+        <is>
+          <t>孔</t>
+        </is>
+      </c>
+      <c r="C3157" s="0" t="inlineStr">
+        <is>
+          <t>kǒng</t>
+        </is>
+      </c>
+      <c r="D3157" s="0" t="inlineStr">
+        <is>
+          <t>小洞，窟窿。</t>
+        </is>
+      </c>
+      <c r="E3157" s="0" t="inlineStr">
+        <is>
+          <t>lỗ, hốc</t>
+        </is>
+      </c>
+      <c r="F3157" s="0" t="inlineStr">
+        <is>
+          <t>这件衣服穿的时间太长了，袖子上都磨出了一个小孔。</t>
+        </is>
+      </c>
+      <c r="G3157" s="0" t="inlineStr"/>
+      <c r="H3157" s="0" t="inlineStr"/>
+    </row>
+    <row r="3158">
+      <c r="A3158" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3158" s="0" t="inlineStr">
+        <is>
+          <t>循序渐进</t>
+        </is>
+      </c>
+      <c r="C3158" s="0" t="inlineStr">
+        <is>
+          <t>xúnxùjiànjìn</t>
+        </is>
+      </c>
+      <c r="D3158" s="0" t="inlineStr">
+        <is>
+          <t>按照一定的顺序，一步一步地向前发展，不能着急。</t>
+        </is>
+      </c>
+      <c r="E3158" s="0" t="inlineStr">
+        <is>
+          <t>tuần tự tiến lên, theo trình tự từng bước</t>
+        </is>
+      </c>
+      <c r="F3158" s="0" t="inlineStr">
+        <is>
+          <t>我教HSK1-3的学生时，一直强调学中文要循序渐进，不能一下子学太多语法点。</t>
+        </is>
+      </c>
+      <c r="G3158" s="0" t="inlineStr"/>
+      <c r="H3158" s="0" t="inlineStr"/>
+    </row>
+    <row r="3159">
+      <c r="A3159" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3159" s="0" t="inlineStr">
+        <is>
+          <t>急于求成</t>
+        </is>
+      </c>
+      <c r="C3159" s="0" t="inlineStr">
+        <is>
+          <t>jíyúqiúchéng</t>
+        </is>
+      </c>
+      <c r="D3159" s="0" t="inlineStr">
+        <is>
+          <t>急着想要马上取得成功，不愿意慢慢努力。</t>
+        </is>
+      </c>
+      <c r="E3159" s="0" t="inlineStr">
+        <is>
+          <t>nóng vội muốn thành công nhanh</t>
+        </is>
+      </c>
+      <c r="F3159" s="0" t="inlineStr">
+        <is>
+          <t>备考HSK6的时候我也曾经急于求成，后来才明白积累词汇才是王道。</t>
+        </is>
+      </c>
+      <c r="G3159" s="0" t="inlineStr"/>
+      <c r="H3159" s="0" t="inlineStr"/>
+    </row>
+    <row r="3160">
+      <c r="A3160" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3160" s="0" t="inlineStr">
+        <is>
+          <t>剧烈</t>
+        </is>
+      </c>
+      <c r="C3160" s="0" t="inlineStr">
+        <is>
+          <t>jùliè</t>
+        </is>
+      </c>
+      <c r="D3160" s="0" t="inlineStr">
+        <is>
+          <t>（运动、变化等）非常猛烈，程度很深。</t>
+        </is>
+      </c>
+      <c r="E3160" s="0" t="inlineStr">
+        <is>
+          <t>kịch liệt, dữ dội, mạnh mẽ</t>
+        </is>
+      </c>
+      <c r="F3160" s="0" t="inlineStr">
+        <is>
+          <t>医生说我心脏不太好，不适合做剧烈运动，只能散步或游泳。</t>
+        </is>
+      </c>
+      <c r="G3160" s="0" t="inlineStr"/>
+      <c r="H3160" s="0" t="inlineStr"/>
+    </row>
+    <row r="3161">
+      <c r="A3161" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3161" s="0" t="inlineStr">
+        <is>
+          <t>幅度</t>
+        </is>
+      </c>
+      <c r="C3161" s="0" t="inlineStr">
+        <is>
+          <t>fúdù</t>
+        </is>
+      </c>
+      <c r="D3161" s="0" t="inlineStr">
+        <is>
+          <t>事物变化的大小、范围的宽窄。</t>
+        </is>
+      </c>
+      <c r="E3161" s="0" t="inlineStr">
+        <is>
+          <t>biên độ, mức độ (dao động)</t>
+        </is>
+      </c>
+      <c r="F3161" s="0" t="inlineStr">
+        <is>
+          <t>这个月公司的销售额有了很大幅度的提高，大家都很开心。</t>
+        </is>
+      </c>
+      <c r="G3161" s="0" t="inlineStr"/>
+      <c r="H3161" s="0" t="inlineStr"/>
+    </row>
+    <row r="3162">
+      <c r="A3162" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3162" s="0" t="inlineStr">
+        <is>
+          <t>迁就</t>
+        </is>
+      </c>
+      <c r="C3162" s="0" t="inlineStr">
+        <is>
+          <t>qiānjiù</t>
+        </is>
+      </c>
+      <c r="D3162" s="0" t="inlineStr">
+        <is>
+          <t>为了让别人满意，勉强按照对方的想法去做，降低自己的要求。</t>
+        </is>
+      </c>
+      <c r="E3162" s="0" t="inlineStr">
+        <is>
+          <t>nhân nhượng, chiều theo</t>
+        </is>
+      </c>
+      <c r="F3162" s="0" t="inlineStr">
+        <is>
+          <t>教学生的时候，我不会一味迁就他们不想背单词的想法，该要求的还是要要求。</t>
+        </is>
+      </c>
+      <c r="G3162" s="0" t="inlineStr"/>
+      <c r="H3162" s="0" t="inlineStr"/>
+    </row>
+    <row r="3163">
+      <c r="A3163" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3163" s="0" t="inlineStr">
+        <is>
+          <t>坚定</t>
+        </is>
+      </c>
+      <c r="C3163" s="0" t="inlineStr">
+        <is>
+          <t>jiāndìng</t>
+        </is>
+      </c>
+      <c r="D3163" s="0" t="inlineStr">
+        <is>
+          <t>（信念、态度、立场等）稳定，不会轻易改变。</t>
+        </is>
+      </c>
+      <c r="E3163" s="0" t="inlineStr">
+        <is>
+          <t>kiên định, vững vàng</t>
+        </is>
+      </c>
+      <c r="F3163" s="0" t="inlineStr">
+        <is>
+          <t>我下定了坚定的决心，无论多忙，每天都要抽出时间学中文。</t>
+        </is>
+      </c>
+      <c r="G3163" s="0" t="inlineStr"/>
+      <c r="H3163" s="0" t="inlineStr"/>
+    </row>
+    <row r="3164">
+      <c r="A3164" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3164" s="0" t="inlineStr">
+        <is>
+          <t>坚韧</t>
+        </is>
+      </c>
+      <c r="C3164" s="0" t="inlineStr">
+        <is>
+          <t>jiānrèn</t>
+        </is>
+      </c>
+      <c r="D3164" s="0" t="inlineStr">
+        <is>
+          <t>坚固而有韧性，不容易被折断或打倒（多形容意志、精神）。</t>
+        </is>
+      </c>
+      <c r="E3164" s="0" t="inlineStr">
+        <is>
+          <t>kiên cường, bền bỉ, dẻo dai</t>
+        </is>
+      </c>
+      <c r="F3164" s="0" t="inlineStr">
+        <is>
+          <t>一个人要想学好一门外语，坚韧的毅力比聪明的头脑更重要。</t>
+        </is>
+      </c>
+      <c r="G3164" s="0" t="inlineStr"/>
+      <c r="H3164" s="0" t="inlineStr"/>
+    </row>
+    <row r="3165">
+      <c r="A3165" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3165" s="0" t="inlineStr">
+        <is>
+          <t>狠心</t>
+        </is>
+      </c>
+      <c r="C3165" s="0" t="inlineStr">
+        <is>
+          <t>hěnxīn</t>
+        </is>
+      </c>
+      <c r="D3165" s="0" t="inlineStr">
+        <is>
+          <t>下定决心不顾一切地（去做某件不容易或不忍心的事）。</t>
+        </is>
+      </c>
+      <c r="E3165" s="0" t="inlineStr">
+        <is>
+          <t>quyết tâm dứt khoát, cứng rắn với bản thân</t>
+        </is>
+      </c>
+      <c r="F3165" s="0" t="inlineStr">
+        <is>
+          <t>为了准备HSK6考试，我狠心推掉了很多朋友的聚会邀请，专心复习。</t>
+        </is>
+      </c>
+      <c r="G3165" s="0" t="inlineStr"/>
+      <c r="H3165" s="0" t="inlineStr"/>
+    </row>
+    <row r="3166">
+      <c r="A3166" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3166" s="0" t="inlineStr">
+        <is>
+          <t>半途而废</t>
+        </is>
+      </c>
+      <c r="C3166" s="0" t="inlineStr">
+        <is>
+          <t>bàntú'érfèi</t>
+        </is>
+      </c>
+      <c r="D3166" s="0" t="inlineStr">
+        <is>
+          <t>事情做到一半就停下来，不能坚持到最后。</t>
+        </is>
+      </c>
+      <c r="E3166" s="0" t="inlineStr">
+        <is>
+          <t>bỏ dở giữa chừng</t>
+        </is>
+      </c>
+      <c r="F3166" s="0" t="inlineStr">
+        <is>
+          <t>学中文最忌讳半途而废，很多人学了一半觉得难就放弃了，很可惜。</t>
+        </is>
+      </c>
+      <c r="G3166" s="0" t="inlineStr"/>
+      <c r="H3166" s="0" t="inlineStr"/>
+    </row>
+    <row r="3167">
+      <c r="A3167" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3167" s="0" t="inlineStr">
+        <is>
+          <t>衰退</t>
+        </is>
+      </c>
+      <c r="C3167" s="0" t="inlineStr">
+        <is>
+          <t>shuāituì</t>
+        </is>
+      </c>
+      <c r="D3167" s="0" t="inlineStr">
+        <is>
+          <t>（身体、能力、经济等）逐渐变差、变弱。</t>
+        </is>
+      </c>
+      <c r="E3167" s="0" t="inlineStr">
+        <is>
+          <t>suy thoái, suy giảm</t>
+        </is>
+      </c>
+      <c r="F3167" s="0" t="inlineStr">
+        <is>
+          <t>好几年不怎么说英语了，我感觉自己的英语口语能力都衰退了。</t>
+        </is>
+      </c>
+      <c r="G3167" s="0" t="inlineStr"/>
+      <c r="H3167" s="0" t="inlineStr"/>
+    </row>
+    <row r="3168">
+      <c r="A3168" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3168" s="0" t="inlineStr">
+        <is>
+          <t>著作</t>
+        </is>
+      </c>
+      <c r="C3168" s="0" t="inlineStr">
+        <is>
+          <t>zhùzuò</t>
+        </is>
+      </c>
+      <c r="D3168" s="0" t="inlineStr">
+        <is>
+          <t>写出来的文章或书，多指有学术或文学价值的作品。</t>
+        </is>
+      </c>
+      <c r="E3168" s="0" t="inlineStr">
+        <is>
+          <t>trước tác, tác phẩm (sách vở)</t>
+        </is>
+      </c>
+      <c r="F3168" s="0" t="inlineStr">
+        <is>
+          <t>那位语言学家关于汉语语法的著作，对我教HSK1-3很有帮助。</t>
+        </is>
+      </c>
+      <c r="G3168" s="0" t="inlineStr"/>
+      <c r="H3168" s="0" t="inlineStr"/>
+    </row>
+    <row r="3169">
+      <c r="A3169" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3169" s="0" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="C3169" s="0" t="inlineStr">
+        <is>
+          <t>fǎnshè</t>
+        </is>
+      </c>
+      <c r="D3169" s="0" t="inlineStr">
+        <is>
+          <t>光、声音等碰到物体后又弹回来。</t>
+        </is>
+      </c>
+      <c r="E3169" s="0" t="inlineStr">
+        <is>
+          <t>phản xạ</t>
+        </is>
+      </c>
+      <c r="F3169" s="0" t="inlineStr">
+        <is>
+          <t>教室里的白板反射着阳光，有点儿刺眼，我只好把窗帘拉上了。</t>
+        </is>
+      </c>
+      <c r="G3169" s="0" t="inlineStr"/>
+      <c r="H3169" s="0" t="inlineStr"/>
+    </row>
+    <row r="3170">
+      <c r="A3170" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3170" s="0" t="inlineStr">
+        <is>
+          <t>弱点</t>
+        </is>
+      </c>
+      <c r="C3170" s="0" t="inlineStr">
+        <is>
+          <t>ruòdiǎn</t>
+        </is>
+      </c>
+      <c r="D3170" s="0" t="inlineStr">
+        <is>
+          <t>一个人或事物不够好、比较薄弱的地方。</t>
+        </is>
+      </c>
+      <c r="E3170" s="0" t="inlineStr">
+        <is>
+          <t>điểm yếu, nhược điểm</t>
+        </is>
+      </c>
+      <c r="F3170" s="0" t="inlineStr">
+        <is>
+          <t>语法是我教学生时发现他们最大的弱点，所以我会多花时间讲练习。</t>
+        </is>
+      </c>
+      <c r="G3170" s="0" t="inlineStr"/>
+      <c r="H3170" s="0" t="inlineStr"/>
+    </row>
+    <row r="3171">
+      <c r="A3171" s="0" t="inlineStr">
+        <is>
+          <t>Bài 31</t>
+        </is>
+      </c>
+      <c r="B3171" s="0" t="inlineStr">
+        <is>
+          <t>虐待</t>
+        </is>
+      </c>
+      <c r="C3171" s="0" t="inlineStr">
+        <is>
+          <t>nüèdài</t>
+        </is>
+      </c>
+      <c r="D3171" s="0" t="inlineStr">
+        <is>
+          <t>用很残忍的方式对待人或动物，让对方受苦。</t>
+        </is>
+      </c>
+      <c r="E3171" s="0" t="inlineStr">
+        <is>
+          <t>ngược đãi, hành hạ</t>
+        </is>
+      </c>
+      <c r="F3171" s="0" t="inlineStr">
+        <is>
+          <t>新闻里报道有人虐待宠物，看了让人非常生气。</t>
+        </is>
+      </c>
+      <c r="G3171" s="0" t="inlineStr"/>
+      <c r="H3171" s="0" t="inlineStr"/>
+    </row>
+    <row r="3172">
+      <c r="A3172" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3172" s="0" t="inlineStr">
+        <is>
+          <t>背叛</t>
+        </is>
+      </c>
+      <c r="C3172" s="0" t="inlineStr">
+        <is>
+          <t>bèipàn</t>
+        </is>
+      </c>
+      <c r="D3172" s="0" t="inlineStr">
+        <is>
+          <t>违背原来的承诺或立场，站到对立的一方去。</t>
+        </is>
+      </c>
+      <c r="E3172" s="0" t="inlineStr">
+        <is>
+          <t>phản bội</t>
+        </is>
+      </c>
+      <c r="F3172" s="0" t="inlineStr">
+        <is>
+          <t>他为了升职背叛了一起共事多年的同事，这让我很失望。</t>
+        </is>
+      </c>
+      <c r="G3172" s="0" t="inlineStr"/>
+      <c r="H3172" s="0" t="inlineStr"/>
+    </row>
+    <row r="3173">
+      <c r="A3173" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3173" s="0" t="inlineStr">
+        <is>
+          <t>上进</t>
+        </is>
+      </c>
+      <c r="C3173" s="0" t="inlineStr">
+        <is>
+          <t>shàngjìn</t>
+        </is>
+      </c>
+      <c r="D3173" s="0" t="inlineStr">
+        <is>
+          <t>努力向更好的方向发展，不甘落后。</t>
+        </is>
+      </c>
+      <c r="E3173" s="0" t="inlineStr">
+        <is>
+          <t>cầu tiến, tiến bộ</t>
+        </is>
+      </c>
+      <c r="F3173" s="0" t="inlineStr">
+        <is>
+          <t>我教的HSK6学生虽然基础一般，但很上进，每天都主动复习生词。</t>
+        </is>
+      </c>
+      <c r="G3173" s="0" t="inlineStr"/>
+      <c r="H3173" s="0" t="inlineStr"/>
+    </row>
+    <row r="3174">
+      <c r="A3174" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3174" s="0" t="inlineStr">
+        <is>
+          <t>抱负</t>
+        </is>
+      </c>
+      <c r="C3174" s="0" t="inlineStr">
+        <is>
+          <t>bàofù</t>
+        </is>
+      </c>
+      <c r="D3174" s="0" t="inlineStr">
+        <is>
+          <t>远大的理想和志向。</t>
+        </is>
+      </c>
+      <c r="E3174" s="0" t="inlineStr">
+        <is>
+          <t>hoài bão</t>
+        </is>
+      </c>
+      <c r="F3174" s="0" t="inlineStr">
+        <is>
+          <t>我的抱负是通过HSK6考试，以后能在中国公司里用中文独立完成商务谈判。</t>
+        </is>
+      </c>
+      <c r="G3174" s="0" t="inlineStr"/>
+      <c r="H3174" s="0" t="inlineStr"/>
+    </row>
+    <row r="3175">
+      <c r="A3175" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3175" s="0" t="inlineStr">
+        <is>
+          <t>魄力</t>
+        </is>
+      </c>
+      <c r="C3175" s="0" t="inlineStr">
+        <is>
+          <t>pòlì</t>
+        </is>
+      </c>
+      <c r="D3175" s="0" t="inlineStr">
+        <is>
+          <t>做事果断、有胆量和决断力。</t>
+        </is>
+      </c>
+      <c r="E3175" s="0" t="inlineStr">
+        <is>
+          <t>khí phách, sự quyết đoán</t>
+        </is>
+      </c>
+      <c r="F3175" s="0" t="inlineStr">
+        <is>
+          <t>我们公司的中国老板做决定很有魄力，从不拖泥带水。</t>
+        </is>
+      </c>
+      <c r="G3175" s="0" t="inlineStr"/>
+      <c r="H3175" s="0" t="inlineStr"/>
+    </row>
+    <row r="3176">
+      <c r="A3176" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3176" s="0" t="inlineStr">
+        <is>
+          <t>开阔</t>
+        </is>
+      </c>
+      <c r="C3176" s="0" t="inlineStr">
+        <is>
+          <t>kāikuò</t>
+        </is>
+      </c>
+      <c r="D3176" s="0" t="inlineStr">
+        <is>
+          <t>心胸宽广，不计较小事；也指空间宽广。</t>
+        </is>
+      </c>
+      <c r="E3176" s="0" t="inlineStr">
+        <is>
+          <t>rộng mở, khoáng đạt</t>
+        </is>
+      </c>
+      <c r="F3176" s="0" t="inlineStr">
+        <is>
+          <t>在中国工作几年后，我的眼界变得比以前开阔多了。</t>
+        </is>
+      </c>
+      <c r="G3176" s="0" t="inlineStr"/>
+      <c r="H3176" s="0" t="inlineStr"/>
+    </row>
+    <row r="3177">
+      <c r="A3177" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3177" s="0" t="inlineStr">
+        <is>
+          <t>处境</t>
+        </is>
+      </c>
+      <c r="C3177" s="0" t="inlineStr">
+        <is>
+          <t>chǔjìng</t>
+        </is>
+      </c>
+      <c r="D3177" s="0" t="inlineStr">
+        <is>
+          <t>所处的境地或状况，多指不利的情况。</t>
+        </is>
+      </c>
+      <c r="E3177" s="0" t="inlineStr">
+        <is>
+          <t>hoàn cảnh, cảnh ngộ</t>
+        </is>
+      </c>
+      <c r="F3177" s="0" t="inlineStr">
+        <is>
+          <t>刚到中国工作时，我完全听不懂同事说话，处境很尴尬。</t>
+        </is>
+      </c>
+      <c r="G3177" s="0" t="inlineStr"/>
+      <c r="H3177" s="0" t="inlineStr"/>
+    </row>
+    <row r="3178">
+      <c r="A3178" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3178" s="0" t="inlineStr">
+        <is>
+          <t>打击</t>
+        </is>
+      </c>
+      <c r="C3178" s="0" t="inlineStr">
+        <is>
+          <t>dǎjī</t>
+        </is>
+      </c>
+      <c r="D3178" s="0" t="inlineStr">
+        <is>
+          <t>使受到严重的挫折或伤害。</t>
+        </is>
+      </c>
+      <c r="E3178" s="0" t="inlineStr">
+        <is>
+          <t>đả kích, giáng đòn</t>
+        </is>
+      </c>
+      <c r="F3178" s="0" t="inlineStr">
+        <is>
+          <t>第一次HSK6模拟考只考了180分，这对我是不小的打击。</t>
+        </is>
+      </c>
+      <c r="G3178" s="0" t="inlineStr"/>
+      <c r="H3178" s="0" t="inlineStr"/>
+    </row>
+    <row r="3179">
+      <c r="A3179" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3179" s="0" t="inlineStr">
+        <is>
+          <t>脆弱</t>
+        </is>
+      </c>
+      <c r="C3179" s="0" t="inlineStr">
+        <is>
+          <t>cuìruò</t>
+        </is>
+      </c>
+      <c r="D3179" s="0" t="inlineStr">
+        <is>
+          <t>禁不起挫折，意志薄弱。</t>
+        </is>
+      </c>
+      <c r="E3179" s="0" t="inlineStr">
+        <is>
+          <t>yếu đuối, mong manh</t>
+        </is>
+      </c>
+      <c r="F3179" s="0" t="inlineStr">
+        <is>
+          <t>教HSK1的孩子时，我发现有的孩子一被批评就哭，心理特别脆弱。</t>
+        </is>
+      </c>
+      <c r="G3179" s="0" t="inlineStr"/>
+      <c r="H3179" s="0" t="inlineStr"/>
+    </row>
+    <row r="3180">
+      <c r="A3180" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3180" s="0" t="inlineStr">
+        <is>
+          <t>榜样</t>
+        </is>
+      </c>
+      <c r="C3180" s="0" t="inlineStr">
+        <is>
+          <t>bǎngyàng</t>
+        </is>
+      </c>
+      <c r="D3180" s="0" t="inlineStr">
+        <is>
+          <t>值得别人学习的好例子。</t>
+        </is>
+      </c>
+      <c r="E3180" s="0" t="inlineStr">
+        <is>
+          <t>tấm gương</t>
+        </is>
+      </c>
+      <c r="F3180" s="0" t="inlineStr">
+        <is>
+          <t>那位坚持自学十年中文的网友，是我学习HSK6的榜样。</t>
+        </is>
+      </c>
+      <c r="G3180" s="0" t="inlineStr"/>
+      <c r="H3180" s="0" t="inlineStr"/>
+    </row>
+    <row r="3181">
+      <c r="A3181" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3181" s="0" t="inlineStr">
+        <is>
+          <t>光彩</t>
+        </is>
+      </c>
+      <c r="C3181" s="0" t="inlineStr">
+        <is>
+          <t>guāngcǎi</t>
+        </is>
+      </c>
+      <c r="D3181" s="0" t="inlineStr">
+        <is>
+          <t>光泽色彩，也指光荣、体面。</t>
+        </is>
+      </c>
+      <c r="E3181" s="0" t="inlineStr">
+        <is>
+          <t>vẻ vang, vinh dự</t>
+        </is>
+      </c>
+      <c r="F3181" s="0" t="inlineStr">
+        <is>
+          <t>能用中文给中国同事做培训，我觉得特别光彩。</t>
+        </is>
+      </c>
+      <c r="G3181" s="0" t="inlineStr"/>
+      <c r="H3181" s="0" t="inlineStr"/>
+    </row>
+    <row r="3182">
+      <c r="A3182" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3182" s="0" t="inlineStr">
+        <is>
+          <t>理智</t>
+        </is>
+      </c>
+      <c r="C3182" s="0" t="inlineStr">
+        <is>
+          <t>lǐzhì</t>
+        </is>
+      </c>
+      <c r="D3182" s="0" t="inlineStr">
+        <is>
+          <t>能用理性控制自己的情感和行为。</t>
+        </is>
+      </c>
+      <c r="E3182" s="0" t="inlineStr">
+        <is>
+          <t>lý trí, tỉnh táo</t>
+        </is>
+      </c>
+      <c r="F3182" s="0" t="inlineStr">
+        <is>
+          <t>面对客户的误解，我尽量保持理智，用中文慢慢解释清楚。</t>
+        </is>
+      </c>
+      <c r="G3182" s="0" t="inlineStr"/>
+      <c r="H3182" s="0" t="inlineStr"/>
+    </row>
+    <row r="3183">
+      <c r="A3183" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3183" s="0" t="inlineStr">
+        <is>
+          <t>哭泣</t>
+        </is>
+      </c>
+      <c r="C3183" s="0" t="inlineStr">
+        <is>
+          <t>kūqì</t>
+        </is>
+      </c>
+      <c r="D3183" s="0" t="inlineStr">
+        <is>
+          <t>因伤心而流泪。</t>
+        </is>
+      </c>
+      <c r="E3183" s="0" t="inlineStr">
+        <is>
+          <t>khóc</t>
+        </is>
+      </c>
+      <c r="F3183" s="0" t="inlineStr">
+        <is>
+          <t>收到HSKK没通过的成绩单那天，我一个人在办公室哭泣了很久。</t>
+        </is>
+      </c>
+      <c r="G3183" s="0" t="inlineStr"/>
+      <c r="H3183" s="0" t="inlineStr"/>
+    </row>
+    <row r="3184">
+      <c r="A3184" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3184" s="0" t="inlineStr">
+        <is>
+          <t>否决</t>
+        </is>
+      </c>
+      <c r="C3184" s="0" t="inlineStr">
+        <is>
+          <t>fǒujué</t>
+        </is>
+      </c>
+      <c r="D3184" s="0" t="inlineStr">
+        <is>
+          <t>不同意，使提议不能通过。</t>
+        </is>
+      </c>
+      <c r="E3184" s="0" t="inlineStr">
+        <is>
+          <t>phủ quyết, bác bỏ</t>
+        </is>
+      </c>
+      <c r="F3184" s="0" t="inlineStr">
+        <is>
+          <t>我提出的教学计划被中方负责人否决了，因为进度太快。</t>
+        </is>
+      </c>
+      <c r="G3184" s="0" t="inlineStr"/>
+      <c r="H3184" s="0" t="inlineStr"/>
+    </row>
+    <row r="3185">
+      <c r="A3185" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3185" s="0" t="inlineStr">
+        <is>
+          <t>出息</t>
+        </is>
+      </c>
+      <c r="C3185" s="0" t="inlineStr">
+        <is>
+          <t>chūxi</t>
+        </is>
+      </c>
+      <c r="D3185" s="0" t="inlineStr">
+        <is>
+          <t>前途，出路（多用于"有出息"）。</t>
+        </is>
+      </c>
+      <c r="E3185" s="0" t="inlineStr">
+        <is>
+          <t>tiền đồ, triển vọng</t>
+        </is>
+      </c>
+      <c r="F3185" s="0" t="inlineStr">
+        <is>
+          <t>妈妈常说，学好中文以后才会有出息。</t>
+        </is>
+      </c>
+      <c r="G3185" s="0" t="inlineStr"/>
+      <c r="H3185" s="0" t="inlineStr"/>
+    </row>
+    <row r="3186">
+      <c r="A3186" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3186" s="0" t="inlineStr">
+        <is>
+          <t>含糊</t>
+        </is>
+      </c>
+      <c r="C3186" s="0" t="inlineStr">
+        <is>
+          <t>hánhu</t>
+        </is>
+      </c>
+      <c r="D3186" s="0" t="inlineStr">
+        <is>
+          <t>不清楚，不明确。</t>
+        </is>
+      </c>
+      <c r="E3186" s="0" t="inlineStr">
+        <is>
+          <t>mập mờ, không rõ ràng</t>
+        </is>
+      </c>
+      <c r="F3186" s="0" t="inlineStr">
+        <is>
+          <t>学生问我这个语法点的用法，我不能含糊，得查清楚再回答。</t>
+        </is>
+      </c>
+      <c r="G3186" s="0" t="inlineStr"/>
+      <c r="H3186" s="0" t="inlineStr"/>
+    </row>
+    <row r="3187">
+      <c r="A3187" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3187" s="0" t="inlineStr">
+        <is>
+          <t>束缚</t>
+        </is>
+      </c>
+      <c r="C3187" s="0" t="inlineStr">
+        <is>
+          <t>shùfù</t>
+        </is>
+      </c>
+      <c r="D3187" s="0" t="inlineStr">
+        <is>
+          <t>限制约束，使不能自由行动。</t>
+        </is>
+      </c>
+      <c r="E3187" s="0" t="inlineStr">
+        <is>
+          <t>ràng buộc, trói buộc</t>
+        </is>
+      </c>
+      <c r="F3187" s="0" t="inlineStr">
+        <is>
+          <t>刚学中文时，我总被母语的语法习惯束缚，说话很不自然。</t>
+        </is>
+      </c>
+      <c r="G3187" s="0" t="inlineStr"/>
+      <c r="H3187" s="0" t="inlineStr"/>
+    </row>
+    <row r="3188">
+      <c r="A3188" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3188" s="0" t="inlineStr">
+        <is>
+          <t>魔鬼</t>
+        </is>
+      </c>
+      <c r="C3188" s="0" t="inlineStr">
+        <is>
+          <t>móguǐ</t>
+        </is>
+      </c>
+      <c r="D3188" s="0" t="inlineStr">
+        <is>
+          <t>传说中害人的恶鬼，也比喻凶恶的人。</t>
+        </is>
+      </c>
+      <c r="E3188" s="0" t="inlineStr">
+        <is>
+          <t>ác quỷ, ma quỷ</t>
+        </is>
+      </c>
+      <c r="F3188" s="0" t="inlineStr">
+        <is>
+          <t>那个中文老师批改作业特别严格，学生私下叫她"魔鬼老师"。</t>
+        </is>
+      </c>
+      <c r="G3188" s="0" t="inlineStr"/>
+      <c r="H3188" s="0" t="inlineStr"/>
+    </row>
+    <row r="3189">
+      <c r="A3189" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3189" s="0" t="inlineStr">
+        <is>
+          <t>神仙</t>
+        </is>
+      </c>
+      <c r="C3189" s="0" t="inlineStr">
+        <is>
+          <t>shénxiān</t>
+        </is>
+      </c>
+      <c r="D3189" s="0" t="inlineStr">
+        <is>
+          <t>神话中长生不老、法力无边的人物。</t>
+        </is>
+      </c>
+      <c r="E3189" s="0" t="inlineStr">
+        <is>
+          <t>thần tiên</t>
+        </is>
+      </c>
+      <c r="F3189" s="0" t="inlineStr">
+        <is>
+          <t>给HSK1的孩子们讲神仙的故事，比直接讲语法有意思多了。</t>
+        </is>
+      </c>
+      <c r="G3189" s="0" t="inlineStr"/>
+      <c r="H3189" s="0" t="inlineStr"/>
+    </row>
+    <row r="3190">
+      <c r="A3190" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3190" s="0" t="inlineStr">
+        <is>
+          <t>健全</t>
+        </is>
+      </c>
+      <c r="C3190" s="0" t="inlineStr">
+        <is>
+          <t>jiànquán</t>
+        </is>
+      </c>
+      <c r="D3190" s="0" t="inlineStr">
+        <is>
+          <t>完善，没有缺陷。</t>
+        </is>
+      </c>
+      <c r="E3190" s="0" t="inlineStr">
+        <is>
+          <t>hoàn thiện, kiện toàn</t>
+        </is>
+      </c>
+      <c r="F3190" s="0" t="inlineStr">
+        <is>
+          <t>一个健全的学习计划应该包括听说读写四个方面。</t>
+        </is>
+      </c>
+      <c r="G3190" s="0" t="inlineStr"/>
+      <c r="H3190" s="0" t="inlineStr"/>
+    </row>
+    <row r="3191">
+      <c r="A3191" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3191" s="0" t="inlineStr">
+        <is>
+          <t>塌</t>
+        </is>
+      </c>
+      <c r="C3191" s="0" t="inlineStr">
+        <is>
+          <t>tā</t>
+        </is>
+      </c>
+      <c r="D3191" s="0" t="inlineStr">
+        <is>
+          <t>陷下去，倒下来。</t>
+        </is>
+      </c>
+      <c r="E3191" s="0" t="inlineStr">
+        <is>
+          <t>sập, đổ</t>
+        </is>
+      </c>
+      <c r="F3191" s="0" t="inlineStr">
+        <is>
+          <t>老家的老房子年久失修，去年台风一来就塌了一角。</t>
+        </is>
+      </c>
+      <c r="G3191" s="0" t="inlineStr"/>
+      <c r="H3191" s="0" t="inlineStr"/>
+    </row>
+    <row r="3192">
+      <c r="A3192" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3192" s="0" t="inlineStr">
+        <is>
+          <t>反之</t>
+        </is>
+      </c>
+      <c r="C3192" s="0" t="inlineStr">
+        <is>
+          <t>fǎnzhī</t>
+        </is>
+      </c>
+      <c r="D3192" s="0" t="inlineStr">
+        <is>
+          <t>与此相反，从相反的方面说。</t>
+        </is>
+      </c>
+      <c r="E3192" s="0" t="inlineStr">
+        <is>
+          <t>ngược lại</t>
+        </is>
+      </c>
+      <c r="F3192" s="0" t="inlineStr">
+        <is>
+          <t>每天坚持读课文，中文水平就会进步；反之，三天打鱼两天晒网，很快就会退步。</t>
+        </is>
+      </c>
+      <c r="G3192" s="0" t="inlineStr"/>
+      <c r="H3192" s="0" t="inlineStr"/>
+    </row>
+    <row r="3193">
+      <c r="A3193" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3193" s="0" t="inlineStr">
+        <is>
+          <t>娃娃</t>
+        </is>
+      </c>
+      <c r="C3193" s="0" t="inlineStr">
+        <is>
+          <t>wáwa</t>
+        </is>
+      </c>
+      <c r="D3193" s="0" t="inlineStr">
+        <is>
+          <t>小孩子。</t>
+        </is>
+      </c>
+      <c r="E3193" s="0" t="inlineStr">
+        <is>
+          <t>em bé, đứa trẻ</t>
+        </is>
+      </c>
+      <c r="F3193" s="0" t="inlineStr">
+        <is>
+          <t>我教的HSK1班里最小的娃娃才五岁，发音却很标准。</t>
+        </is>
+      </c>
+      <c r="G3193" s="0" t="inlineStr"/>
+      <c r="H3193" s="0" t="inlineStr"/>
+    </row>
+    <row r="3194">
+      <c r="A3194" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3194" s="0" t="inlineStr">
+        <is>
+          <t>鞭策</t>
+        </is>
+      </c>
+      <c r="C3194" s="0" t="inlineStr">
+        <is>
+          <t>biāncè</t>
+        </is>
+      </c>
+      <c r="D3194" s="0" t="inlineStr">
+        <is>
+          <t>用言语或行动督促、激励人进步。</t>
+        </is>
+      </c>
+      <c r="E3194" s="0" t="inlineStr">
+        <is>
+          <t>thúc đẩy, khích lệ</t>
+        </is>
+      </c>
+      <c r="F3194" s="0" t="inlineStr">
+        <is>
+          <t>老师严格的要求一直鞭策着我坚持每天背生词。</t>
+        </is>
+      </c>
+      <c r="G3194" s="0" t="inlineStr"/>
+      <c r="H3194" s="0" t="inlineStr"/>
+    </row>
+    <row r="3195">
+      <c r="A3195" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3195" s="0" t="inlineStr">
+        <is>
+          <t>潜移默化</t>
+        </is>
+      </c>
+      <c r="C3195" s="0" t="inlineStr">
+        <is>
+          <t>qiányímòhuà</t>
+        </is>
+      </c>
+      <c r="D3195" s="0" t="inlineStr">
+        <is>
+          <t>在不知不觉中受到影响而发生变化。</t>
+        </is>
+      </c>
+      <c r="E3195" s="0" t="inlineStr">
+        <is>
+          <t>ảnh hưởng ngấm ngầm, thay đổi dần dần</t>
+        </is>
+      </c>
+      <c r="F3195" s="0" t="inlineStr">
+        <is>
+          <t>每天和中国同事一起吃饭聊天，我的口语在潜移默化中提高了不少。</t>
+        </is>
+      </c>
+      <c r="G3195" s="0" t="inlineStr"/>
+      <c r="H3195" s="0" t="inlineStr"/>
+    </row>
+    <row r="3196">
+      <c r="A3196" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3196" s="0" t="inlineStr">
+        <is>
+          <t>赋予</t>
+        </is>
+      </c>
+      <c r="C3196" s="0" t="inlineStr">
+        <is>
+          <t>fùyǔ</t>
+        </is>
+      </c>
+      <c r="D3196" s="0" t="inlineStr">
+        <is>
+          <t>交给，给予（多用于重要的责任、意义等）。</t>
+        </is>
+      </c>
+      <c r="E3196" s="0" t="inlineStr">
+        <is>
+          <t>trao cho, ban cho</t>
+        </is>
+      </c>
+      <c r="F3196" s="0" t="inlineStr">
+        <is>
+          <t>公司把培训新员工中文的重任赋予了我，我感到既有压力又很荣幸。</t>
+        </is>
+      </c>
+      <c r="G3196" s="0" t="inlineStr"/>
+      <c r="H3196" s="0" t="inlineStr"/>
+    </row>
+    <row r="3197">
+      <c r="A3197" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3197" s="0" t="inlineStr">
+        <is>
+          <t>鄙视</t>
+        </is>
+      </c>
+      <c r="C3197" s="0" t="inlineStr">
+        <is>
+          <t>bǐshì</t>
+        </is>
+      </c>
+      <c r="D3197" s="0" t="inlineStr">
+        <is>
+          <t>轻视，看不起。</t>
+        </is>
+      </c>
+      <c r="E3197" s="0" t="inlineStr">
+        <is>
+          <t>khinh miệt, coi thường</t>
+        </is>
+      </c>
+      <c r="F3197" s="0" t="inlineStr">
+        <is>
+          <t>我从不鄙视说错语法的学生，因为犯错才是学习的必经过程。</t>
+        </is>
+      </c>
+      <c r="G3197" s="0" t="inlineStr"/>
+      <c r="H3197" s="0" t="inlineStr"/>
+    </row>
+    <row r="3198">
+      <c r="A3198" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3198" s="0" t="inlineStr">
+        <is>
+          <t>扮演</t>
+        </is>
+      </c>
+      <c r="C3198" s="0" t="inlineStr">
+        <is>
+          <t>bànyǎn</t>
+        </is>
+      </c>
+      <c r="D3198" s="0" t="inlineStr">
+        <is>
+          <t>在戏剧或活动中充当某种角色。</t>
+        </is>
+      </c>
+      <c r="E3198" s="0" t="inlineStr">
+        <is>
+          <t>đóng vai</t>
+        </is>
+      </c>
+      <c r="F3198" s="0" t="inlineStr">
+        <is>
+          <t>在HSK1课堂上，我常常扮演不同的角色，跟孩子们做对话练习。</t>
+        </is>
+      </c>
+      <c r="G3198" s="0" t="inlineStr"/>
+      <c r="H3198" s="0" t="inlineStr"/>
+    </row>
+    <row r="3199">
+      <c r="A3199" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3199" s="0" t="inlineStr">
+        <is>
+          <t>讥笑</t>
+        </is>
+      </c>
+      <c r="C3199" s="0" t="inlineStr">
+        <is>
+          <t>jīxiào</t>
+        </is>
+      </c>
+      <c r="D3199" s="0" t="inlineStr">
+        <is>
+          <t>用言语讽刺、嘲笑别人。</t>
+        </is>
+      </c>
+      <c r="E3199" s="0" t="inlineStr">
+        <is>
+          <t>chế giễu, cười nhạo</t>
+        </is>
+      </c>
+      <c r="F3199" s="0" t="inlineStr">
+        <is>
+          <t>有些学生因为发音不标准被同学讥笑，从此就越来越不敢开口说中文了。</t>
+        </is>
+      </c>
+      <c r="G3199" s="0" t="inlineStr"/>
+      <c r="H3199" s="0" t="inlineStr"/>
+    </row>
+    <row r="3200">
+      <c r="A3200" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3200" s="0" t="inlineStr">
+        <is>
+          <t>恶心</t>
+        </is>
+      </c>
+      <c r="C3200" s="0" t="inlineStr">
+        <is>
+          <t>ěxin</t>
+        </is>
+      </c>
+      <c r="D3200" s="0" t="inlineStr">
+        <is>
+          <t>使人想呕吐，也指令人厌恶。</t>
+        </is>
+      </c>
+      <c r="E3200" s="0" t="inlineStr">
+        <is>
+          <t>buồn nôn, ghê tởm</t>
+        </is>
+      </c>
+      <c r="F3200" s="0" t="inlineStr">
+        <is>
+          <t>第一次吃臭豆腐，那股味道让我觉得有点恶心，可吃惯了反而喜欢。</t>
+        </is>
+      </c>
+      <c r="G3200" s="0" t="inlineStr"/>
+      <c r="H3200" s="0" t="inlineStr"/>
+    </row>
+    <row r="3201">
+      <c r="A3201" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3201" s="0" t="inlineStr">
+        <is>
+          <t>体面</t>
+        </is>
+      </c>
+      <c r="C3201" s="0" t="inlineStr">
+        <is>
+          <t>tǐmiàn</t>
+        </is>
+      </c>
+      <c r="D3201" s="0" t="inlineStr">
+        <is>
+          <t>有面子，光彩；（外表）大方得体。</t>
+        </is>
+      </c>
+      <c r="E3201" s="0" t="inlineStr">
+        <is>
+          <t>thể diện, đàng hoàng</t>
+        </is>
+      </c>
+      <c r="F3201" s="0" t="inlineStr">
+        <is>
+          <t>通过HSK6以后，我终于能体面地跟中国客户全程用中文开会了。</t>
+        </is>
+      </c>
+      <c r="G3201" s="0" t="inlineStr"/>
+      <c r="H3201" s="0" t="inlineStr"/>
+    </row>
+    <row r="3202">
+      <c r="A3202" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3202" s="0" t="inlineStr">
+        <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="C3202" s="0" t="inlineStr">
+        <is>
+          <t>jīsù</t>
+        </is>
+      </c>
+      <c r="D3202" s="0" t="inlineStr">
+        <is>
+          <t>生物体内分泌的、能调节生理功能的物质。</t>
+        </is>
+      </c>
+      <c r="E3202" s="0" t="inlineStr">
+        <is>
+          <t>hormone, kích thích tố</t>
+        </is>
+      </c>
+      <c r="F3202" s="0" t="inlineStr">
+        <is>
+          <t>压力太大时，身体会分泌一种叫"压力激素"的物质，让人更容易疲劳。</t>
+        </is>
+      </c>
+      <c r="G3202" s="0" t="inlineStr"/>
+      <c r="H3202" s="0" t="inlineStr"/>
+    </row>
+    <row r="3203">
+      <c r="A3203" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3203" s="0" t="inlineStr">
+        <is>
+          <t>转移</t>
+        </is>
+      </c>
+      <c r="C3203" s="0" t="inlineStr">
+        <is>
+          <t>zhuǎnyí</t>
+        </is>
+      </c>
+      <c r="D3203" s="0" t="inlineStr">
+        <is>
+          <t>从一个地方或状态改变到另一个地方或状态。</t>
+        </is>
+      </c>
+      <c r="E3203" s="0" t="inlineStr">
+        <is>
+          <t>chuyển dời, chuyển hướng</t>
+        </is>
+      </c>
+      <c r="F3203" s="0" t="inlineStr">
+        <is>
+          <t>考试压力太大的时候，我会把注意力转移到运动上，跑完步心情就好多了。</t>
+        </is>
+      </c>
+      <c r="G3203" s="0" t="inlineStr"/>
+      <c r="H3203" s="0" t="inlineStr"/>
+    </row>
+    <row r="3204">
+      <c r="A3204" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3204" s="0" t="inlineStr">
+        <is>
+          <t>喉咙</t>
+        </is>
+      </c>
+      <c r="C3204" s="0" t="inlineStr">
+        <is>
+          <t>hóulóng</t>
+        </is>
+      </c>
+      <c r="D3204" s="0" t="inlineStr">
+        <is>
+          <t>咽喉，脖子里连接口腔和气管、食道的部位。</t>
+        </is>
+      </c>
+      <c r="E3204" s="0" t="inlineStr">
+        <is>
+          <t>cổ họng</t>
+        </is>
+      </c>
+      <c r="F3204" s="0" t="inlineStr">
+        <is>
+          <t>在办公室讲了一天中文，晚上喉咙常常又干又疼。</t>
+        </is>
+      </c>
+      <c r="G3204" s="0" t="inlineStr"/>
+      <c r="H3204" s="0" t="inlineStr"/>
+    </row>
+    <row r="3205">
+      <c r="A3205" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3205" s="0" t="inlineStr">
+        <is>
+          <t>鼻涕</t>
+        </is>
+      </c>
+      <c r="C3205" s="0" t="inlineStr">
+        <is>
+          <t>bítì</t>
+        </is>
+      </c>
+      <c r="D3205" s="0" t="inlineStr">
+        <is>
+          <t>鼻子里分泌的液体。</t>
+        </is>
+      </c>
+      <c r="E3205" s="0" t="inlineStr">
+        <is>
+          <t>nước mũi</t>
+        </is>
+      </c>
+      <c r="F3205" s="0" t="inlineStr">
+        <is>
+          <t>北方的冬天太干燥，我一到室外冷风一吹就直流鼻涕。</t>
+        </is>
+      </c>
+      <c r="G3205" s="0" t="inlineStr"/>
+      <c r="H3205" s="0" t="inlineStr"/>
+    </row>
+    <row r="3206">
+      <c r="A3206" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3206" s="0" t="inlineStr">
+        <is>
+          <t>之际</t>
+        </is>
+      </c>
+      <c r="C3206" s="0" t="inlineStr">
+        <is>
+          <t>zhījì</t>
+        </is>
+      </c>
+      <c r="D3206" s="0" t="inlineStr">
+        <is>
+          <t>表示正当某个时刻或阶段的时候，多用于书面语。</t>
+        </is>
+      </c>
+      <c r="E3206" s="0" t="inlineStr">
+        <is>
+          <t>vào lúc, đúng dịp (thời điểm, văn viết)</t>
+        </is>
+      </c>
+      <c r="F3206" s="0" t="inlineStr">
+        <is>
+          <t>期末考试之际，我把所有生词都重新整理了一遍。</t>
+        </is>
+      </c>
+      <c r="G3206" s="0" t="inlineStr"/>
+      <c r="H3206" s="0" t="inlineStr"/>
+    </row>
+    <row r="3207">
+      <c r="A3207" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3207" s="0" t="inlineStr">
+        <is>
+          <t>修复</t>
+        </is>
+      </c>
+      <c r="C3207" s="0" t="inlineStr">
+        <is>
+          <t>xiūfù</t>
+        </is>
+      </c>
+      <c r="D3207" s="0" t="inlineStr">
+        <is>
+          <t>修理使恢复原状。</t>
+        </is>
+      </c>
+      <c r="E3207" s="0" t="inlineStr">
+        <is>
+          <t>phục hồi, sửa chữa</t>
+        </is>
+      </c>
+      <c r="F3207" s="0" t="inlineStr">
+        <is>
+          <t>说错话伤了同事的心以后，我花了好几天时间才把关系修复好。</t>
+        </is>
+      </c>
+      <c r="G3207" s="0" t="inlineStr"/>
+      <c r="H3207" s="0" t="inlineStr"/>
+    </row>
+    <row r="3208">
+      <c r="A3208" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3208" s="0" t="inlineStr">
+        <is>
+          <t>宣泄</t>
+        </is>
+      </c>
+      <c r="C3208" s="0" t="inlineStr">
+        <is>
+          <t>xuānxiè</t>
+        </is>
+      </c>
+      <c r="D3208" s="0" t="inlineStr">
+        <is>
+          <t>把积压的情绪释放出来。</t>
+        </is>
+      </c>
+      <c r="E3208" s="0" t="inlineStr">
+        <is>
+          <t>giải tỏa, xả (cảm xúc)</t>
+        </is>
+      </c>
+      <c r="F3208" s="0" t="inlineStr">
+        <is>
+          <t>工作压力大的时候，我喜欢用写日记的方式宣泄情绪。</t>
+        </is>
+      </c>
+      <c r="G3208" s="0" t="inlineStr"/>
+      <c r="H3208" s="0" t="inlineStr"/>
+    </row>
+    <row r="3209">
+      <c r="A3209" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3209" s="0" t="inlineStr">
+        <is>
+          <t>许可</t>
+        </is>
+      </c>
+      <c r="C3209" s="0" t="inlineStr">
+        <is>
+          <t>xǔkě</t>
+        </is>
+      </c>
+      <c r="D3209" s="0" t="inlineStr">
+        <is>
+          <t>准许，同意（多用于正式、书面场合，也可作名词）。</t>
+        </is>
+      </c>
+      <c r="E3209" s="0" t="inlineStr">
+        <is>
+          <t>cho phép, giấy phép</t>
+        </is>
+      </c>
+      <c r="F3209" s="0" t="inlineStr">
+        <is>
+          <t>没有得到公司许可，我们不能随便把客户资料带出办公室。</t>
+        </is>
+      </c>
+      <c r="G3209" s="0" t="inlineStr"/>
+      <c r="H3209" s="0" t="inlineStr"/>
+    </row>
+    <row r="3210">
+      <c r="A3210" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3210" s="0" t="inlineStr">
+        <is>
+          <t>倡导</t>
+        </is>
+      </c>
+      <c r="C3210" s="0" t="inlineStr">
+        <is>
+          <t>chàngdǎo</t>
+        </is>
+      </c>
+      <c r="D3210" s="0" t="inlineStr">
+        <is>
+          <t>首先提出并加以提倡。</t>
+        </is>
+      </c>
+      <c r="E3210" s="0" t="inlineStr">
+        <is>
+          <t>đề xướng, cổ vũ</t>
+        </is>
+      </c>
+      <c r="F3210" s="0" t="inlineStr">
+        <is>
+          <t>这家公司一直倡导员工每天抽半小时学一门外语。</t>
+        </is>
+      </c>
+      <c r="G3210" s="0" t="inlineStr"/>
+      <c r="H3210" s="0" t="inlineStr"/>
+    </row>
+    <row r="3211">
+      <c r="A3211" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3211" s="0" t="inlineStr">
+        <is>
+          <t>情理</t>
+        </is>
+      </c>
+      <c r="C3211" s="0" t="inlineStr">
+        <is>
+          <t>qínglǐ</t>
+        </is>
+      </c>
+      <c r="D3211" s="0" t="inlineStr">
+        <is>
+          <t>人之常情和事情的道理。</t>
+        </is>
+      </c>
+      <c r="E3211" s="0" t="inlineStr">
+        <is>
+          <t>lẽ thường, đạo lý thông thường</t>
+        </is>
+      </c>
+      <c r="F3211" s="0" t="inlineStr">
+        <is>
+          <t>学生一时听不懂老师讲的语法，这是情理之中的事，不必着急。</t>
+        </is>
+      </c>
+      <c r="G3211" s="0" t="inlineStr"/>
+      <c r="H3211" s="0" t="inlineStr"/>
+    </row>
+    <row r="3212">
+      <c r="A3212" s="0" t="inlineStr">
+        <is>
+          <t>Bài 32</t>
+        </is>
+      </c>
+      <c r="B3212" s="0" t="inlineStr">
+        <is>
+          <t>允许</t>
+        </is>
+      </c>
+      <c r="C3212" s="0" t="inlineStr">
+        <is>
+          <t>yǔnxǔ</t>
+        </is>
+      </c>
+      <c r="D3212" s="0" t="inlineStr">
+        <is>
+          <t>准许，同意（口语中常用，后面可以直接带宾语）。</t>
+        </is>
+      </c>
+      <c r="E3212" s="0" t="inlineStr">
+        <is>
+          <t>cho phép</t>
+        </is>
+      </c>
+      <c r="F3212" s="0" t="inlineStr">
+        <is>
+          <t>老师允许我们上课时用手机查生词的意思。</t>
+        </is>
+      </c>
+      <c r="G3212" s="0" t="inlineStr"/>
+      <c r="H3212" s="0" t="inlineStr"/>
+    </row>
+    <row r="3213">
+      <c r="A3213" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3213" s="0" t="inlineStr">
+        <is>
+          <t>为期</t>
+        </is>
+      </c>
+      <c r="C3213" s="0" t="inlineStr">
+        <is>
+          <t>wéiqī</t>
+        </is>
+      </c>
+      <c r="D3213" s="0" t="inlineStr">
+        <is>
+          <t>以某段时间为限度，从开始到结束共经历多长时间。</t>
+        </is>
+      </c>
+      <c r="E3213" s="0" t="inlineStr">
+        <is>
+          <t>kéo dài trong khoảng (thời hạn là)</t>
+        </is>
+      </c>
+      <c r="F3213" s="0" t="inlineStr">
+        <is>
+          <t>我报名参加了一个为期三个月的HSK6冲刺班，每天都要交口语作业。</t>
+        </is>
+      </c>
+      <c r="G3213" s="0" t="inlineStr"/>
+      <c r="H3213" s="0" t="inlineStr"/>
+    </row>
+    <row r="3214">
+      <c r="A3214" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3214" s="0" t="inlineStr">
+        <is>
+          <t>桥梁</t>
+        </is>
+      </c>
+      <c r="C3214" s="0" t="inlineStr">
+        <is>
+          <t>qiáoliáng</t>
+        </is>
+      </c>
+      <c r="D3214" s="0" t="inlineStr">
+        <is>
+          <t>架在河流、山谷或道路上方便通行的建筑物；也比喻沟通两者的中间事物。</t>
+        </is>
+      </c>
+      <c r="E3214" s="0" t="inlineStr">
+        <is>
+          <t>cầu; (nghĩa bóng) cầu nối</t>
+        </is>
+      </c>
+      <c r="F3214" s="0" t="inlineStr">
+        <is>
+          <t>我常跟中国同事说，语言是文化交流的桥梁，学好汉语能让我更好地融入这里的工作环境。</t>
+        </is>
+      </c>
+      <c r="G3214" s="0" t="inlineStr"/>
+      <c r="H3214" s="0" t="inlineStr"/>
+    </row>
+    <row r="3215">
+      <c r="A3215" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3215" s="0" t="inlineStr">
+        <is>
+          <t>平原</t>
+        </is>
+      </c>
+      <c r="C3215" s="0" t="inlineStr">
+        <is>
+          <t>píngyuán</t>
+        </is>
+      </c>
+      <c r="D3215" s="0" t="inlineStr">
+        <is>
+          <t>地势平坦、面积广阔的陆地。</t>
+        </is>
+      </c>
+      <c r="E3215" s="0" t="inlineStr">
+        <is>
+          <t>đồng bằng</t>
+        </is>
+      </c>
+      <c r="F3215" s="0" t="inlineStr">
+        <is>
+          <t>我工作的城市周围都是平原，没有山，所以我周末只能在公园里跑步锻炼。</t>
+        </is>
+      </c>
+      <c r="G3215" s="0" t="inlineStr"/>
+      <c r="H3215" s="0" t="inlineStr"/>
+    </row>
+    <row r="3216">
+      <c r="A3216" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3216" s="0" t="inlineStr">
+        <is>
+          <t>夹杂</t>
+        </is>
+      </c>
+      <c r="C3216" s="0" t="inlineStr">
+        <is>
+          <t>jiāzá</t>
+        </is>
+      </c>
+      <c r="D3216" s="0" t="inlineStr">
+        <is>
+          <t>别的事物混在主要事物里面。</t>
+        </is>
+      </c>
+      <c r="E3216" s="0" t="inlineStr">
+        <is>
+          <t>pha trộn, lẫn vào</t>
+        </is>
+      </c>
+      <c r="F3216" s="0" t="inlineStr">
+        <is>
+          <t>我说中文的时候，有时会不自觉地夹杂着一些越南语词，同事听了觉得很有意思。</t>
+        </is>
+      </c>
+      <c r="G3216" s="0" t="inlineStr"/>
+      <c r="H3216" s="0" t="inlineStr"/>
+    </row>
+    <row r="3217">
+      <c r="A3217" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3217" s="0" t="inlineStr">
+        <is>
+          <t>呼啸</t>
+        </is>
+      </c>
+      <c r="C3217" s="0" t="inlineStr">
+        <is>
+          <t>hūxiào</t>
+        </is>
+      </c>
+      <c r="D3217" s="0" t="inlineStr">
+        <is>
+          <t>发出高而长的声音，多形容风、车等。</t>
+        </is>
+      </c>
+      <c r="E3217" s="0" t="inlineStr">
+        <is>
+          <t>rít lên, gào rú (gió, xe...)</t>
+        </is>
+      </c>
+      <c r="F3217" s="0" t="inlineStr">
+        <is>
+          <t>冬天在中国北方，寒风呼啸着刮过窗户，我只能裹紧外套去上班。</t>
+        </is>
+      </c>
+      <c r="G3217" s="0" t="inlineStr"/>
+      <c r="H3217" s="0" t="inlineStr"/>
+    </row>
+    <row r="3218">
+      <c r="A3218" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3218" s="0" t="inlineStr">
+        <is>
+          <t>宽敞</t>
+        </is>
+      </c>
+      <c r="C3218" s="0" t="inlineStr">
+        <is>
+          <t>kuānchang</t>
+        </is>
+      </c>
+      <c r="D3218" s="0" t="inlineStr">
+        <is>
+          <t>地方很大，不狭窄。</t>
+        </is>
+      </c>
+      <c r="E3218" s="0" t="inlineStr">
+        <is>
+          <t>rộng rãi</t>
+        </is>
+      </c>
+      <c r="F3218" s="0" t="inlineStr">
+        <is>
+          <t>我们公司新办公室很宽敞，光线也好，我每天备课教HSK1-3的学生都很有心情。</t>
+        </is>
+      </c>
+      <c r="G3218" s="0" t="inlineStr"/>
+      <c r="H3218" s="0" t="inlineStr"/>
+    </row>
+    <row r="3219">
+      <c r="A3219" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3219" s="0" t="inlineStr">
+        <is>
+          <t>齐全</t>
+        </is>
+      </c>
+      <c r="C3219" s="0" t="inlineStr">
+        <is>
+          <t>qíquán</t>
+        </is>
+      </c>
+      <c r="D3219" s="0" t="inlineStr">
+        <is>
+          <t>应该有的东西都有，一样不缺。</t>
+        </is>
+      </c>
+      <c r="E3219" s="0" t="inlineStr">
+        <is>
+          <t>đầy đủ, hoàn chỉnh</t>
+        </is>
+      </c>
+      <c r="F3219" s="0" t="inlineStr">
+        <is>
+          <t>我教HSK1的教材和教具都很齐全，学生学拼音的时候用起来很方便。</t>
+        </is>
+      </c>
+      <c r="G3219" s="0" t="inlineStr"/>
+      <c r="H3219" s="0" t="inlineStr"/>
+    </row>
+    <row r="3220">
+      <c r="A3220" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3220" s="0" t="inlineStr">
+        <is>
+          <t>封闭</t>
+        </is>
+      </c>
+      <c r="C3220" s="0" t="inlineStr">
+        <is>
+          <t>fēngbì</t>
+        </is>
+      </c>
+      <c r="D3220" s="0" t="inlineStr">
+        <is>
+          <t>与外界隔绝，不让通行或接触。</t>
+        </is>
+      </c>
+      <c r="E3220" s="0" t="inlineStr">
+        <is>
+          <t>đóng kín, bế quan</t>
+        </is>
+      </c>
+      <c r="F3220" s="0" t="inlineStr">
+        <is>
+          <t>备考HSK6的最后一周，我把手机封闭起来，专心刷真题。</t>
+        </is>
+      </c>
+      <c r="G3220" s="0" t="inlineStr"/>
+      <c r="H3220" s="0" t="inlineStr"/>
+    </row>
+    <row r="3221">
+      <c r="A3221" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3221" s="0" t="inlineStr">
+        <is>
+          <t>符号</t>
+        </is>
+      </c>
+      <c r="C3221" s="0" t="inlineStr">
+        <is>
+          <t>fúhào</t>
+        </is>
+      </c>
+      <c r="D3221" s="0" t="inlineStr">
+        <is>
+          <t>记录、表示某种意义的记号或标志。</t>
+        </is>
+      </c>
+      <c r="E3221" s="0" t="inlineStr">
+        <is>
+          <t>ký hiệu</t>
+        </is>
+      </c>
+      <c r="F3221" s="0" t="inlineStr">
+        <is>
+          <t>拼音里的声调符号我教了很多遍，学生还是容易把二声和三声搞混。</t>
+        </is>
+      </c>
+      <c r="G3221" s="0" t="inlineStr"/>
+      <c r="H3221" s="0" t="inlineStr"/>
+    </row>
+    <row r="3222">
+      <c r="A3222" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3222" s="0" t="inlineStr">
+        <is>
+          <t>喧哗</t>
+        </is>
+      </c>
+      <c r="C3222" s="0" t="inlineStr">
+        <is>
+          <t>xuānhuá</t>
+        </is>
+      </c>
+      <c r="D3222" s="0" t="inlineStr">
+        <is>
+          <t>声音大而杂乱。</t>
+        </is>
+      </c>
+      <c r="E3222" s="0" t="inlineStr">
+        <is>
+          <t>ồn ào, huyên náo</t>
+        </is>
+      </c>
+      <c r="F3222" s="0" t="inlineStr">
+        <is>
+          <t>办公室太喧哗的时候，我就戴上耳机听HSK6听力真题，练耳朵也顺便屏蔽噪音。</t>
+        </is>
+      </c>
+      <c r="G3222" s="0" t="inlineStr"/>
+      <c r="H3222" s="0" t="inlineStr"/>
+    </row>
+    <row r="3223">
+      <c r="A3223" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3223" s="0" t="inlineStr">
+        <is>
+          <t>威风</t>
+        </is>
+      </c>
+      <c r="C3223" s="0" t="inlineStr">
+        <is>
+          <t>wēifēng</t>
+        </is>
+      </c>
+      <c r="D3223" s="0" t="inlineStr">
+        <is>
+          <t>使人敬畏、令人佩服的气势。</t>
+        </is>
+      </c>
+      <c r="E3223" s="0" t="inlineStr">
+        <is>
+          <t>oai phong, uy phong</t>
+        </is>
+      </c>
+      <c r="F3223" s="0" t="inlineStr">
+        <is>
+          <t>我教的一个HSK3小朋友说，学好汉语以后可以像电视里的将军一样威风，特别可爱。</t>
+        </is>
+      </c>
+      <c r="G3223" s="0" t="inlineStr"/>
+      <c r="H3223" s="0" t="inlineStr"/>
+    </row>
+    <row r="3224">
+      <c r="A3224" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3224" s="0" t="inlineStr">
+        <is>
+          <t>演绎</t>
+        </is>
+      </c>
+      <c r="C3224" s="0" t="inlineStr">
+        <is>
+          <t>yǎnyì</t>
+        </is>
+      </c>
+      <c r="D3224" s="0" t="inlineStr">
+        <is>
+          <t>展现、表演出来；也指由一般原理推出个别结论。</t>
+        </is>
+      </c>
+      <c r="E3224" s="0" t="inlineStr">
+        <is>
+          <t>diễn giải, diễn xuất</t>
+        </is>
+      </c>
+      <c r="F3224" s="0" t="inlineStr">
+        <is>
+          <t>这部电视剧演绎了一个普通中国家庭三代人的故事，我常拿来当口语课的听力材料。</t>
+        </is>
+      </c>
+      <c r="G3224" s="0" t="inlineStr"/>
+      <c r="H3224" s="0" t="inlineStr"/>
+    </row>
+    <row r="3225">
+      <c r="A3225" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3225" s="0" t="inlineStr">
+        <is>
+          <t>不屑一顾</t>
+        </is>
+      </c>
+      <c r="C3225" s="0" t="inlineStr">
+        <is>
+          <t>búxièyígù</t>
+        </is>
+      </c>
+      <c r="D3225" s="0" t="inlineStr">
+        <is>
+          <t>认为不值得一看，形容非常轻视。</t>
+        </is>
+      </c>
+      <c r="E3225" s="0" t="inlineStr">
+        <is>
+          <t>coi thường, chẳng thèm để mắt tới</t>
+        </is>
+      </c>
+      <c r="F3225" s="0" t="inlineStr">
+        <is>
+          <t>以前我对语法书不屑一顾，觉得靠语感就够了，考了几次HSK6作文才发现是自己太天真。</t>
+        </is>
+      </c>
+      <c r="G3225" s="0" t="inlineStr"/>
+      <c r="H3225" s="0" t="inlineStr"/>
+    </row>
+    <row r="3226">
+      <c r="A3226" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3226" s="0" t="inlineStr">
+        <is>
+          <t>电源</t>
+        </is>
+      </c>
+      <c r="C3226" s="0" t="inlineStr">
+        <is>
+          <t>diànyuán</t>
+        </is>
+      </c>
+      <c r="D3226" s="0" t="inlineStr">
+        <is>
+          <t>供电的来源，如插座、电池等。</t>
+        </is>
+      </c>
+      <c r="E3226" s="0" t="inlineStr">
+        <is>
+          <t>nguồn điện</t>
+        </is>
+      </c>
+      <c r="F3226" s="0" t="inlineStr">
+        <is>
+          <t>出差去中国上课前，我一定检查行李箱里有没有带转换插头，不然笔记本电脑找不到电源就麻烦了。</t>
+        </is>
+      </c>
+      <c r="G3226" s="0" t="inlineStr"/>
+      <c r="H3226" s="0" t="inlineStr"/>
+    </row>
+    <row r="3227">
+      <c r="A3227" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3227" s="0" t="inlineStr">
+        <is>
+          <t>闭塞</t>
+        </is>
+      </c>
+      <c r="C3227" s="0" t="inlineStr">
+        <is>
+          <t>bìsè</t>
+        </is>
+      </c>
+      <c r="D3227" s="0" t="inlineStr">
+        <is>
+          <t>交通不便，信息不流通。</t>
+        </is>
+      </c>
+      <c r="E3227" s="0" t="inlineStr">
+        <is>
+          <t>hẻo lánh, bế tắc (giao thông/thông tin)</t>
+        </is>
+      </c>
+      <c r="F3227" s="0" t="inlineStr">
+        <is>
+          <t>我第一次去的那个中国小城市有点闭塞，手机信号很差，反而让我认真复习了一整天HSK6词汇。</t>
+        </is>
+      </c>
+      <c r="G3227" s="0" t="inlineStr"/>
+      <c r="H3227" s="0" t="inlineStr"/>
+    </row>
+    <row r="3228">
+      <c r="A3228" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3228" s="0" t="inlineStr">
+        <is>
+          <t>久违</t>
+        </is>
+      </c>
+      <c r="C3228" s="0" t="inlineStr">
+        <is>
+          <t>jiǔwéi</t>
+        </is>
+      </c>
+      <c r="D3228" s="0" t="inlineStr">
+        <is>
+          <t>长时间没有见面或没有接触。</t>
+        </is>
+      </c>
+      <c r="E3228" s="0" t="inlineStr">
+        <is>
+          <t>đã lâu không gặp/không có</t>
+        </is>
+      </c>
+      <c r="F3228" s="0" t="inlineStr">
+        <is>
+          <t>上完HSK6课，我和久违的中国老同事视频聊天，久违的乡音让我特别开心。</t>
+        </is>
+      </c>
+      <c r="G3228" s="0" t="inlineStr"/>
+      <c r="H3228" s="0" t="inlineStr"/>
+    </row>
+    <row r="3229">
+      <c r="A3229" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3229" s="0" t="inlineStr">
+        <is>
+          <t>正义</t>
+        </is>
+      </c>
+      <c r="C3229" s="0" t="inlineStr">
+        <is>
+          <t>zhèngyì</t>
+        </is>
+      </c>
+      <c r="D3229" s="0" t="inlineStr">
+        <is>
+          <t>公正、公平，符合道理和良心。</t>
+        </is>
+      </c>
+      <c r="E3229" s="0" t="inlineStr">
+        <is>
+          <t>chính nghĩa, công lý</t>
+        </is>
+      </c>
+      <c r="F3229" s="0" t="inlineStr">
+        <is>
+          <t>我给HSK3学生讲“正义”这个词的时候，用了动画片里英雄打坏人的例子，他们一下子就理解了。</t>
+        </is>
+      </c>
+      <c r="G3229" s="0" t="inlineStr"/>
+      <c r="H3229" s="0" t="inlineStr"/>
+    </row>
+    <row r="3230">
+      <c r="A3230" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3230" s="0" t="inlineStr">
+        <is>
+          <t>见义勇为</t>
+        </is>
+      </c>
+      <c r="C3230" s="0" t="inlineStr">
+        <is>
+          <t>jiànyìyǒngwéi</t>
+        </is>
+      </c>
+      <c r="D3230" s="0" t="inlineStr">
+        <is>
+          <t>看到正义的事情，勇敢地去做。</t>
+        </is>
+      </c>
+      <c r="E3230" s="0" t="inlineStr">
+        <is>
+          <t>thấy việc nghĩa thì dũng cảm ra tay</t>
+        </is>
+      </c>
+      <c r="F3230" s="0" t="inlineStr">
+        <is>
+          <t>我看到一段新闻，一位路人见义勇为救了落水的孩子，就把这个当作HSK6写作的素材讲给学生听。</t>
+        </is>
+      </c>
+      <c r="G3230" s="0" t="inlineStr"/>
+      <c r="H3230" s="0" t="inlineStr"/>
+    </row>
+    <row r="3231">
+      <c r="A3231" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3231" s="0" t="inlineStr">
+        <is>
+          <t>洪水</t>
+        </is>
+      </c>
+      <c r="C3231" s="0" t="inlineStr">
+        <is>
+          <t>hóngshuǐ</t>
+        </is>
+      </c>
+      <c r="D3231" s="0" t="inlineStr">
+        <is>
+          <t>因大雨或江河泛滥而形成的大水。</t>
+        </is>
+      </c>
+      <c r="E3231" s="0" t="inlineStr">
+        <is>
+          <t>lũ lụt, nước lũ</t>
+        </is>
+      </c>
+      <c r="F3231" s="0" t="inlineStr">
+        <is>
+          <t>去年南方发洪水的新闻，我剪了一段当作HSK6听力理解的补充材料。</t>
+        </is>
+      </c>
+      <c r="G3231" s="0" t="inlineStr"/>
+      <c r="H3231" s="0" t="inlineStr"/>
+    </row>
+    <row r="3232">
+      <c r="A3232" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3232" s="0" t="inlineStr">
+        <is>
+          <t>英勇</t>
+        </is>
+      </c>
+      <c r="C3232" s="0" t="inlineStr">
+        <is>
+          <t>yīngyǒng</t>
+        </is>
+      </c>
+      <c r="D3232" s="0" t="inlineStr">
+        <is>
+          <t>勇敢出色，不怕危险。</t>
+        </is>
+      </c>
+      <c r="E3232" s="0" t="inlineStr">
+        <is>
+          <t>anh dũng, dũng cảm</t>
+        </is>
+      </c>
+      <c r="F3232" s="0" t="inlineStr">
+        <is>
+          <t>消防员英勇救火的视频，我常用来教HSK1-3的学生“勇敢”这个话题的词汇。</t>
+        </is>
+      </c>
+      <c r="G3232" s="0" t="inlineStr"/>
+      <c r="H3232" s="0" t="inlineStr"/>
+    </row>
+    <row r="3233">
+      <c r="A3233" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3233" s="0" t="inlineStr">
+        <is>
+          <t>贵族</t>
+        </is>
+      </c>
+      <c r="C3233" s="0" t="inlineStr">
+        <is>
+          <t>guìzú</t>
+        </is>
+      </c>
+      <c r="D3233" s="0" t="inlineStr">
+        <is>
+          <t>社会上享有特权的上层阶级。</t>
+        </is>
+      </c>
+      <c r="E3233" s="0" t="inlineStr">
+        <is>
+          <t>quý tộc</t>
+        </is>
+      </c>
+      <c r="F3233" s="0" t="inlineStr">
+        <is>
+          <t>我跟学生开玩笑说，学好汉语以后去中国点菜都不用看图片了，感觉自己像语言贵族一样自信。</t>
+        </is>
+      </c>
+      <c r="G3233" s="0" t="inlineStr"/>
+      <c r="H3233" s="0" t="inlineStr"/>
+    </row>
+    <row r="3234">
+      <c r="A3234" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3234" s="0" t="inlineStr">
+        <is>
+          <t>播种</t>
+        </is>
+      </c>
+      <c r="C3234" s="0" t="inlineStr">
+        <is>
+          <t>bōzhǒng</t>
+        </is>
+      </c>
+      <c r="D3234" s="0" t="inlineStr">
+        <is>
+          <t>把种子撒到土地里。</t>
+        </is>
+      </c>
+      <c r="E3234" s="0" t="inlineStr">
+        <is>
+          <t>gieo hạt, gieo trồng</t>
+        </is>
+      </c>
+      <c r="F3234" s="0" t="inlineStr">
+        <is>
+          <t>我常跟自己说，学外语就像播种，每天背几个词，慢慢才能等到HSK6高分的收获。</t>
+        </is>
+      </c>
+      <c r="G3234" s="0" t="inlineStr"/>
+      <c r="H3234" s="0" t="inlineStr"/>
+    </row>
+    <row r="3235">
+      <c r="A3235" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3235" s="0" t="inlineStr">
+        <is>
+          <t>承包</t>
+        </is>
+      </c>
+      <c r="C3235" s="0" t="inlineStr">
+        <is>
+          <t>chéngbāo</t>
+        </is>
+      </c>
+      <c r="D3235" s="0" t="inlineStr">
+        <is>
+          <t>依照合同承担、完成某项工作的任务。</t>
+        </is>
+      </c>
+      <c r="E3235" s="0" t="inlineStr">
+        <is>
+          <t>nhận thầu, nhận khoán</t>
+        </is>
+      </c>
+      <c r="F3235" s="0" t="inlineStr">
+        <is>
+          <t>这学期的HSK1-3口语课全部由我一个人承包，工作量不小，但很有成就感。</t>
+        </is>
+      </c>
+      <c r="G3235" s="0" t="inlineStr"/>
+      <c r="H3235" s="0" t="inlineStr"/>
+    </row>
+    <row r="3236">
+      <c r="A3236" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3236" s="0" t="inlineStr">
+        <is>
+          <t>方言</t>
+        </is>
+      </c>
+      <c r="C3236" s="0" t="inlineStr">
+        <is>
+          <t>fāngyán</t>
+        </is>
+      </c>
+      <c r="D3236" s="0" t="inlineStr">
+        <is>
+          <t>一个地区特有的、跟标准语不完全相同的语言。</t>
+        </is>
+      </c>
+      <c r="E3236" s="0" t="inlineStr">
+        <is>
+          <t>phương ngữ, tiếng địa phương</t>
+        </is>
+      </c>
+      <c r="F3236" s="0" t="inlineStr">
+        <is>
+          <t>我工作的城市同事说话夹杂很重的方言，刚开始我只能听懂普通话，现在慢慢也能猜出几句方言了。</t>
+        </is>
+      </c>
+      <c r="G3236" s="0" t="inlineStr"/>
+      <c r="H3236" s="0" t="inlineStr"/>
+    </row>
+    <row r="3237">
+      <c r="A3237" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3237" s="0" t="inlineStr">
+        <is>
+          <t>捣乱</t>
+        </is>
+      </c>
+      <c r="C3237" s="0" t="inlineStr">
+        <is>
+          <t>dǎoluàn</t>
+        </is>
+      </c>
+      <c r="D3237" s="0" t="inlineStr">
+        <is>
+          <t>故意扰乱秩序，找麻烦。</t>
+        </is>
+      </c>
+      <c r="E3237" s="0" t="inlineStr">
+        <is>
+          <t>quấy phá, gây rối</t>
+        </is>
+      </c>
+      <c r="F3237" s="0" t="inlineStr">
+        <is>
+          <t>我教HSK1的小朋友上课有时会捣乱，我就用游戏的方式把他们的注意力拉回来。</t>
+        </is>
+      </c>
+      <c r="G3237" s="0" t="inlineStr"/>
+      <c r="H3237" s="0" t="inlineStr"/>
+    </row>
+    <row r="3238">
+      <c r="A3238" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3238" s="0" t="inlineStr">
+        <is>
+          <t>狼狈</t>
+        </is>
+      </c>
+      <c r="C3238" s="0" t="inlineStr">
+        <is>
+          <t>lángbèi</t>
+        </is>
+      </c>
+      <c r="D3238" s="0" t="inlineStr">
+        <is>
+          <t>形容非常窘迫、难堪的样子。</t>
+        </is>
+      </c>
+      <c r="E3238" s="0" t="inlineStr">
+        <is>
+          <t>lúng túng, thảm hại</t>
+        </is>
+      </c>
+      <c r="F3238" s="0" t="inlineStr">
+        <is>
+          <t>我第一次用中文做HSK6口头报告，紧张得说错好几个词，狼狈极了。</t>
+        </is>
+      </c>
+      <c r="G3238" s="0" t="inlineStr"/>
+      <c r="H3238" s="0" t="inlineStr"/>
+    </row>
+    <row r="3239">
+      <c r="A3239" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3239" s="0" t="inlineStr">
+        <is>
+          <t>幼稚</t>
+        </is>
+      </c>
+      <c r="C3239" s="0" t="inlineStr">
+        <is>
+          <t>yòuzhì</t>
+        </is>
+      </c>
+      <c r="D3239" s="0" t="inlineStr">
+        <is>
+          <t>年纪小，思想或做法简单、不成熟。</t>
+        </is>
+      </c>
+      <c r="E3239" s="0" t="inlineStr">
+        <is>
+          <t>ấu trĩ, non nớt</t>
+        </is>
+      </c>
+      <c r="F3239" s="0" t="inlineStr">
+        <is>
+          <t>现在回头看自己刚学汉语时写的日记，觉得那些想法真幼稚，但也挺可爱的。</t>
+        </is>
+      </c>
+      <c r="G3239" s="0" t="inlineStr"/>
+      <c r="H3239" s="0" t="inlineStr"/>
+    </row>
+    <row r="3240">
+      <c r="A3240" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3240" s="0" t="inlineStr">
+        <is>
+          <t>双胞胎</t>
+        </is>
+      </c>
+      <c r="C3240" s="0" t="inlineStr">
+        <is>
+          <t>shuāngbāotāi</t>
+        </is>
+      </c>
+      <c r="D3240" s="0" t="inlineStr">
+        <is>
+          <t>同一次出生的两个孩子。</t>
+        </is>
+      </c>
+      <c r="E3240" s="0" t="inlineStr">
+        <is>
+          <t>cặp song sinh</t>
+        </is>
+      </c>
+      <c r="F3240" s="0" t="inlineStr">
+        <is>
+          <t>我教的学生里有一对双胞胎姐妹，两人的汉语水平差不多，考HSK3都是一次就过。</t>
+        </is>
+      </c>
+      <c r="G3240" s="0" t="inlineStr"/>
+      <c r="H3240" s="0" t="inlineStr"/>
+    </row>
+    <row r="3241">
+      <c r="A3241" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3241" s="0" t="inlineStr">
+        <is>
+          <t>家常</t>
+        </is>
+      </c>
+      <c r="C3241" s="0" t="inlineStr">
+        <is>
+          <t>jiācháng</t>
+        </is>
+      </c>
+      <c r="D3241" s="0" t="inlineStr">
+        <is>
+          <t>家庭日常生活中的琐事。</t>
+        </is>
+      </c>
+      <c r="E3241" s="0" t="inlineStr">
+        <is>
+          <t>chuyện thường ngày (trong gia đình)</t>
+        </is>
+      </c>
+      <c r="F3241" s="0" t="inlineStr">
+        <is>
+          <t>下课后我常跟中国同事聊家常，这也是我练口语最自然的机会。</t>
+        </is>
+      </c>
+      <c r="G3241" s="0" t="inlineStr"/>
+      <c r="H3241" s="0" t="inlineStr"/>
+    </row>
+    <row r="3242">
+      <c r="A3242" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3242" s="0" t="inlineStr">
+        <is>
+          <t>回顾</t>
+        </is>
+      </c>
+      <c r="C3242" s="0" t="inlineStr">
+        <is>
+          <t>huígù</t>
+        </is>
+      </c>
+      <c r="D3242" s="0" t="inlineStr">
+        <is>
+          <t>回过头来看过去发生的事情。</t>
+        </is>
+      </c>
+      <c r="E3242" s="0" t="inlineStr">
+        <is>
+          <t>hồi tưởng, nhìn lại</t>
+        </is>
+      </c>
+      <c r="F3242" s="0" t="inlineStr">
+        <is>
+          <t>每次考完HSK6，我都会回顾自己这段时间的学习计划，看看哪里还需要调整。</t>
+        </is>
+      </c>
+      <c r="G3242" s="0" t="inlineStr"/>
+      <c r="H3242" s="0" t="inlineStr"/>
+    </row>
+    <row r="3243">
+      <c r="A3243" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3243" s="0" t="inlineStr">
+        <is>
+          <t>往事</t>
+        </is>
+      </c>
+      <c r="C3243" s="0" t="inlineStr">
+        <is>
+          <t>wǎngshì</t>
+        </is>
+      </c>
+      <c r="D3243" s="0" t="inlineStr">
+        <is>
+          <t>过去发生的事情。</t>
+        </is>
+      </c>
+      <c r="E3243" s="0" t="inlineStr">
+        <is>
+          <t>chuyện xưa, chuyện đã qua</t>
+        </is>
+      </c>
+      <c r="F3243" s="0" t="inlineStr">
+        <is>
+          <t>跟中国朋友聊起刚来工作时闹的笑话，那些往事现在想起来都觉得好笑。</t>
+        </is>
+      </c>
+      <c r="G3243" s="0" t="inlineStr"/>
+      <c r="H3243" s="0" t="inlineStr"/>
+    </row>
+    <row r="3244">
+      <c r="A3244" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3244" s="0" t="inlineStr">
+        <is>
+          <t>方圆</t>
+        </is>
+      </c>
+      <c r="C3244" s="0" t="inlineStr">
+        <is>
+          <t>fāngyuán</t>
+        </is>
+      </c>
+      <c r="D3244" s="0" t="inlineStr">
+        <is>
+          <t>周围一定范围的地区。</t>
+        </is>
+      </c>
+      <c r="E3244" s="0" t="inlineStr">
+        <is>
+          <t>chu vi, xung quanh (trong phạm vi)</t>
+        </is>
+      </c>
+      <c r="F3244" s="0" t="inlineStr">
+        <is>
+          <t>我住的小区方圆几公里内就有三所汉语培训学校，竞争很激烈。</t>
+        </is>
+      </c>
+      <c r="G3244" s="0" t="inlineStr"/>
+      <c r="H3244" s="0" t="inlineStr"/>
+    </row>
+    <row r="3245">
+      <c r="A3245" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3245" s="0" t="inlineStr">
+        <is>
+          <t>爆炸</t>
+        </is>
+      </c>
+      <c r="C3245" s="0" t="inlineStr">
+        <is>
+          <t>bàozhà</t>
+        </is>
+      </c>
+      <c r="D3245" s="0" t="inlineStr">
+        <is>
+          <t>物体因剧烈反应而突然破裂、发出巨响。</t>
+        </is>
+      </c>
+      <c r="E3245" s="0" t="inlineStr">
+        <is>
+          <t>nổ, bùng nổ</t>
+        </is>
+      </c>
+      <c r="F3245" s="0" t="inlineStr">
+        <is>
+          <t>我用“信息爆炸”这个词给HSK6学生讲现代生活的话题，他们都能举出自己的例子。</t>
+        </is>
+      </c>
+      <c r="G3245" s="0" t="inlineStr"/>
+      <c r="H3245" s="0" t="inlineStr"/>
+    </row>
+    <row r="3246">
+      <c r="A3246" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3246" s="0" t="inlineStr">
+        <is>
+          <t>对联</t>
+        </is>
+      </c>
+      <c r="C3246" s="0" t="inlineStr">
+        <is>
+          <t>duìlián</t>
+        </is>
+      </c>
+      <c r="D3246" s="0" t="inlineStr">
+        <is>
+          <t>春节等场合贴在门两边、字数相等、意思相对的两句话。</t>
+        </is>
+      </c>
+      <c r="E3246" s="0" t="inlineStr">
+        <is>
+          <t>câu đối</t>
+        </is>
+      </c>
+      <c r="F3246" s="0" t="inlineStr">
+        <is>
+          <t>今年春节，中国同事教我写对联，我这才知道上联下联还要平仄相对，学问不小。</t>
+        </is>
+      </c>
+      <c r="G3246" s="0" t="inlineStr"/>
+      <c r="H3246" s="0" t="inlineStr"/>
+    </row>
+    <row r="3247">
+      <c r="A3247" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3247" s="0" t="inlineStr">
+        <is>
+          <t>拜年</t>
+        </is>
+      </c>
+      <c r="C3247" s="0" t="inlineStr">
+        <is>
+          <t>bàinián</t>
+        </is>
+      </c>
+      <c r="D3247" s="0" t="inlineStr">
+        <is>
+          <t>春节时向长辈或亲友祝贺新年。</t>
+        </is>
+      </c>
+      <c r="E3247" s="0" t="inlineStr">
+        <is>
+          <t>chúc Tết, đi chúc Tết</t>
+        </is>
+      </c>
+      <c r="F3247" s="0" t="inlineStr">
+        <is>
+          <t>在中国工作的第一个春节，我跟着同事去给他父母拜年，学到了不少年俗用语。</t>
+        </is>
+      </c>
+      <c r="G3247" s="0" t="inlineStr"/>
+      <c r="H3247" s="0" t="inlineStr"/>
+    </row>
+    <row r="3248">
+      <c r="A3248" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3248" s="0" t="inlineStr">
+        <is>
+          <t>元宵节</t>
+        </is>
+      </c>
+      <c r="C3248" s="0" t="inlineStr">
+        <is>
+          <t>yuánxiāojié</t>
+        </is>
+      </c>
+      <c r="D3248" s="0" t="inlineStr">
+        <is>
+          <t>农历正月十五的传统节日，有吃元宵、看花灯的习俗。</t>
+        </is>
+      </c>
+      <c r="E3248" s="0" t="inlineStr">
+        <is>
+          <t>Tết Nguyên tiêu</t>
+        </is>
+      </c>
+      <c r="F3248" s="0" t="inlineStr">
+        <is>
+          <t>元宵节那天办公室发了汤圆，同事顺便教我用汉语说“团团圆圆”祝福大家。</t>
+        </is>
+      </c>
+      <c r="G3248" s="0" t="inlineStr"/>
+      <c r="H3248" s="0" t="inlineStr"/>
+    </row>
+    <row r="3249">
+      <c r="A3249" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3249" s="0" t="inlineStr">
+        <is>
+          <t>天伦之乐</t>
+        </is>
+      </c>
+      <c r="C3249" s="0" t="inlineStr">
+        <is>
+          <t>tiānlúnzhīlè</t>
+        </is>
+      </c>
+      <c r="D3249" s="0" t="inlineStr">
+        <is>
+          <t>家人团聚在一起享受的快乐。</t>
+        </is>
+      </c>
+      <c r="E3249" s="0" t="inlineStr">
+        <is>
+          <t>niềm vui sum vầy gia đình</t>
+        </is>
+      </c>
+      <c r="F3249" s="0" t="inlineStr">
+        <is>
+          <t>每次视频通话看到家人围坐吃饭，我都特别想念那种天伦之乐的感觉。</t>
+        </is>
+      </c>
+      <c r="G3249" s="0" t="inlineStr"/>
+      <c r="H3249" s="0" t="inlineStr"/>
+    </row>
+    <row r="3250">
+      <c r="A3250" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3250" s="0" t="inlineStr">
+        <is>
+          <t>正月</t>
+        </is>
+      </c>
+      <c r="C3250" s="0" t="inlineStr">
+        <is>
+          <t>zhēngyuè</t>
+        </is>
+      </c>
+      <c r="D3250" s="0" t="inlineStr">
+        <is>
+          <t>农历一年的第一个月。</t>
+        </is>
+      </c>
+      <c r="E3250" s="0" t="inlineStr">
+        <is>
+          <t>tháng Giêng (âm lịch)</t>
+        </is>
+      </c>
+      <c r="F3250" s="0" t="inlineStr">
+        <is>
+          <t>中国同事告诉我，正月十五之前很多店铺还没正式开工，我备课的时候要提前问清楚放假安排。</t>
+        </is>
+      </c>
+      <c r="G3250" s="0" t="inlineStr"/>
+      <c r="H3250" s="0" t="inlineStr"/>
+    </row>
+    <row r="3251">
+      <c r="A3251" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3251" s="0" t="inlineStr">
+        <is>
+          <t>寺庙</t>
+        </is>
+      </c>
+      <c r="C3251" s="0" t="inlineStr">
+        <is>
+          <t>sìmiào</t>
+        </is>
+      </c>
+      <c r="D3251" s="0" t="inlineStr">
+        <is>
+          <t>供奉神佛、供人祭拜的建筑。</t>
+        </is>
+      </c>
+      <c r="E3251" s="0" t="inlineStr">
+        <is>
+          <t>chùa, đền, miếu</t>
+        </is>
+      </c>
+      <c r="F3251" s="0" t="inlineStr">
+        <is>
+          <t>周末我常去附近的寺庙走走，顺便跟卖香的老人练几句方言。</t>
+        </is>
+      </c>
+      <c r="G3251" s="0" t="inlineStr"/>
+      <c r="H3251" s="0" t="inlineStr"/>
+    </row>
+    <row r="3252">
+      <c r="A3252" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3252" s="0" t="inlineStr">
+        <is>
+          <t>眼神</t>
+        </is>
+      </c>
+      <c r="C3252" s="0" t="inlineStr">
+        <is>
+          <t>yǎnshén</t>
+        </is>
+      </c>
+      <c r="D3252" s="0" t="inlineStr">
+        <is>
+          <t>眼睛的神态，表达出的表情或含义。</t>
+        </is>
+      </c>
+      <c r="E3252" s="0" t="inlineStr">
+        <is>
+          <t>ánh mắt, thần thái của mắt</t>
+        </is>
+      </c>
+      <c r="F3252" s="0" t="inlineStr">
+        <is>
+          <t>学生答不出HSK6口语题的时候，眼神里都是紧张，我就先让他们放松深呼吸。</t>
+        </is>
+      </c>
+      <c r="G3252" s="0" t="inlineStr"/>
+      <c r="H3252" s="0" t="inlineStr"/>
+    </row>
+    <row r="3253">
+      <c r="A3253" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3253" s="0" t="inlineStr">
+        <is>
+          <t>新郎</t>
+        </is>
+      </c>
+      <c r="C3253" s="0" t="inlineStr">
+        <is>
+          <t>xīnláng</t>
+        </is>
+      </c>
+      <c r="D3253" s="0" t="inlineStr">
+        <is>
+          <t>结婚仪式上的男方。</t>
+        </is>
+      </c>
+      <c r="E3253" s="0" t="inlineStr">
+        <is>
+          <t>chú rể</t>
+        </is>
+      </c>
+      <c r="F3253" s="0" t="inlineStr">
+        <is>
+          <t>参加中国同事的婚礼，我才知道新郎接亲的时候还要回答伴娘团出的各种问题，特别有意思。</t>
+        </is>
+      </c>
+      <c r="G3253" s="0" t="inlineStr"/>
+      <c r="H3253" s="0" t="inlineStr"/>
+    </row>
+    <row r="3254">
+      <c r="A3254" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3254" s="0" t="inlineStr">
+        <is>
+          <t>新娘</t>
+        </is>
+      </c>
+      <c r="C3254" s="0" t="inlineStr">
+        <is>
+          <t>xīnniáng</t>
+        </is>
+      </c>
+      <c r="D3254" s="0" t="inlineStr">
+        <is>
+          <t>结婚仪式上的女方。</t>
+        </is>
+      </c>
+      <c r="E3254" s="0" t="inlineStr">
+        <is>
+          <t>cô dâu</t>
+        </is>
+      </c>
+      <c r="F3254" s="0" t="inlineStr">
+        <is>
+          <t>那天婚礼上新娘穿着红色的中式礼服，特别好看，我趁机学了不少婚俗词汇。</t>
+        </is>
+      </c>
+      <c r="G3254" s="0" t="inlineStr"/>
+      <c r="H3254" s="0" t="inlineStr"/>
+    </row>
+    <row r="3255">
+      <c r="A3255" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3255" s="0" t="inlineStr">
+        <is>
+          <t>响应</t>
+        </is>
+      </c>
+      <c r="C3255" s="0" t="inlineStr">
+        <is>
+          <t>xiǎngyìng</t>
+        </is>
+      </c>
+      <c r="D3255" s="0" t="inlineStr">
+        <is>
+          <t>对别人的号召、倡议做出反应，表示支持。</t>
+        </is>
+      </c>
+      <c r="E3255" s="0" t="inlineStr">
+        <is>
+          <t>hưởng ứng, đáp lại</t>
+        </is>
+      </c>
+      <c r="F3255" s="0" t="inlineStr">
+        <is>
+          <t>学校号召大家参加中文演讲比赛，我响应报了名，也顺便逼自己练一次公开表达。</t>
+        </is>
+      </c>
+      <c r="G3255" s="0" t="inlineStr"/>
+      <c r="H3255" s="0" t="inlineStr"/>
+    </row>
+    <row r="3256">
+      <c r="A3256" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3256" s="0" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="C3256" s="0" t="inlineStr">
+        <is>
+          <t>shèqū</t>
+        </is>
+      </c>
+      <c r="D3256" s="0" t="inlineStr">
+        <is>
+          <t>共同居住在一个地区、有共同生活联系的一群人。</t>
+        </is>
+      </c>
+      <c r="E3256" s="0" t="inlineStr">
+        <is>
+          <t>khu dân cư, cộng đồng dân cư</t>
+        </is>
+      </c>
+      <c r="F3256" s="0" t="inlineStr">
+        <is>
+          <t>我住的社区每个月都会组织中文角活动，附近不少外国人都来参加。</t>
+        </is>
+      </c>
+      <c r="G3256" s="0" t="inlineStr"/>
+      <c r="H3256" s="0" t="inlineStr"/>
+    </row>
+    <row r="3257">
+      <c r="A3257" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3257" s="0" t="inlineStr">
+        <is>
+          <t>物业</t>
+        </is>
+      </c>
+      <c r="C3257" s="0" t="inlineStr">
+        <is>
+          <t>wùyè</t>
+        </is>
+      </c>
+      <c r="D3257" s="0" t="inlineStr">
+        <is>
+          <t>负责管理小区、大楼日常事务的机构或人员。</t>
+        </is>
+      </c>
+      <c r="E3257" s="0" t="inlineStr">
+        <is>
+          <t>(đơn vị) quản lý tòa nhà</t>
+        </is>
+      </c>
+      <c r="F3257" s="0" t="inlineStr">
+        <is>
+          <t>家里的暖气坏了，我打电话给物业，用汉语说清楚问题，物业师傅当天就来修了。</t>
+        </is>
+      </c>
+      <c r="G3257" s="0" t="inlineStr"/>
+      <c r="H3257" s="0" t="inlineStr"/>
+    </row>
+    <row r="3258">
+      <c r="A3258" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3258" s="0" t="inlineStr">
+        <is>
+          <t>媳妇</t>
+        </is>
+      </c>
+      <c r="C3258" s="0" t="inlineStr">
+        <is>
+          <t>xífù</t>
+        </is>
+      </c>
+      <c r="D3258" s="0" t="inlineStr">
+        <is>
+          <t>儿子的妻子；口语中也指自己的妻子。</t>
+        </is>
+      </c>
+      <c r="E3258" s="0" t="inlineStr">
+        <is>
+          <t>con dâu; (khẩu ngữ) vợ</t>
+        </is>
+      </c>
+      <c r="F3258" s="0" t="inlineStr">
+        <is>
+          <t>同事总跟我夸他媳妇做的饭好吃，听得我都想跟他学几道家常菜的说法。</t>
+        </is>
+      </c>
+      <c r="G3258" s="0" t="inlineStr"/>
+      <c r="H3258" s="0" t="inlineStr"/>
+    </row>
+    <row r="3259">
+      <c r="A3259" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3259" s="0" t="inlineStr">
+        <is>
+          <t>贤惠</t>
+        </is>
+      </c>
+      <c r="C3259" s="0" t="inlineStr">
+        <is>
+          <t>xiánhuì</t>
+        </is>
+      </c>
+      <c r="D3259" s="0" t="inlineStr">
+        <is>
+          <t>形容女性心地善良、通情达理、善于持家。</t>
+        </is>
+      </c>
+      <c r="E3259" s="0" t="inlineStr">
+        <is>
+          <t>hiền thục, đảm đang</t>
+        </is>
+      </c>
+      <c r="F3259" s="0" t="inlineStr">
+        <is>
+          <t>同事总说他媳妇既贤惠又能干，家里家外都照顾得很好，这也是我学到的一个常用夸人词。</t>
+        </is>
+      </c>
+      <c r="G3259" s="0" t="inlineStr"/>
+      <c r="H3259" s="0" t="inlineStr"/>
+    </row>
+    <row r="3260">
+      <c r="A3260" s="0" t="inlineStr">
+        <is>
+          <t>Bài 33</t>
+        </is>
+      </c>
+      <c r="B3260" s="0" t="inlineStr">
+        <is>
+          <t>现场</t>
+        </is>
+      </c>
+      <c r="C3260" s="0" t="inlineStr">
+        <is>
+          <t>xiànchǎng</t>
+        </is>
+      </c>
+      <c r="D3260" s="0" t="inlineStr">
+        <is>
+          <t>事情发生的地点，强调场地本身，后边常跟名词。</t>
+        </is>
+      </c>
+      <c r="E3260" s="0" t="inlineStr">
+        <is>
+          <t>hiện trường, tại chỗ (địa điểm)</t>
+        </is>
+      </c>
+      <c r="F3260" s="0" t="inlineStr">
+        <is>
+          <t>上周公司请了一位汉语老师现场教发音，我们几个同事都跟着现场练习。</t>
+        </is>
+      </c>
+      <c r="G3260" s="0" t="inlineStr"/>
+      <c r="H3260" s="0" t="inlineStr"/>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3261" t="inlineStr">
+        <is>
+          <t>霞</t>
+        </is>
+      </c>
+      <c r="C3261" t="inlineStr">
+        <is>
+          <t>xiá</t>
+        </is>
+      </c>
+      <c r="D3261" t="inlineStr">
+        <is>
+          <t>日出或日落前后天空中出现的彩色云。</t>
+        </is>
+      </c>
+      <c r="E3261" t="inlineStr">
+        <is>
+          <t>ráng mây (ráng chiều, ráng sáng)</t>
+        </is>
+      </c>
+      <c r="F3261" t="inlineStr">
+        <is>
+          <t>我每天早上去中文中心的路上，都能看到满天的朝霞，心情特别好。</t>
+        </is>
+      </c>
+      <c r="G3261" t="inlineStr"/>
+      <c r="H3261" t="inlineStr"/>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3262" t="inlineStr">
+        <is>
+          <t>朴素</t>
+        </is>
+      </c>
+      <c r="C3262" t="inlineStr">
+        <is>
+          <t>pǔsù</t>
+        </is>
+      </c>
+      <c r="D3262" t="inlineStr">
+        <is>
+          <t>生活简单，不奢侈，不讲究穿着打扮。</t>
+        </is>
+      </c>
+      <c r="E3262" t="inlineStr">
+        <is>
+          <t>giản dị, mộc mạc</t>
+        </is>
+      </c>
+      <c r="F3262" t="inlineStr">
+        <is>
+          <t>我教HSK1-3的时候，尽量用朴素的语言解释语法，让学生容易理解。</t>
+        </is>
+      </c>
+      <c r="G3262" t="inlineStr"/>
+      <c r="H3262" t="inlineStr"/>
+    </row>
+    <row r="3263">
+      <c r="A3263" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3263" t="inlineStr">
+        <is>
+          <t>温和</t>
+        </is>
+      </c>
+      <c r="C3263" t="inlineStr">
+        <is>
+          <t>wēnhé</t>
+        </is>
+      </c>
+      <c r="D3263" t="inlineStr">
+        <is>
+          <t>（性情、态度、语言）不严厉，使人感到亲切；也可指气候不冷不热。</t>
+        </is>
+      </c>
+      <c r="E3263" t="inlineStr">
+        <is>
+          <t>ôn hòa (tính cách/khí hậu)</t>
+        </is>
+      </c>
+      <c r="F3263" t="inlineStr">
+        <is>
+          <t>我发现中国同事对新人说话都很温和，这让我在陌生的工作环境里没那么紧张。</t>
+        </is>
+      </c>
+      <c r="G3263" t="inlineStr"/>
+      <c r="H3263" t="inlineStr"/>
+    </row>
+    <row r="3264">
+      <c r="A3264" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3264" t="inlineStr">
+        <is>
+          <t>颠簸</t>
+        </is>
+      </c>
+      <c r="C3264" t="inlineStr">
+        <is>
+          <t>diānbǒ</t>
+        </is>
+      </c>
+      <c r="D3264" t="inlineStr">
+        <is>
+          <t>（车、船等）上下震动，不平稳。</t>
+        </is>
+      </c>
+      <c r="E3264" t="inlineStr">
+        <is>
+          <t>xóc nảy, chòng chành</t>
+        </is>
+      </c>
+      <c r="F3264" t="inlineStr">
+        <is>
+          <t>从我住的地方到公司要坐一个小时的公交车，路上颠簸得厉害，我经常利用这段时间背HSK6生词。</t>
+        </is>
+      </c>
+      <c r="G3264" t="inlineStr"/>
+      <c r="H3264" t="inlineStr"/>
+    </row>
+    <row r="3265">
+      <c r="A3265" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3265" t="inlineStr">
+        <is>
+          <t>巷</t>
+        </is>
+      </c>
+      <c r="C3265" t="inlineStr">
+        <is>
+          <t>xiàng</t>
+        </is>
+      </c>
+      <c r="D3265" t="inlineStr">
+        <is>
+          <t>城市或乡镇中比较窄的街道。</t>
+        </is>
+      </c>
+      <c r="E3265" t="inlineStr">
+        <is>
+          <t>ngõ, hẻm</t>
+        </is>
+      </c>
+      <c r="F3265" t="inlineStr">
+        <is>
+          <t>我住的小区旁边有一条老巷子，周末我常常去那儿的小店买早饭。</t>
+        </is>
+      </c>
+      <c r="G3265" t="inlineStr"/>
+      <c r="H3265" t="inlineStr"/>
+    </row>
+    <row r="3266">
+      <c r="A3266" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3266" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
+        </is>
+      </c>
+      <c r="C3266" t="inlineStr">
+        <is>
+          <t>táocí</t>
+        </is>
+      </c>
+      <c r="D3266" t="inlineStr">
+        <is>
+          <t>陶器和瓷器的统称。</t>
+        </is>
+      </c>
+      <c r="E3266" t="inlineStr">
+        <is>
+          <t>đồ gốm sứ</t>
+        </is>
+      </c>
+      <c r="F3266" t="inlineStr">
+        <is>
+          <t>上次去景德镇旅游，我买了几件陶瓷茶具，打算送给教我中文的老师。</t>
+        </is>
+      </c>
+      <c r="G3266" t="inlineStr"/>
+      <c r="H3266" t="inlineStr"/>
+    </row>
+    <row r="3267">
+      <c r="A3267" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3267" t="inlineStr">
+        <is>
+          <t>收藏</t>
+        </is>
+      </c>
+      <c r="C3267" t="inlineStr">
+        <is>
+          <t>shōucáng</t>
+        </is>
+      </c>
+      <c r="D3267" t="inlineStr">
+        <is>
+          <t>收集并保存有价值的东西。</t>
+        </is>
+      </c>
+      <c r="E3267" t="inlineStr">
+        <is>
+          <t>sưu tầm, cất giữ</t>
+        </is>
+      </c>
+      <c r="F3267" t="inlineStr">
+        <is>
+          <t>我的房东是个收藏爱好者，家里收藏了不少老照片和邮票。</t>
+        </is>
+      </c>
+      <c r="G3267" t="inlineStr"/>
+      <c r="H3267" t="inlineStr"/>
+    </row>
+    <row r="3268">
+      <c r="A3268" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3268" t="inlineStr">
+        <is>
+          <t>鉴定</t>
+        </is>
+      </c>
+      <c r="C3268" t="inlineStr">
+        <is>
+          <t>jiàndìng</t>
+        </is>
+      </c>
+      <c r="D3268" t="inlineStr">
+        <is>
+          <t>通过科学方法辨别事物的真假、好坏或年代。</t>
+        </is>
+      </c>
+      <c r="E3268" t="inlineStr">
+        <is>
+          <t>giám định, thẩm định</t>
+        </is>
+      </c>
+      <c r="F3268" t="inlineStr">
+        <is>
+          <t>为了准备HSK6考试，我经常请中国朋友帮我鉴定我写的作文有没有语法错误。</t>
+        </is>
+      </c>
+      <c r="G3268" t="inlineStr"/>
+      <c r="H3268" t="inlineStr"/>
+    </row>
+    <row r="3269">
+      <c r="A3269" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3269" t="inlineStr">
+        <is>
+          <t>无偿</t>
+        </is>
+      </c>
+      <c r="C3269" t="inlineStr">
+        <is>
+          <t>wúcháng</t>
+        </is>
+      </c>
+      <c r="D3269" t="inlineStr">
+        <is>
+          <t>不要报酬，不收取费用。</t>
+        </is>
+      </c>
+      <c r="E3269" t="inlineStr">
+        <is>
+          <t>vô thường, miễn phí</t>
+        </is>
+      </c>
+      <c r="F3269" t="inlineStr">
+        <is>
+          <t>我在语言交换活动上无偿教中国朋友学越南语，他们也教我中文。</t>
+        </is>
+      </c>
+      <c r="G3269" t="inlineStr"/>
+      <c r="H3269" t="inlineStr"/>
+    </row>
+    <row r="3270">
+      <c r="A3270" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3270" t="inlineStr">
+        <is>
+          <t>赠送</t>
+        </is>
+      </c>
+      <c r="C3270" t="inlineStr">
+        <is>
+          <t>zèngsòng</t>
+        </is>
+      </c>
+      <c r="D3270" t="inlineStr">
+        <is>
+          <t>无代价地把东西送给别人。</t>
+        </is>
+      </c>
+      <c r="E3270" t="inlineStr">
+        <is>
+          <t>tặng, biếu</t>
+        </is>
+      </c>
+      <c r="F3270" t="inlineStr">
+        <is>
+          <t>我通过HSK6考试后，打算把自己整理的生词笔记赠送给下一届的学生。</t>
+        </is>
+      </c>
+      <c r="G3270" t="inlineStr"/>
+      <c r="H3270" t="inlineStr"/>
+    </row>
+    <row r="3271">
+      <c r="A3271" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3271" t="inlineStr">
+        <is>
+          <t>络绎不绝</t>
+        </is>
+      </c>
+      <c r="C3271" t="inlineStr">
+        <is>
+          <t>luòyìbùjué</t>
+        </is>
+      </c>
+      <c r="D3271" t="inlineStr">
+        <is>
+          <t>形容行人、车马等前后相连，来往不断。</t>
+        </is>
+      </c>
+      <c r="E3271" t="inlineStr">
+        <is>
+          <t>nườm nượp không dứt</t>
+        </is>
+      </c>
+      <c r="F3271" t="inlineStr">
+        <is>
+          <t>每次学校放假的时候，来我们汉语角报名的学生都络绎不绝。</t>
+        </is>
+      </c>
+      <c r="G3271" t="inlineStr"/>
+      <c r="H3271" t="inlineStr"/>
+    </row>
+    <row r="3272">
+      <c r="A3272" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3272" t="inlineStr">
+        <is>
+          <t>文物</t>
+        </is>
+      </c>
+      <c r="C3272" t="inlineStr">
+        <is>
+          <t>wénwù</t>
+        </is>
+      </c>
+      <c r="D3272" t="inlineStr">
+        <is>
+          <t>历史遗留下来的、在文化发展史上有价值的东西。</t>
+        </is>
+      </c>
+      <c r="E3272" t="inlineStr">
+        <is>
+          <t>văn vật, di vật văn hóa</t>
+        </is>
+      </c>
+      <c r="F3272" t="inlineStr">
+        <is>
+          <t>我周末常去博物馆看文物展览，顺便练习用中文给自己讲解历史背景。</t>
+        </is>
+      </c>
+      <c r="G3272" t="inlineStr"/>
+      <c r="H3272" t="inlineStr"/>
+    </row>
+    <row r="3273">
+      <c r="A3273" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3273" t="inlineStr">
+        <is>
+          <t>同志</t>
+        </is>
+      </c>
+      <c r="C3273" t="inlineStr">
+        <is>
+          <t>tóngzhì</t>
+        </is>
+      </c>
+      <c r="D3273" t="inlineStr">
+        <is>
+          <t>为共同理想而奋斗的人，也用作对人的称呼。</t>
+        </is>
+      </c>
+      <c r="E3273" t="inlineStr">
+        <is>
+          <t>đồng chí</t>
+        </is>
+      </c>
+      <c r="F3273" t="inlineStr">
+        <is>
+          <t>我们公司里的中国同事互相开玩笑时，也会用“同志”来称呼对方，挺有意思的。</t>
+        </is>
+      </c>
+      <c r="G3273" t="inlineStr"/>
+      <c r="H3273" t="inlineStr"/>
+    </row>
+    <row r="3274">
+      <c r="A3274" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3274" t="inlineStr">
+        <is>
+          <t>打包</t>
+        </is>
+      </c>
+      <c r="C3274" t="inlineStr">
+        <is>
+          <t>dǎbāo</t>
+        </is>
+      </c>
+      <c r="D3274" t="inlineStr">
+        <is>
+          <t>把东西包装起来；也指把没吃完的食物包装带走。</t>
+        </is>
+      </c>
+      <c r="E3274" t="inlineStr">
+        <is>
+          <t>đóng gói, gói mang về</t>
+        </is>
+      </c>
+      <c r="F3274" t="inlineStr">
+        <is>
+          <t>在中国吃饭如果吃不完，我会不好意思地请服务员帮我打包带走。</t>
+        </is>
+      </c>
+      <c r="G3274" t="inlineStr"/>
+      <c r="H3274" t="inlineStr"/>
+    </row>
+    <row r="3275">
+      <c r="A3275" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3275" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C3275" t="inlineStr">
+        <is>
+          <t>dāpèi</t>
+        </is>
+      </c>
+      <c r="D3275" t="inlineStr">
+        <is>
+          <t>按一定的要求安排、配合。</t>
+        </is>
+      </c>
+      <c r="E3275" t="inlineStr">
+        <is>
+          <t>phối hợp, kết hợp</t>
+        </is>
+      </c>
+      <c r="F3275" t="inlineStr">
+        <is>
+          <t>备考HSK6的时候，我把语法和口语练习搭配起来学，效果比单独背语法好多了。</t>
+        </is>
+      </c>
+      <c r="G3275" t="inlineStr"/>
+      <c r="H3275" t="inlineStr"/>
+    </row>
+    <row r="3276">
+      <c r="A3276" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3276" t="inlineStr">
+        <is>
+          <t>图案</t>
+        </is>
+      </c>
+      <c r="C3276" t="inlineStr">
+        <is>
+          <t>tú'àn</t>
+        </is>
+      </c>
+      <c r="D3276" t="inlineStr">
+        <is>
+          <t>有装饰意味的花纹或图形。</t>
+        </is>
+      </c>
+      <c r="E3276" t="inlineStr">
+        <is>
+          <t>hoa văn, họa tiết</t>
+        </is>
+      </c>
+      <c r="F3276" t="inlineStr">
+        <is>
+          <t>我给HSK1的小朋友设计生词卡片时，喜欢加一些简单的图案帮助他们记忆。</t>
+        </is>
+      </c>
+      <c r="G3276" t="inlineStr"/>
+      <c r="H3276" t="inlineStr"/>
+    </row>
+    <row r="3277">
+      <c r="A3277" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3277" t="inlineStr">
+        <is>
+          <t>威望</t>
+        </is>
+      </c>
+      <c r="C3277" t="inlineStr">
+        <is>
+          <t>wēiwàng</t>
+        </is>
+      </c>
+      <c r="D3277" t="inlineStr">
+        <is>
+          <t>使人信服的名声和地位。</t>
+        </is>
+      </c>
+      <c r="E3277" t="inlineStr">
+        <is>
+          <t>uy tín, uy vọng</t>
+        </is>
+      </c>
+      <c r="F3277" t="inlineStr">
+        <is>
+          <t>那位教了三十年中文的老师在我们学校很有威望，学生都很尊敬她。</t>
+        </is>
+      </c>
+      <c r="G3277" t="inlineStr"/>
+      <c r="H3277" t="inlineStr"/>
+    </row>
+    <row r="3278">
+      <c r="A3278" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3278" t="inlineStr">
+        <is>
+          <t>吝啬</t>
+        </is>
+      </c>
+      <c r="C3278" t="inlineStr">
+        <is>
+          <t>lìnsè</t>
+        </is>
+      </c>
+      <c r="D3278" t="inlineStr">
+        <is>
+          <t>过分爱惜自己的财物，不肯拿出来帮助别人。</t>
+        </is>
+      </c>
+      <c r="E3278" t="inlineStr">
+        <is>
+          <t>keo kiệt, hà tiện</t>
+        </is>
+      </c>
+      <c r="F3278" t="inlineStr">
+        <is>
+          <t>我室友对钱很吝啬，但在买中文书和字典上却从不吝啬。</t>
+        </is>
+      </c>
+      <c r="G3278" t="inlineStr"/>
+      <c r="H3278" t="inlineStr"/>
+    </row>
+    <row r="3279">
+      <c r="A3279" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3279" t="inlineStr">
+        <is>
+          <t>尚且</t>
+        </is>
+      </c>
+      <c r="C3279" t="inlineStr">
+        <is>
+          <t>shàngqiě</t>
+        </is>
+      </c>
+      <c r="D3279" t="inlineStr">
+        <is>
+          <t>连词，用于让步，表示“甲事已如此，何况乙事”。</t>
+        </is>
+      </c>
+      <c r="E3279" t="inlineStr">
+        <is>
+          <t>hãy còn, huống hồ</t>
+        </is>
+      </c>
+      <c r="F3279" t="inlineStr">
+        <is>
+          <t>母语者尚且会写错这个汉字，何况我们这些学外语的人呢？</t>
+        </is>
+      </c>
+      <c r="G3279" t="inlineStr"/>
+      <c r="H3279" t="inlineStr"/>
+    </row>
+    <row r="3280">
+      <c r="A3280" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3280" t="inlineStr">
+        <is>
+          <t>不惜</t>
+        </is>
+      </c>
+      <c r="C3280" t="inlineStr">
+        <is>
+          <t>bùxī</t>
+        </is>
+      </c>
+      <c r="D3280" t="inlineStr">
+        <is>
+          <t>不顾惜（代价、力量等），舍得。</t>
+        </is>
+      </c>
+      <c r="E3280" t="inlineStr">
+        <is>
+          <t>không tiếc, bất chấp</t>
+        </is>
+      </c>
+      <c r="F3280" t="inlineStr">
+        <is>
+          <t>为了通过HSK6，我不惜每天早起一个小时背单词。</t>
+        </is>
+      </c>
+      <c r="G3280" t="inlineStr"/>
+      <c r="H3280" t="inlineStr"/>
+    </row>
+    <row r="3281">
+      <c r="A3281" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3281" t="inlineStr">
+        <is>
+          <t>可观</t>
+        </is>
+      </c>
+      <c r="C3281" t="inlineStr">
+        <is>
+          <t>kěguān</t>
+        </is>
+      </c>
+      <c r="D3281" t="inlineStr">
+        <is>
+          <t>（数量、程度等）值得看重，不小。</t>
+        </is>
+      </c>
+      <c r="E3281" t="inlineStr">
+        <is>
+          <t>đáng kể</t>
+        </is>
+      </c>
+      <c r="F3281" t="inlineStr">
+        <is>
+          <t>这学期我教的HSK1-3学生已经有可观的进步，好几个都能简单对话了。</t>
+        </is>
+      </c>
+      <c r="G3281" t="inlineStr"/>
+      <c r="H3281" t="inlineStr"/>
+    </row>
+    <row r="3282">
+      <c r="A3282" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3282" t="inlineStr">
+        <is>
+          <t>皇帝</t>
+        </is>
+      </c>
+      <c r="C3282" t="inlineStr">
+        <is>
+          <t>huángdì</t>
+        </is>
+      </c>
+      <c r="D3282" t="inlineStr">
+        <is>
+          <t>古代帝制国家最高统治者的称号。</t>
+        </is>
+      </c>
+      <c r="E3282" t="inlineStr">
+        <is>
+          <t>hoàng đế</t>
+        </is>
+      </c>
+      <c r="F3282" t="inlineStr">
+        <is>
+          <t>学中国历史课文的时候，我才知道原来“陛下”是用来称呼皇帝的。</t>
+        </is>
+      </c>
+      <c r="G3282" t="inlineStr"/>
+      <c r="H3282" t="inlineStr"/>
+    </row>
+    <row r="3283">
+      <c r="A3283" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3283" t="inlineStr">
+        <is>
+          <t>皇后</t>
+        </is>
+      </c>
+      <c r="C3283" t="inlineStr">
+        <is>
+          <t>huánghòu</t>
+        </is>
+      </c>
+      <c r="D3283" t="inlineStr">
+        <is>
+          <t>皇帝的正妻。</t>
+        </is>
+      </c>
+      <c r="E3283" t="inlineStr">
+        <is>
+          <t>hoàng hậu</t>
+        </is>
+      </c>
+      <c r="F3283" t="inlineStr">
+        <is>
+          <t>上次课文里提到的那位皇后，让我想到很多中国古装剧的情节。</t>
+        </is>
+      </c>
+      <c r="G3283" t="inlineStr"/>
+      <c r="H3283" t="inlineStr"/>
+    </row>
+    <row r="3284">
+      <c r="A3284" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3284" t="inlineStr">
+        <is>
+          <t>销毁</t>
+        </is>
+      </c>
+      <c r="C3284" t="inlineStr">
+        <is>
+          <t>xiāohuǐ</t>
+        </is>
+      </c>
+      <c r="D3284" t="inlineStr">
+        <is>
+          <t>熔化毁掉或烧掉。</t>
+        </is>
+      </c>
+      <c r="E3284" t="inlineStr">
+        <is>
+          <t>tiêu hủy, thiêu hủy</t>
+        </is>
+      </c>
+      <c r="F3284" t="inlineStr">
+        <is>
+          <t>每次考完试，老师都会把不合格的答题纸集中销毁。</t>
+        </is>
+      </c>
+      <c r="G3284" t="inlineStr"/>
+      <c r="H3284" t="inlineStr"/>
+    </row>
+    <row r="3285">
+      <c r="A3285" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3285" t="inlineStr">
+        <is>
+          <t>手艺</t>
+        </is>
+      </c>
+      <c r="C3285" t="inlineStr">
+        <is>
+          <t>shǒuyì</t>
+        </is>
+      </c>
+      <c r="D3285" t="inlineStr">
+        <is>
+          <t>手工技术。</t>
+        </is>
+      </c>
+      <c r="E3285" t="inlineStr">
+        <is>
+          <t>tay nghề, thủ nghệ</t>
+        </is>
+      </c>
+      <c r="F3285" t="inlineStr">
+        <is>
+          <t>我的中国同事的妈妈手艺特别好，包的饺子比饭店做的还好吃。</t>
+        </is>
+      </c>
+      <c r="G3285" t="inlineStr"/>
+      <c r="H3285" t="inlineStr"/>
+    </row>
+    <row r="3286">
+      <c r="A3286" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3286" t="inlineStr">
+        <is>
+          <t>凝聚</t>
+        </is>
+      </c>
+      <c r="C3286" t="inlineStr">
+        <is>
+          <t>níngjù</t>
+        </is>
+      </c>
+      <c r="D3286" t="inlineStr">
+        <is>
+          <t>（气体变成液体或液体变成固体）聚集；比喻力量、感情等聚集在一起。</t>
+        </is>
+      </c>
+      <c r="E3286" t="inlineStr">
+        <is>
+          <t>ngưng tụ, kết tụ</t>
+        </is>
+      </c>
+      <c r="F3286" t="inlineStr">
+        <is>
+          <t>这份生词表凝聚了我三年自学中文的心血。</t>
+        </is>
+      </c>
+      <c r="G3286" t="inlineStr"/>
+      <c r="H3286" t="inlineStr"/>
+    </row>
+    <row r="3287">
+      <c r="A3287" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3287" t="inlineStr">
+        <is>
+          <t>结晶</t>
+        </is>
+      </c>
+      <c r="C3287" t="inlineStr">
+        <is>
+          <t>jiéjīng</t>
+        </is>
+      </c>
+      <c r="D3287" t="inlineStr">
+        <is>
+          <t>物质从液态变成固态；比喻辛勤劳动获得的成果。</t>
+        </is>
+      </c>
+      <c r="E3287" t="inlineStr">
+        <is>
+          <t>kết tinh, thành quả</t>
+        </is>
+      </c>
+      <c r="F3287" t="inlineStr">
+        <is>
+          <t>我做的这套HSK6生词学习页是我多次备课经验的结晶。</t>
+        </is>
+      </c>
+      <c r="G3287" t="inlineStr"/>
+      <c r="H3287" t="inlineStr"/>
+    </row>
+    <row r="3288">
+      <c r="A3288" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3288" t="inlineStr">
+        <is>
+          <t>籍贯</t>
+        </is>
+      </c>
+      <c r="C3288" t="inlineStr">
+        <is>
+          <t>jíguàn</t>
+        </is>
+      </c>
+      <c r="D3288" t="inlineStr">
+        <is>
+          <t>祖居或个人出生的地方。</t>
+        </is>
+      </c>
+      <c r="E3288" t="inlineStr">
+        <is>
+          <t>nguyên quán, quê quán</t>
+        </is>
+      </c>
+      <c r="F3288" t="inlineStr">
+        <is>
+          <t>每次填中国的表格，籍贯那一栏我都要想一下该怎么解释我是越南人。</t>
+        </is>
+      </c>
+      <c r="G3288" t="inlineStr"/>
+      <c r="H3288" t="inlineStr"/>
+    </row>
+    <row r="3289">
+      <c r="A3289" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3289" t="inlineStr">
+        <is>
+          <t>采购</t>
+        </is>
+      </c>
+      <c r="C3289" t="inlineStr">
+        <is>
+          <t>cǎigòu</t>
+        </is>
+      </c>
+      <c r="D3289" t="inlineStr">
+        <is>
+          <t>（为机关、企业等）选购物资，也指从事这项工作的人。</t>
+        </is>
+      </c>
+      <c r="E3289" t="inlineStr">
+        <is>
+          <t>mua sắm, thu mua</t>
+        </is>
+      </c>
+      <c r="F3289" t="inlineStr">
+        <is>
+          <t>我们公司的采购部门这周要跟一家中国供应商谈价格，我被叫去帮忙做口译。</t>
+        </is>
+      </c>
+      <c r="G3289" t="inlineStr"/>
+      <c r="H3289" t="inlineStr"/>
+    </row>
+    <row r="3290">
+      <c r="A3290" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3290" t="inlineStr">
+        <is>
+          <t>创业</t>
+        </is>
+      </c>
+      <c r="C3290" t="inlineStr">
+        <is>
+          <t>chuàngyè</t>
+        </is>
+      </c>
+      <c r="D3290" t="inlineStr">
+        <is>
+          <t>开创事业。</t>
+        </is>
+      </c>
+      <c r="E3290" t="inlineStr">
+        <is>
+          <t>khởi nghiệp, lập nghiệp</t>
+        </is>
+      </c>
+      <c r="F3290" t="inlineStr">
+        <is>
+          <t>我认识的一位中国朋友辞职后自己创业，开了一家小小的语言培训中心。</t>
+        </is>
+      </c>
+      <c r="G3290" t="inlineStr"/>
+      <c r="H3290" t="inlineStr"/>
+    </row>
+    <row r="3291">
+      <c r="A3291" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3291" t="inlineStr">
+        <is>
+          <t>神圣</t>
+        </is>
+      </c>
+      <c r="C3291" t="inlineStr">
+        <is>
+          <t>shénshèng</t>
+        </is>
+      </c>
+      <c r="D3291" t="inlineStr">
+        <is>
+          <t>极其崇高、庄严，不可亵渎。</t>
+        </is>
+      </c>
+      <c r="E3291" t="inlineStr">
+        <is>
+          <t>thần thánh, thiêng liêng</t>
+        </is>
+      </c>
+      <c r="F3291" t="inlineStr">
+        <is>
+          <t>我觉得教小朋友学中文是一件很神圣的工作，因为我在帮他们打开一扇新世界的门。</t>
+        </is>
+      </c>
+      <c r="G3291" t="inlineStr"/>
+      <c r="H3291" t="inlineStr"/>
+    </row>
+    <row r="3292">
+      <c r="A3292" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3292" t="inlineStr">
+        <is>
+          <t>使命</t>
+        </is>
+      </c>
+      <c r="C3292" t="inlineStr">
+        <is>
+          <t>shǐmìng</t>
+        </is>
+      </c>
+      <c r="D3292" t="inlineStr">
+        <is>
+          <t>重大的责任。</t>
+        </is>
+      </c>
+      <c r="E3292" t="inlineStr">
+        <is>
+          <t>sứ mệnh</t>
+        </is>
+      </c>
+      <c r="F3292" t="inlineStr">
+        <is>
+          <t>我给自己定的使命是三年内把HSK6考到220分以上。</t>
+        </is>
+      </c>
+      <c r="G3292" t="inlineStr"/>
+      <c r="H3292" t="inlineStr"/>
+    </row>
+    <row r="3293">
+      <c r="A3293" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3293" t="inlineStr">
+        <is>
+          <t>看待</t>
+        </is>
+      </c>
+      <c r="C3293" t="inlineStr">
+        <is>
+          <t>kàndài</t>
+        </is>
+      </c>
+      <c r="D3293" t="inlineStr">
+        <is>
+          <t>对待，对人或事物抱着某种看法。</t>
+        </is>
+      </c>
+      <c r="E3293" t="inlineStr">
+        <is>
+          <t>nhìn nhận, đối xử</t>
+        </is>
+      </c>
+      <c r="F3293" t="inlineStr">
+        <is>
+          <t>刚到中国工作的时候，我很担心同事会怎么看待我这个外国人。</t>
+        </is>
+      </c>
+      <c r="G3293" t="inlineStr"/>
+      <c r="H3293" t="inlineStr"/>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3294" t="inlineStr">
+        <is>
+          <t>家属</t>
+        </is>
+      </c>
+      <c r="C3294" t="inlineStr">
+        <is>
+          <t>jiāshǔ</t>
+        </is>
+      </c>
+      <c r="D3294" t="inlineStr">
+        <is>
+          <t>家庭成员（多指职工本人以外的）。</t>
+        </is>
+      </c>
+      <c r="E3294" t="inlineStr">
+        <is>
+          <t>người thân, gia quyến</t>
+        </is>
+      </c>
+      <c r="F3294" t="inlineStr">
+        <is>
+          <t>公司春节聚餐的时候，也邀请了员工的家属一起参加。</t>
+        </is>
+      </c>
+      <c r="G3294" t="inlineStr"/>
+      <c r="H3294" t="inlineStr"/>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3295" t="inlineStr">
+        <is>
+          <t>泛滥</t>
+        </is>
+      </c>
+      <c r="C3295" t="inlineStr">
+        <is>
+          <t>fànlàn</t>
+        </is>
+      </c>
+      <c r="D3295" t="inlineStr">
+        <is>
+          <t>（水）漫溢；比喻坏的事物不受限制地传播。</t>
+        </is>
+      </c>
+      <c r="E3295" t="inlineStr">
+        <is>
+          <t>tràn lan, lũ lụt</t>
+        </is>
+      </c>
+      <c r="F3295" t="inlineStr">
+        <is>
+          <t>网上关于学中文“速成”的错误方法很泛滥，我都是靠踏实练习才进步的。</t>
+        </is>
+      </c>
+      <c r="G3295" t="inlineStr"/>
+      <c r="H3295" t="inlineStr"/>
+    </row>
+    <row r="3296">
+      <c r="A3296" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3296" t="inlineStr">
+        <is>
+          <t>表彰</t>
+        </is>
+      </c>
+      <c r="C3296" t="inlineStr">
+        <is>
+          <t>biǎozhāng</t>
+        </is>
+      </c>
+      <c r="D3296" t="inlineStr">
+        <is>
+          <t>表扬先进人物或事迹。</t>
+        </is>
+      </c>
+      <c r="E3296" t="inlineStr">
+        <is>
+          <t>biểu dương, tuyên dương</t>
+        </is>
+      </c>
+      <c r="F3296" t="inlineStr">
+        <is>
+          <t>这学期表现最好的HSK1学生，我打算在期末课上公开表彰他。</t>
+        </is>
+      </c>
+      <c r="G3296" t="inlineStr"/>
+      <c r="H3296" t="inlineStr"/>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3297" t="inlineStr">
+        <is>
+          <t>荣誉</t>
+        </is>
+      </c>
+      <c r="C3297" t="inlineStr">
+        <is>
+          <t>róngyù</t>
+        </is>
+      </c>
+      <c r="D3297" t="inlineStr">
+        <is>
+          <t>光荣的名誉。</t>
+        </is>
+      </c>
+      <c r="E3297" t="inlineStr">
+        <is>
+          <t>vinh dự, danh dự</t>
+        </is>
+      </c>
+      <c r="F3297" t="inlineStr">
+        <is>
+          <t>能被邀请去帮公司培训新员工的中文，我觉得是一种荣誉。</t>
+        </is>
+      </c>
+      <c r="G3297" t="inlineStr"/>
+      <c r="H3297" t="inlineStr"/>
+    </row>
+    <row r="3298">
+      <c r="A3298" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3298" t="inlineStr">
+        <is>
+          <t>奖励</t>
+        </is>
+      </c>
+      <c r="C3298" t="inlineStr">
+        <is>
+          <t>jiǎnglì</t>
+        </is>
+      </c>
+      <c r="D3298" t="inlineStr">
+        <is>
+          <t>给予荣誉或财物来鼓励。</t>
+        </is>
+      </c>
+      <c r="E3298" t="inlineStr">
+        <is>
+          <t>khen thưởng</t>
+        </is>
+      </c>
+      <c r="F3298" t="inlineStr">
+        <is>
+          <t>为了鼓励学生认真背生词，我每周都会奖励表现最好的人一张小贴纸。</t>
+        </is>
+      </c>
+      <c r="G3298" t="inlineStr"/>
+      <c r="H3298" t="inlineStr"/>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3299" t="inlineStr">
+        <is>
+          <t>称号</t>
+        </is>
+      </c>
+      <c r="C3299" t="inlineStr">
+        <is>
+          <t>chēnghào</t>
+        </is>
+      </c>
+      <c r="D3299" t="inlineStr">
+        <is>
+          <t>给予某人或某集体的名称（多为光荣的）。</t>
+        </is>
+      </c>
+      <c r="E3299" t="inlineStr">
+        <is>
+          <t>danh hiệu</t>
+        </is>
+      </c>
+      <c r="F3299" t="inlineStr">
+        <is>
+          <t>我给自己定了一个小目标——拿到“HSK6高分”这个称号。</t>
+        </is>
+      </c>
+      <c r="G3299" t="inlineStr"/>
+      <c r="H3299" t="inlineStr"/>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3300" t="inlineStr">
+        <is>
+          <t>争气</t>
+        </is>
+      </c>
+      <c r="C3300" t="inlineStr">
+        <is>
+          <t>zhēngqì</t>
+        </is>
+      </c>
+      <c r="D3300" t="inlineStr">
+        <is>
+          <t>力求做好，不落后，不甘示弱。</t>
+        </is>
+      </c>
+      <c r="E3300" t="inlineStr">
+        <is>
+          <t>quyết chí phấn đấu, không chịu thua kém</t>
+        </is>
+      </c>
+      <c r="F3300" t="inlineStr">
+        <is>
+          <t>这次模拟考没考好，我告诉自己下次一定要争气。</t>
+        </is>
+      </c>
+      <c r="G3300" t="inlineStr"/>
+      <c r="H3300" t="inlineStr"/>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3301" t="inlineStr">
+        <is>
+          <t>沾光</t>
+        </is>
+      </c>
+      <c r="C3301" t="inlineStr">
+        <is>
+          <t>zhānguāng</t>
+        </is>
+      </c>
+      <c r="D3301" t="inlineStr">
+        <is>
+          <t>因为跟别人或事物有关系而得到好处。</t>
+        </is>
+      </c>
+      <c r="E3301" t="inlineStr">
+        <is>
+          <t>được thơm lây, hưởng ké</t>
+        </is>
+      </c>
+      <c r="F3301" t="inlineStr">
+        <is>
+          <t>我教的一个学生HSK考了满分，同事都说我沾了学生的光。</t>
+        </is>
+      </c>
+      <c r="G3301" t="inlineStr"/>
+      <c r="H3301" t="inlineStr"/>
+    </row>
+    <row r="3302">
+      <c r="A3302" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3302" t="inlineStr">
+        <is>
+          <t>品质</t>
+        </is>
+      </c>
+      <c r="C3302" t="inlineStr">
+        <is>
+          <t>pǐnzhì</t>
+        </is>
+      </c>
+      <c r="D3302" t="inlineStr">
+        <is>
+          <t>人的行为、作风所表现的思想品格；也指物品的质量。</t>
+        </is>
+      </c>
+      <c r="E3302" t="inlineStr">
+        <is>
+          <t>phẩm chất, chất lượng</t>
+        </is>
+      </c>
+      <c r="F3302" t="inlineStr">
+        <is>
+          <t>我很欣赏那位老师认真负责的品质，所以一直把她当作自己教学的榜样。</t>
+        </is>
+      </c>
+      <c r="G3302" t="inlineStr"/>
+      <c r="H3302" t="inlineStr"/>
+    </row>
+    <row r="3303">
+      <c r="A3303" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3303" t="inlineStr">
+        <is>
+          <t>乐意</t>
+        </is>
+      </c>
+      <c r="C3303" t="inlineStr">
+        <is>
+          <t>lèyì</t>
+        </is>
+      </c>
+      <c r="D3303" t="inlineStr">
+        <is>
+          <t>愿意，心甘情愿。</t>
+        </is>
+      </c>
+      <c r="E3303" t="inlineStr">
+        <is>
+          <t>sẵn lòng, vui lòng</t>
+        </is>
+      </c>
+      <c r="F3303" t="inlineStr">
+        <is>
+          <t>只要学生有问题，我都很乐意用中文和越南语两种语言解释给他们听。</t>
+        </is>
+      </c>
+      <c r="G3303" t="inlineStr"/>
+      <c r="H3303" t="inlineStr"/>
+    </row>
+    <row r="3304">
+      <c r="A3304" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3304" t="inlineStr">
+        <is>
+          <t>次序</t>
+        </is>
+      </c>
+      <c r="C3304" t="inlineStr">
+        <is>
+          <t>cìxù</t>
+        </is>
+      </c>
+      <c r="D3304" t="inlineStr">
+        <is>
+          <t>事物在一定条件下的排列顺序。</t>
+        </is>
+      </c>
+      <c r="E3304" t="inlineStr">
+        <is>
+          <t>thứ tự, trình tự</t>
+        </is>
+      </c>
+      <c r="F3304" t="inlineStr">
+        <is>
+          <t>我把HSK6生词按难易次序排列，先学简单的，再挑战难的成语。</t>
+        </is>
+      </c>
+      <c r="G3304" t="inlineStr"/>
+      <c r="H3304" t="inlineStr"/>
+    </row>
+    <row r="3305">
+      <c r="A3305" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3305" t="inlineStr">
+        <is>
+          <t>精益求精</t>
+        </is>
+      </c>
+      <c r="C3305" t="inlineStr">
+        <is>
+          <t>jīngyìqiújīng</t>
+        </is>
+      </c>
+      <c r="D3305" t="inlineStr">
+        <is>
+          <t>已经很好了，还要求更好。</t>
+        </is>
+      </c>
+      <c r="E3305" t="inlineStr">
+        <is>
+          <t>cầu toàn, không ngừng hoàn thiện</t>
+        </is>
+      </c>
+      <c r="F3305" t="inlineStr">
+        <is>
+          <t>我的中文写作已经能拿高分了，但我还是想精益求精，继续减少小语法错误。</t>
+        </is>
+      </c>
+      <c r="G3305" t="inlineStr"/>
+      <c r="H3305" t="inlineStr"/>
+    </row>
+    <row r="3306">
+      <c r="A3306" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3306" t="inlineStr">
+        <is>
+          <t>朝代</t>
+        </is>
+      </c>
+      <c r="C3306" t="inlineStr">
+        <is>
+          <t>cháodài</t>
+        </is>
+      </c>
+      <c r="D3306" t="inlineStr">
+        <is>
+          <t>建立国号的君主或整个王朝所统治的时代。</t>
+        </is>
+      </c>
+      <c r="E3306" t="inlineStr">
+        <is>
+          <t>triều đại</t>
+        </is>
+      </c>
+      <c r="F3306" t="inlineStr">
+        <is>
+          <t>我教HSK1的孩子们唱一首关于中国朝代顺序的儿歌，帮助他们记忆。</t>
+        </is>
+      </c>
+      <c r="G3306" t="inlineStr"/>
+      <c r="H3306" t="inlineStr"/>
+    </row>
+    <row r="3307">
+      <c r="A3307" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3307" t="inlineStr">
+        <is>
+          <t>拥护</t>
+        </is>
+      </c>
+      <c r="C3307" t="inlineStr">
+        <is>
+          <t>yōnghù</t>
+        </is>
+      </c>
+      <c r="D3307" t="inlineStr">
+        <is>
+          <t>拥戴支持（某种主张、领导人或政党等）。</t>
+        </is>
+      </c>
+      <c r="E3307" t="inlineStr">
+        <is>
+          <t>ủng hộ</t>
+        </is>
+      </c>
+      <c r="F3307" t="inlineStr">
+        <is>
+          <t>老师提出增加口语练习的时间，我们全班同学都很拥护这个提议。</t>
+        </is>
+      </c>
+      <c r="G3307" t="inlineStr"/>
+      <c r="H3307" t="inlineStr"/>
+    </row>
+    <row r="3308">
+      <c r="A3308" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3308" t="inlineStr">
+        <is>
+          <t>威信</t>
+        </is>
+      </c>
+      <c r="C3308" t="inlineStr">
+        <is>
+          <t>wēixìn</t>
+        </is>
+      </c>
+      <c r="D3308" t="inlineStr">
+        <is>
+          <t>使人信服的力量和威望。</t>
+        </is>
+      </c>
+      <c r="E3308" t="inlineStr">
+        <is>
+          <t>uy tín</t>
+        </is>
+      </c>
+      <c r="F3308" t="inlineStr">
+        <is>
+          <t>一位老师要在学生心里树立威信，光靠严厉是不够的，还要靠专业和耐心。</t>
+        </is>
+      </c>
+      <c r="G3308" t="inlineStr"/>
+      <c r="H3308" t="inlineStr"/>
+    </row>
+    <row r="3309">
+      <c r="A3309" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3309" t="inlineStr">
+        <is>
+          <t>当代</t>
+        </is>
+      </c>
+      <c r="C3309" t="inlineStr">
+        <is>
+          <t>dāngdài</t>
+        </is>
+      </c>
+      <c r="D3309" t="inlineStr">
+        <is>
+          <t>当前这个时代。</t>
+        </is>
+      </c>
+      <c r="E3309" t="inlineStr">
+        <is>
+          <t>đương đại, đương thời</t>
+        </is>
+      </c>
+      <c r="F3309" t="inlineStr">
+        <is>
+          <t>我很喜欢读当代中国作家写的短篇小说，语言比较贴近日常生活。</t>
+        </is>
+      </c>
+      <c r="G3309" t="inlineStr"/>
+      <c r="H3309" t="inlineStr"/>
+    </row>
+    <row r="3310">
+      <c r="A3310" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3310" t="inlineStr">
+        <is>
+          <t>级别</t>
+        </is>
+      </c>
+      <c r="C3310" t="inlineStr">
+        <is>
+          <t>jíbié</t>
+        </is>
+      </c>
+      <c r="D3310" t="inlineStr">
+        <is>
+          <t>按等级划分的差别。</t>
+        </is>
+      </c>
+      <c r="E3310" t="inlineStr">
+        <is>
+          <t>cấp bậc, đẳng cấp</t>
+        </is>
+      </c>
+      <c r="F3310" t="inlineStr">
+        <is>
+          <t>HSK考试分成好几个级别，我现在正在为最高级别HSK6努力。</t>
+        </is>
+      </c>
+      <c r="G3310" t="inlineStr"/>
+      <c r="H3310" t="inlineStr"/>
+    </row>
+    <row r="3311">
+      <c r="A3311" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3311" t="inlineStr">
+        <is>
+          <t>泰斗</t>
+        </is>
+      </c>
+      <c r="C3311" t="inlineStr">
+        <is>
+          <t>tàidǒu</t>
+        </is>
+      </c>
+      <c r="D3311" t="inlineStr">
+        <is>
+          <t>比喻在某一方面负有名望、为众人所敬仰的人。</t>
+        </is>
+      </c>
+      <c r="E3311" t="inlineStr">
+        <is>
+          <t>bậc thái đẩu, cây đa cây đề</t>
+        </is>
+      </c>
+      <c r="F3311" t="inlineStr">
+        <is>
+          <t>我很崇拜的一位汉语教学泰斗写了很多关于HSK6写作方法的书。</t>
+        </is>
+      </c>
+      <c r="G3311" t="inlineStr"/>
+      <c r="H3311" t="inlineStr"/>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="inlineStr">
+        <is>
+          <t>Bài 34</t>
+        </is>
+      </c>
+      <c r="B3312" t="inlineStr">
+        <is>
+          <t>温柔</t>
+        </is>
+      </c>
+      <c r="C3312" t="inlineStr">
+        <is>
+          <t>wēnróu</t>
+        </is>
+      </c>
+      <c r="D3312" t="inlineStr">
+        <is>
+          <t>形容脾气好，有不同意见时能顺从别人的意思，多用于形容女性的性情、语言。</t>
+        </is>
+      </c>
+      <c r="E3312" t="inlineStr">
+        <is>
+          <t>dịu dàng, ôn nhu</t>
+        </is>
+      </c>
+      <c r="F3312" t="inlineStr">
+        <is>
+          <t>我们班有位女同学说话总是温柔又有耐心，跟她一起练口语我一点也不紧张。</t>
+        </is>
+      </c>
+      <c r="G3312" t="inlineStr"/>
+      <c r="H3312" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H3025">
